--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{917D7944-7ABB-E940-B937-0D46581BEA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F9A8E57-8111-474C-9B1D-A9F8A6B0FA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issuer" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="215">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -63,385 +63,418 @@
     <t>SERIES: Trading (non-additive)</t>
   </si>
   <si>
-    <t>MSGS</t>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>FAIR ISAAC ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>RHMG</t>
+  </si>
+  <si>
+    <t>MSLYT26S</t>
+  </si>
+  <si>
+    <t>4901</t>
+  </si>
+  <si>
+    <t>NICE</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>RCIb</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
+    <t>TYL</t>
+  </si>
+  <si>
+    <t>T CN</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>WTC</t>
+  </si>
+  <si>
+    <t>WSP</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>LAUR</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>CNXC</t>
   </si>
   <si>
     <t>TEPRF</t>
   </si>
   <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>MADISON SQUARE GARDEN SPORT CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>Instrument</t>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>FWONK</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>6752</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>SAPG</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>QRVO</t>
+  </si>
+  <si>
+    <t>MSLYT26L</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>ETSY</t>
+  </si>
+  <si>
+    <t>SPHR</t>
+  </si>
+  <si>
+    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
   </si>
   <si>
     <t>AUTODESK ORD (NMS)</t>
   </si>
   <si>
-    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t>NICE</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>TYL</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>SATS</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>RHMG</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>ARM</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>WTC</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>WSP</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>CDW</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>LAUR</t>
-  </si>
-  <si>
-    <t>STN</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>FWONK</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>6857</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>BILL</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>SAPG</t>
-  </si>
-  <si>
-    <t>6752</t>
-  </si>
-  <si>
-    <t>MKSI</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>QRVO</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>VSAT</t>
-  </si>
-  <si>
-    <t>DAST</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>PYPL</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>LBTYA</t>
-  </si>
-  <si>
-    <t>TTWO</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>GFS</t>
-  </si>
-  <si>
-    <t>ENPH</t>
-  </si>
-  <si>
-    <t>LBTYK</t>
-  </si>
-  <si>
-    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
-  </si>
-  <si>
     <t>CINTAS ORD (NMS)</t>
   </si>
   <si>
+    <t>EQUIFAX ORD (NYS)</t>
+  </si>
+  <si>
     <t>CANON ORD (TYO) CFD</t>
   </si>
   <si>
-    <t>EQUIFAX ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FAIR ISAAC ORD (NYS)</t>
+    <t>LOGITECH N ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CROWDSTRIKE HOLDINGS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>VERISK ANALYTICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>EBAY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>SERVICETITAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
   </si>
   <si>
     <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
   </si>
   <si>
-    <t>INFOSYS ADR REP ORD (NYS)</t>
-  </si>
-  <si>
-    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>VERISK ANALYTICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NEW YORK TIMES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EBAY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+    <t>SAMSARA CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>RHEINMETALL ORD (GER)</t>
+  </si>
+  <si>
+    <t>MSLYT26S INDEX CFD</t>
+  </si>
+  <si>
+    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
   </si>
   <si>
     <t>NICE ADR REP 1 ORD (NMS)</t>
   </si>
   <si>
-    <t>CROWDSTRIKE HOLDINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>UBER TECHNOLOGIES INC (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SANRIO ORD (TYO) CFD</t>
   </si>
   <si>
     <t>REA GROUP ORD (ASX) CFD</t>
@@ -450,139 +483,133 @@
     <t>GARTNER ORD (NYS)</t>
   </si>
   <si>
-    <t>QUALCOMM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
+    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
+  </si>
+  <si>
+    <t>CDW ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TELUS ORD (TOR)</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SLM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SEZZLE INC (NMS)</t>
+  </si>
+  <si>
+    <t>DUOLINGO CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ARISTA NETWORKS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ADOBE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ROBERT HALF ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CARGURUS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SYMBOTIC CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>QUALYS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WISETECH GLOBAL ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>WSP GLOBAL ORD (TOR)</t>
+  </si>
+  <si>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
   </si>
   <si>
     <t>DATADOG CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>APPLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SAMSARA CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ECHOSTAR CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LOGITECH N ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RHEINMETALL ORD (GER)</t>
-  </si>
-  <si>
-    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CARGURUS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARM HOLDINGS ADR (NMS)</t>
-  </si>
-  <si>
-    <t>ARISTA NETWORKS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>WISETECH GLOBAL ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>SYMBOTIC CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WSP GLOBAL ORD (TOR)</t>
-  </si>
-  <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBERT HALF ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CDW ORD (NMS)</t>
-  </si>
-  <si>
-    <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SEZZLE INC (NMS)</t>
-  </si>
-  <si>
-    <t>NETAPP ORD (NMS)</t>
+    <t>WIX.COM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
+  </si>
+  <si>
+    <t>LAUREATE EDUCATION ORD (NMS)</t>
   </si>
   <si>
     <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
   </si>
   <si>
-    <t>RH ORD (NYS)</t>
-  </si>
-  <si>
-    <t>QUALYS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WIX.COM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LAUREATE EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
     <t>STANTEC ORD (TOR)</t>
   </si>
   <si>
     <t>CONCENTRIX ORD (NMS)</t>
   </si>
   <si>
+    <t>BLOCK CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
     <t>ALPHABET CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>BLOCK CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>BROADCOM ORD (NMS)</t>
+    <t>AMAZON COM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>MAPLEBEAR ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AT&amp;T ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ADVANTEST ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>AUTO1 GROUP ORD (GER)</t>
+  </si>
+  <si>
+    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
+  </si>
+  <si>
+    <t>IRON MOUNTAIN ORD (NYS)</t>
   </si>
   <si>
     <t>LYFT CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
-  </si>
-  <si>
-    <t>IRON MOUNTAIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>MAPLEBEAR ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>AUTO1 GROUP ORD (GER)</t>
+    <t>ORACLE ORD (NYS)</t>
   </si>
   <si>
     <t>ROBLOX CL A ORD (NYS)</t>
@@ -591,67 +618,70 @@
     <t>TESLA ORD (NMS)</t>
   </si>
   <si>
+    <t>TRIMBLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PANASONIC HLDG ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>EATON ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
+    <t>DRAFTKINGS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SK HYNIX ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>SAP ORD (GER)</t>
+  </si>
+  <si>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
+  </si>
+  <si>
+    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>STMICROELECTRONICS ADR (NYS)</t>
+  </si>
+  <si>
+    <t>QORVO ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MSLYT26L INDEX CFD</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
+    <t>WAYFAIR CL A ORD (NYS)</t>
+  </si>
+  <si>
     <t>BILL HOLDINGS ORD (NYS)</t>
   </si>
   <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TRIMBLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SAP ORD (GER)</t>
-  </si>
-  <si>
-    <t>PANASONIC HLDG ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>MKS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ORACLE ORD (NYS)</t>
-  </si>
-  <si>
-    <t>QORVO ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
-  </si>
-  <si>
-    <t>VIASAT ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DASSAULT SYSTEM ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>PAYPAL HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>APPLIED MATERIAL ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LIBERTY GLOBAL CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TAKE TWO INTERACTIVE SOFTWARE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WAYFAIR CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>GLOBALFOUNDRIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ENPHASE ENERGY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LIBERTY GLOBAL CL C ORD (NMS)</t>
+    <t>DYNATRACE ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EVERPURE CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SANDISK ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ETSY ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CLOUDFLARE CL A ORD (NYS)</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q200"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1275,24 +1305,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>7.9455865026348329</v>
+        <v>10.114913123044515</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D45" si="0">IF(B11="","",(C11/100))</f>
-        <v>7.9455865026348327E-2</v>
+        <f t="shared" ref="D11:D48" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10114913123044515</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-4.5415037047817943</v>
+        <v>-7.0254505788774777</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-4.5415037047817942E-2</v>
+        <v>-7.0254505788774776E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -1313,24 +1343,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="10">
-        <v>6.8708326027263427</v>
+        <v>7.4234234046912162</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>6.8708326027263428E-2</v>
+        <v>7.4234234046912165E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.4861190140976008</v>
+        <v>-5.1423608203890385</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-4.4861190140976011E-2</v>
+        <v>-5.1423608203890386E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1341,977 +1371,1004 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="10">
-        <v>5.4774151013854411</v>
+        <v>6.8676479221103426</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.4774151013854411E-2</v>
+        <v>6.8676479221103426E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-4.2197871427778058</v>
+        <v>-5.0438911761510656</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2197871427778061E-2</v>
+        <v>-5.0438911761510656E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" s="10">
-        <v>4.5116088507663319</v>
+        <v>5.7637035126237404</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.511608850766332E-2</v>
+        <v>5.7637035126237406E-2</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.0709587400507496</v>
+        <v>-4.7271739906737658</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0709587400507494E-2</v>
+        <v>-4.7271739906737657E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="10">
-        <v>3.5422600230505501</v>
+        <v>5.0984983719649195</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>3.5422600230505502E-2</v>
+        <v>5.0984983719649192E-2</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-3.7998366529676115</v>
+        <v>-4.6162214322468786</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7998366529676114E-2</v>
+        <v>-4.6162214322468788E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" s="10">
-        <v>3.5143806042718597</v>
+        <v>4.8088529399076929</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>3.5143806042718599E-2</v>
+        <v>4.8088529399076929E-2</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.6438888925374049</v>
+        <v>-4.0816463521898836</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6438888925374051E-2</v>
+        <v>-4.0816463521898834E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" s="10">
-        <v>3.386336187266318</v>
+        <v>4.4356524193573295</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>3.3863361872663179E-2</v>
+        <v>4.4356524193573298E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.3311301387428793</v>
+        <v>-3.7471572765923411</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3311301387428792E-2</v>
+        <v>-3.747157276592341E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" s="10">
-        <v>3.2809192968749947</v>
+        <v>4.2134059992904564</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>3.2809192968749949E-2</v>
+        <v>4.2134059992904566E-2</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.0770632976275549</v>
+        <v>-3.6985352047410642</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0770632976275549E-2</v>
+        <v>-3.6985352047410644E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C19" s="10">
-        <v>3.255709782112409</v>
+        <v>4.0626808900841747</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.2557097821124092E-2</v>
+        <v>4.0626808900841749E-2</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.0406120817445292</v>
+        <v>-3.5731192105080143</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0406120817445294E-2</v>
+        <v>-3.5731192105080141E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" s="10">
-        <v>3.1398745010833453</v>
+        <v>3.9255443710187592</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.1398745010833451E-2</v>
+        <v>3.925544371018759E-2</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-2.9854189323525038</v>
+        <v>-3.4767550578903101</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9854189323525036E-2</v>
+        <v>-3.47675505789031E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="10">
-        <v>3.0452765229632717</v>
+        <v>3.7466845055356335</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.0452765229632715E-2</v>
+        <v>3.7466845055356336E-2</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8785752106651246</v>
+        <v>-3.3787963458236683</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8785752106651245E-2</v>
+        <v>-3.3787963458236682E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" s="10">
-        <v>2.9959320847657147</v>
+        <v>3.621485491156577</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>2.9959320847657147E-2</v>
+        <v>3.6214854911565772E-2</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.8589949056764121</v>
+        <v>-3.2867573111023902</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8589949056764121E-2</v>
+        <v>-3.2867573111023902E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" s="10">
-        <v>2.5778778653644032</v>
+        <v>3.5857433479229086</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>2.5778778653644033E-2</v>
+        <v>3.5857433479229088E-2</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.7557344041589866</v>
+        <v>-2.9874661452109144</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7557344041589868E-2</v>
+        <v>-2.9874661452109142E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" s="10">
-        <v>2.5701980540066631</v>
+        <v>3.4417504543854469</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>2.570198054006663E-2</v>
+        <v>3.441750454385447E-2</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.7443894379250495</v>
+        <v>-2.9113669260193382</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7443894379250496E-2</v>
+        <v>-2.9113669260193382E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25" s="10">
-        <v>2.2203494692308459</v>
+        <v>3.2804380186953459</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>2.2203494692308458E-2</v>
+        <v>3.2804380186953461E-2</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.7360279903436027</v>
+        <v>-2.873761068289765</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7360279903436025E-2</v>
+        <v>-2.8737610682897648E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="10">
-        <v>2.1221052885896698</v>
+        <v>3.2750090472635747</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.1221052885896697E-2</v>
+        <v>3.2750090472635746E-2</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.5203576838404471</v>
+        <v>-2.6738666363436119</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5203576838404473E-2</v>
+        <v>-2.6738666363436119E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" s="10">
-        <v>2.1070422968944205</v>
+        <v>2.8824728500031798</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.1070422968944204E-2</v>
+        <v>2.8824728500031798E-2</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.5088141142200486</v>
+        <v>-2.5441864922387301</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5088141142200485E-2</v>
+        <v>-2.54418649223873E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" s="10">
-        <v>2.0833059263540186</v>
+        <v>2.7187939303252557</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.0833059263540187E-2</v>
+        <v>2.7187939303252556E-2</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.3901766230001549</v>
+        <v>-2.5030046864978872</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.390176623000155E-2</v>
+        <v>-2.5030046864978873E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="10">
-        <v>2.067807872177946</v>
+        <v>2.6809664494920611</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.0678078721779462E-2</v>
+        <v>2.6809664494920612E-2</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.330264121003145</v>
+        <v>-2.4950477813923095</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.330264121003145E-2</v>
+        <v>-2.4950477813923094E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="10">
-        <v>1.9805874045425345</v>
+        <v>2.6409346567269854</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>1.9805874045425345E-2</v>
+        <v>2.6409346567269853E-2</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1837118284709063</v>
+        <v>-2.3917355855546796</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1837118284709064E-2</v>
+        <v>-2.3917355855546794E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" s="10">
-        <v>1.9712322914691018</v>
+        <v>2.5432508064299917</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>1.9712322914691018E-2</v>
+        <v>2.5432508064299916E-2</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0933344605618776</v>
+        <v>-2.3720434192695605</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0933344605618777E-2</v>
+        <v>-2.3720434192695605E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" s="10">
-        <v>1.9620033078177137</v>
+        <v>2.4041281311605101</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>1.9620033078177137E-2</v>
+        <v>2.4041281311605101E-2</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.049956266985248</v>
+        <v>-2.3455525958721712</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0499562669852481E-2</v>
+        <v>-2.3455525958721711E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33" s="10">
-        <v>1.9112837583787572</v>
+        <v>2.3916356095522637</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>1.9112837583787571E-2</v>
+        <v>2.3916356095522638E-2</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9173153634029931</v>
+        <v>-2.2866895573398907</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9173153634029931E-2</v>
+        <v>-2.2866895573398906E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" s="10">
-        <v>1.7087813031835299</v>
+        <v>2.3033102552226299</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>1.7087813031835299E-2</v>
+        <v>2.3033102552226299E-2</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.9047052013576999</v>
+        <v>-2.2422848980240557</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9047052013576999E-2</v>
+        <v>-2.2422848980240558E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C35" s="10">
-        <v>1.6636507013514712</v>
+        <v>2.2605761987862927</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.6636507013514712E-2</v>
+        <v>2.2605761987862925E-2</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.7047066909626769</v>
+        <v>-2.2004985408639794</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7047066909626769E-2</v>
+        <v>-2.2004985408639793E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" s="10">
-        <v>1.2449030995900259</v>
+        <v>2.0950895939814607</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.2449030995900258E-2</v>
+        <v>2.0950895939814605E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.7009970016551186</v>
+        <v>-2.1038836536332797</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7009970016551187E-2</v>
+        <v>-2.1038836536332796E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C37" s="10">
-        <v>1.1688977421281732</v>
+        <v>2.0406048397746366</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.1688977421281731E-2</v>
+        <v>2.0406048397746367E-2</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.6646529422436704</v>
+        <v>-2.0180739639787797</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6646529422436704E-2</v>
+        <v>-2.0180739639787795E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" s="10">
-        <v>1.1155702106868339</v>
+        <v>1.8995888328409045</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.1155702106868339E-2</v>
+        <v>1.8995888328409045E-2</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.6390832606721104</v>
+        <v>-1.7971220988040524</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6390832606721105E-2</v>
+        <v>-1.7971220988040524E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="10">
-        <v>0.99648369998180264</v>
+        <v>1.7761936685728725</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>9.9648369998180265E-3</v>
+        <v>1.7761936685728726E-2</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.5891074135949554</v>
+        <v>-1.7404444461107103</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5891074135949555E-2</v>
+        <v>-1.7404444461107102E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C40" s="10">
-        <v>0.82817958052775298</v>
+        <v>1.7027350005289228</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>8.2817958052775302E-3</v>
+        <v>1.7027350005289228E-2</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.4892150986824619</v>
+        <v>-1.6860273057321093</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.489215098682462E-2</v>
+        <v>-1.6860273057321094E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" s="10">
-        <v>0.57436012889926524</v>
+        <v>1.2796350413276278</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>5.7436012889926528E-3</v>
+        <v>1.2796350413276279E-2</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.478054539584212</v>
+        <v>-1.6768660654297989</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.478054539584212E-2</v>
+        <v>-1.6768660654297989E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C42" s="10">
-        <v>0.5641928749820676</v>
+        <v>1.0959681448661063</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>5.6419287498206761E-3</v>
+        <v>1.0959681448661062E-2</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.4488183339549083</v>
+        <v>-1.5780082917113729</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4488183339549083E-2</v>
+        <v>-1.578008291711373E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C43" s="10">
-        <v>0.40492030938330448</v>
+        <v>0.91552807501435485</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>4.049203093833045E-3</v>
+        <v>9.155280750143548E-3</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.4375635175164947</v>
+        <v>-1.4966184349352989</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.4375635175164946E-2</v>
+        <v>-1.496618434935299E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C44" s="10">
-        <v>0.28028407349629625</v>
+        <v>0.87235924622549432</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>2.8028407349629625E-3</v>
+        <v>8.7235924622549432E-3</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.4220994046303435</v>
+        <v>-1.4711429747531979</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.4220994046303434E-2</v>
+        <v>-1.4711429747531979E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="C45" s="10">
-        <v>0.26691459219006664</v>
+        <v>0.80161459435984606</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>2.6691459219006664E-3</v>
+        <v>8.0161459435984603E-3</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.3287330413426381</v>
+        <v>-1.458038876591176</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3287330413426382E-2</v>
+        <v>-1.4580388765911761E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="9"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
+      <c r="B46" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0.54827879937659163</v>
+      </c>
+      <c r="D46" s="10">
+        <f t="shared" si="0"/>
+        <v>5.4827879937659162E-3</v>
+      </c>
       <c r="F46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.3151183324151723</v>
+        <v>-1.3870569443397152</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3151183324151723E-2</v>
+        <v>-1.3870569443397152E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.52653546359103776</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>5.2653546359103772E-3</v>
+      </c>
       <c r="F47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.1582778656165043</v>
+        <v>-1.3723734746438416</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.1582778656165043E-2</v>
+        <v>-1.3723734746438416E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.5086438044303534</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="0"/>
+        <v>5.0864380443035343E-3</v>
+      </c>
       <c r="F48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.0800449939025112</v>
+        <v>-1.3436569571637658</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0800449939025111E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.3436569571637658E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="9"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
       <c r="F49" s="11" t="s">
         <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.0525949446918972</v>
+        <v>-1.2440525418550425</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0525949446918972E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.2440525418550426E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F50" s="11" t="s">
         <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.0462247684547883</v>
+        <v>-1.1840062613288505</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0462247684547883E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D51" s="1"/>
+        <v>-1.1840062613288505E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.9934233630383229</v>
+        <v>-1.0002671278713637</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-9.9342336303832289E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D52" s="1"/>
+        <v>-1.0002671278713637E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.94480012320495455</v>
+        <v>-0.9459196239568739</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4480012320495455E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D53" s="1"/>
+        <v>-9.4591962395687394E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.91313455713864933</v>
+        <v>-0.92470578535174563</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-9.1313455713864927E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.2470578535174559E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D54" s="1"/>
       <c r="F54" s="11" t="s">
         <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.88760796875471759</v>
+        <v>-0.91374020936421363</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-8.8760796875471757E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.1374020936421368E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.86363158213041968</v>
+        <v>-0.88606621620990911</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-8.6363158213041968E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.8606621620990911E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
         <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.82394246807596072</v>
+        <v>-0.85118947218790486</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.2394246807596071E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.5118947218790486E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.80720963880194196</v>
+        <v>-0.84885910669806452</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.0720963880194195E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.4885910669806452E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
         <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.80396971241864612</v>
+        <v>-0.84172281386665282</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-8.0396971241864616E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.4172281386665285E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
         <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.78951331715088058</v>
+        <v>-0.80320460287803819</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8951331715088058E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.0320460287803819E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.74349728723121411</v>
+        <v>-0.78316461545734595</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4349728723121407E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.8316461545734593E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
         <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.74331569052080704</v>
+        <v>-0.77703891819948889</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4331569052080706E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.7703891819948887E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.72315341131255173</v>
+        <v>-0.74128160519666764</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.2315341131255172E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.4128160519666766E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
         <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.65722371672863966</v>
+        <v>-0.73504018427127416</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-6.5722371672863964E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.3504018427127419E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.65308165430106435</v>
+        <v>-0.66278148523870672</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.5308165430106434E-3</v>
+        <v>-6.6278148523870673E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
@@ -2320,11 +2377,11 @@
         <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.63418766957819195</v>
+        <v>-0.64423842481688998</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.3418766957819197E-3</v>
+        <v>-6.4423842481689001E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
@@ -2333,11 +2390,11 @@
         <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.61693360403735709</v>
+        <v>-0.51114862226544999</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-6.1693360403735709E-3</v>
+        <v>-5.1114862226545E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
@@ -2346,11 +2403,11 @@
         <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.53940708587709818</v>
+        <v>-0.50150101026930494</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-5.3940708587709822E-3</v>
+        <v>-5.0150101026930497E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
@@ -2359,11 +2416,11 @@
         <v>74</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.49666988545089319</v>
+        <v>-0.41729947289927372</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-4.9666988545089318E-3</v>
+        <v>-4.172994728992737E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
@@ -2372,11 +2429,11 @@
         <v>75</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.49503263256976249</v>
+        <v>-0.41190149113877106</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-4.9503263256976248E-3</v>
+        <v>-4.1190149113877108E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
@@ -2385,11 +2442,11 @@
         <v>76</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.48699471027814267</v>
+        <v>-0.40800382426986115</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-4.8699471027814269E-3</v>
+        <v>-4.0800382426986114E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
@@ -2398,50 +2455,59 @@
         <v>77</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.37616461441471311</v>
+        <v>-0.37745419605778052</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-3.7616461441471309E-3</v>
+        <v>-3.7745419605778054E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.2553151023128129</v>
+        <v>-0.28641687175955338</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-2.5531510231281292E-3</v>
+        <v>-2.8641687175955336E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="13"/>
+      <c r="F73" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-0.12149612588398988</v>
+      </c>
+      <c r="H73" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2149612588398988E-3</v>
+      </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
-      <c r="G76" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
+      <c r="G77" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
-      <c r="H78" s="1"/>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
@@ -2828,57 +2894,60 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -2904,6 +2973,9 @@
     </row>
     <row r="200" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H200" s="1"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2913,7 +2985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q200"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -3028,24 +3100,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C11" s="10">
-        <v>7.9455865026348329</v>
+        <v>10.114913123044515</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D45" si="0">IF(B11="","",(C11/100))</f>
-        <v>7.9455865026348327E-2</v>
+        <f t="shared" ref="D11:D50" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10114913123044515</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-4.5415037047817943</v>
+        <v>-7.0254505788774777</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-4.5415037047817942E-2</v>
+        <v>-7.0254505788774776E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -3066,24 +3138,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C12" s="10">
-        <v>6.8708326027263427</v>
+        <v>7.4234234046912162</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>6.8708326027263428E-2</v>
+        <v>7.4234234046912165E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.4861190140976008</v>
+        <v>-5.1423608203890385</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-4.4861190140976011E-2</v>
+        <v>-5.1423608203890386E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3094,1107 +3166,1161 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C13" s="10">
-        <v>5.4774151013854411</v>
+        <v>6.8676479221103426</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.4774151013854411E-2</v>
+        <v>6.8676479221103426E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G13" s="10">
-        <v>-4.2197871427778058</v>
+        <v>-5.0438911761510656</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2197871427778061E-2</v>
+        <v>-5.0438911761510656E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C14" s="10">
-        <v>4.5116088507663319</v>
+        <v>5.7637035126237404</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.511608850766332E-2</v>
+        <v>5.7637035126237406E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.0709587400507496</v>
+        <v>-4.7271739906737658</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0709587400507494E-2</v>
+        <v>-4.7271739906737657E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C15" s="10">
-        <v>3.5422600230505501</v>
+        <v>5.0984983719649195</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>3.5422600230505502E-2</v>
+        <v>5.0984983719649192E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G15" s="10">
-        <v>-3.7998366529676115</v>
+        <v>-4.6162214322468786</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7998366529676114E-2</v>
+        <v>-4.6162214322468788E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C16" s="10">
-        <v>3.5143806042718597</v>
+        <v>4.8088529399076929</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>3.5143806042718599E-2</v>
+        <v>4.8088529399076929E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.6438888925374049</v>
+        <v>-4.0816463521898836</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6438888925374051E-2</v>
+        <v>-4.0816463521898834E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C17" s="10">
-        <v>3.386336187266318</v>
+        <v>4.4356524193573295</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>3.3863361872663179E-2</v>
+        <v>4.4356524193573298E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.3311301387428793</v>
+        <v>-3.7471572765923411</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3311301387428792E-2</v>
+        <v>-3.747157276592341E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C18" s="10">
-        <v>3.2809192968749947</v>
+        <v>4.0626808900841747</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>3.2809192968749949E-2</v>
+        <v>4.0626808900841749E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.0770632976275549</v>
+        <v>-3.6985352047410642</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0770632976275549E-2</v>
+        <v>-3.6985352047410644E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C19" s="10">
-        <v>3.255709782112409</v>
+        <v>3.9255443710187592</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.2557097821124092E-2</v>
+        <v>3.925544371018759E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.0406120817445292</v>
+        <v>-3.5731192105080143</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0406120817445294E-2</v>
+        <v>-3.5731192105080141E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C20" s="10">
-        <v>3.1398745010833453</v>
+        <v>3.7466845055356335</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.1398745010833451E-2</v>
+        <v>3.7466845055356336E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G20" s="10">
-        <v>-2.9854189323525038</v>
+        <v>-3.4767550578903101</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9854189323525036E-2</v>
+        <v>-3.47675505789031E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C21" s="10">
-        <v>3.0452765229632717</v>
+        <v>3.621485491156577</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.0452765229632715E-2</v>
+        <v>3.6214854911565772E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8785752106651246</v>
+        <v>-3.3787963458236683</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8785752106651245E-2</v>
+        <v>-3.3787963458236682E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C22" s="10">
-        <v>2.9959320847657147</v>
+        <v>3.5857433479229086</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>2.9959320847657147E-2</v>
+        <v>3.5857433479229088E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.8589949056764121</v>
+        <v>-3.2867573111023902</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8589949056764121E-2</v>
+        <v>-3.2867573111023902E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C23" s="10">
-        <v>2.5778778653644032</v>
+        <v>3.4417504543854469</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>2.5778778653644033E-2</v>
+        <v>3.441750454385447E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.7557344041589866</v>
+        <v>-2.9874661452109144</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7557344041589868E-2</v>
+        <v>-2.9874661452109142E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C24" s="10">
-        <v>2.5701980540066631</v>
+        <v>3.2804380186953459</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>2.570198054006663E-2</v>
+        <v>3.2804380186953461E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.7443894379250495</v>
+        <v>-2.9113669260193382</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7443894379250496E-2</v>
+        <v>-2.9113669260193382E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C25" s="10">
-        <v>2.2203494692308459</v>
+        <v>3.2750090472635747</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>2.2203494692308458E-2</v>
+        <v>3.2750090472635746E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.7360279903436027</v>
+        <v>-2.873761068289765</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7360279903436025E-2</v>
+        <v>-2.8737610682897648E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C26" s="10">
-        <v>2.1221052885896698</v>
+        <v>2.8824728500031798</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.1221052885896697E-2</v>
+        <v>2.8824728500031798E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.5203576838404471</v>
+        <v>-2.6738666363436119</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5203576838404473E-2</v>
+        <v>-2.6738666363436119E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C27" s="10">
-        <v>2.1070422968944205</v>
+        <v>2.7187939303252557</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.1070422968944204E-2</v>
+        <v>2.7187939303252556E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.5088141142200486</v>
+        <v>-2.5441864922387301</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5088141142200485E-2</v>
+        <v>-2.54418649223873E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C28" s="10">
-        <v>2.0833059263540186</v>
+        <v>2.6809664494920611</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.0833059263540187E-2</v>
+        <v>2.6809664494920612E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.3901766230001549</v>
+        <v>-2.5030046864978872</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.390176623000155E-2</v>
+        <v>-2.5030046864978873E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C29" s="10">
-        <v>2.067807872177946</v>
+        <v>2.6409346567269854</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.0678078721779462E-2</v>
+        <v>2.6409346567269853E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.330264121003145</v>
+        <v>-2.4950477813923095</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.330264121003145E-2</v>
+        <v>-2.4950477813923094E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C30" s="10">
-        <v>1.9805874045425345</v>
+        <v>2.5432508064299917</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>1.9805874045425345E-2</v>
+        <v>2.5432508064299916E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1837118284709063</v>
+        <v>-2.3917355855546796</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1837118284709064E-2</v>
+        <v>-2.3917355855546794E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C31" s="10">
-        <v>1.9712322914691018</v>
+        <v>2.5127136277036066</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>1.9712322914691018E-2</v>
+        <v>2.5127136277036066E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0933344605618776</v>
+        <v>-2.3720434192695605</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0933344605618777E-2</v>
+        <v>-2.3720434192695605E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C32" s="10">
-        <v>1.9620033078177137</v>
+        <v>2.4041281311605101</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>1.9620033078177137E-2</v>
+        <v>2.4041281311605101E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.049956266985248</v>
+        <v>-2.3455525958721712</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0499562669852481E-2</v>
+        <v>-2.3455525958721711E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C33" s="10">
-        <v>1.9112837583787572</v>
+        <v>2.3916356095522637</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>1.9112837583787571E-2</v>
+        <v>2.3916356095522638E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9173153634029931</v>
+        <v>-2.2866895573398907</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9173153634029931E-2</v>
+        <v>-2.2866895573398906E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C34" s="10">
-        <v>1.7087813031835299</v>
+        <v>2.3033102552226299</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>1.7087813031835299E-2</v>
+        <v>2.3033102552226299E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.9047052013576999</v>
+        <v>-2.2422848980240557</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9047052013576999E-2</v>
+        <v>-2.2422848980240558E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C35" s="10">
-        <v>1.6636507013514712</v>
+        <v>2.2605761987862927</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.6636507013514712E-2</v>
+        <v>2.2605761987862925E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.7047066909626769</v>
+        <v>-2.2004985408639794</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7047066909626769E-2</v>
+        <v>-2.2004985408639793E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C36" s="10">
-        <v>1.2449030995900259</v>
+        <v>2.0950895939814607</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.2449030995900258E-2</v>
+        <v>2.0950895939814605E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.7009970016551186</v>
+        <v>-2.1038836536332797</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7009970016551187E-2</v>
+        <v>-2.1038836536332796E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C37" s="10">
-        <v>1.1688977421281732</v>
+        <v>2.0406048397746366</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.1688977421281731E-2</v>
+        <v>2.0406048397746367E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.6646529422436704</v>
+        <v>-2.0180739639787797</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6646529422436704E-2</v>
+        <v>-2.0180739639787795E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C38" s="10">
-        <v>1.1155702106868339</v>
+        <v>1.8995888328409045</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.1155702106868339E-2</v>
+        <v>1.8995888328409045E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.6390832606721104</v>
+        <v>-1.7971220988040524</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6390832606721105E-2</v>
+        <v>-1.7971220988040524E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C39" s="10">
-        <v>0.99648369998180264</v>
+        <v>1.7761936685728725</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>9.9648369998180265E-3</v>
+        <v>1.7761936685728726E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.5891074135949554</v>
+        <v>-1.7404444461107103</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5891074135949555E-2</v>
+        <v>-1.7404444461107102E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C40" s="10">
-        <v>0.82817958052775298</v>
+        <v>1.7027350005289228</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>8.2817958052775302E-3</v>
+        <v>1.7027350005289228E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.4892150986824619</v>
+        <v>-1.6860273057321093</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.489215098682462E-2</v>
+        <v>-1.6860273057321094E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C41" s="10">
-        <v>0.57436012889926524</v>
+        <v>1.70069237158685</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>5.7436012889926528E-3</v>
+        <v>1.70069237158685E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.478054539584212</v>
+        <v>-1.6768660654297989</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.478054539584212E-2</v>
+        <v>-1.6768660654297989E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C42" s="10">
-        <v>0.5641928749820676</v>
+        <v>1.2796350413276278</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>5.6419287498206761E-3</v>
+        <v>1.2796350413276279E-2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.4488183339549083</v>
+        <v>-1.5780082917113729</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4488183339549083E-2</v>
+        <v>-1.578008291711373E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C43" s="10">
-        <v>0.40492030938330448</v>
+        <v>1.0959681448661063</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>4.049203093833045E-3</v>
+        <v>1.0959681448661062E-2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.4375635175164947</v>
+        <v>-1.4966184349352989</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.4375635175164946E-2</v>
+        <v>-1.496618434935299E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C44" s="10">
-        <v>0.28028407349629625</v>
+        <v>0.91552807501435485</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>2.8028407349629625E-3</v>
+        <v>9.155280750143548E-3</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.4220994046303435</v>
+        <v>-1.4711429747531979</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.4220994046303434E-2</v>
+        <v>-1.4711429747531979E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C45" s="10">
+        <v>0.87235924622549432</v>
+      </c>
+      <c r="D45" s="10">
+        <f t="shared" si="0"/>
+        <v>8.7235924622549432E-3</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G45" s="10">
+        <v>-1.458038876591176</v>
+      </c>
+      <c r="H45" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.4580388765911761E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0.80161459435984606</v>
+      </c>
+      <c r="D46" s="10">
+        <f t="shared" si="0"/>
+        <v>8.0161459435984603E-3</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G46" s="10">
+        <v>-1.3870569443397152</v>
+      </c>
+      <c r="H46" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3870569443397152E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.54827879937659163</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>5.4827879937659162E-3</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1.3723734746438416</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3723734746438416E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.52653546359103776</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="0"/>
+        <v>5.2653546359103772E-3</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-1.3436569571637658</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3436569571637658E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C49" s="10">
+        <v>0.5086438044303534</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="0"/>
+        <v>5.0864380443035343E-3</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-1.2440525418550425</v>
+      </c>
+      <c r="H49" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2440525418550426E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="10">
-        <v>0.26691459219006664</v>
-      </c>
-      <c r="D45" s="10">
-        <f t="shared" si="0"/>
-        <v>2.6691459219006664E-3</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G45" s="10">
-        <v>-1.3287330413426381</v>
-      </c>
-      <c r="H45" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.3287330413426382E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="9"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="F46" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G46" s="10">
-        <v>-1.3151183324151723</v>
-      </c>
-      <c r="H46" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.3151183324151723E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F47" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G47" s="10">
-        <v>-1.1582778656165043</v>
-      </c>
-      <c r="H47" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.1582778656165043E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F48" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G48" s="10">
-        <v>-1.0800449939025112</v>
-      </c>
-      <c r="H48" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.0800449939025111E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="F49" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="G49" s="10">
-        <v>-1.0525949446918972</v>
-      </c>
-      <c r="H49" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.0525949446918972E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="C50" s="10">
+        <v>0.32731868690403498</v>
+      </c>
+      <c r="D50" s="10">
+        <f t="shared" si="0"/>
+        <v>3.2731868690403496E-3</v>
+      </c>
       <c r="F50" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.0462247684547883</v>
+        <v>-1.1840062613288505</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0462247684547883E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D51" s="1"/>
+        <v>-1.1840062613288505E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="9"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
       <c r="F51" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.9934233630383229</v>
+        <v>-1.0002671278713637</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-9.9342336303832289E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D52" s="1"/>
+        <v>-1.0002671278713637E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.94480012320495455</v>
+        <v>-0.9459196239568739</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4480012320495455E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D53" s="1"/>
+        <v>-9.4591962395687394E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.91313455713864933</v>
+        <v>-0.92470578535174563</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-9.1313455713864927E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D54" s="1"/>
+        <v>-9.2470578535174559E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F54" s="11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.88760796875471759</v>
+        <v>-0.91374020936421363</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-8.8760796875471757E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D55" s="1"/>
+        <v>-9.1374020936421368E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F55" s="11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.86363158213041968</v>
+        <v>-0.88606621620990911</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-8.6363158213041968E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.8606621620990911E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.82394246807596072</v>
+        <v>-0.85118947218790486</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.2394246807596071E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.5118947218790486E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.80720963880194196</v>
+        <v>-0.84885910669806452</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.0720963880194195E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.4885910669806452E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.80396971241864612</v>
+        <v>-0.84172281386665282</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-8.0396971241864616E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.4172281386665285E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.78951331715088058</v>
+        <v>-0.80320460287803819</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8951331715088058E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.0320460287803819E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.74349728723121411</v>
+        <v>-0.78316461545734595</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4349728723121407E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.8316461545734593E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.74331569052080704</v>
+        <v>-0.77703891819948889</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4331569052080706E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.7703891819948887E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.72315341131255173</v>
+        <v>-0.74128160519666764</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.2315341131255172E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.4128160519666766E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.65722371672863966</v>
+        <v>-0.73504018427127416</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-6.5722371672863964E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.3504018427127419E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.65308165430106435</v>
+        <v>-0.66278148523870672</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.5308165430106434E-3</v>
+        <v>-6.6278148523870673E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.63418766957819195</v>
+        <v>-0.64423842481688998</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.3418766957819197E-3</v>
+        <v>-6.4423842481689001E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.61693360403735709</v>
+        <v>-0.51114862226544999</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-6.1693360403735709E-3</v>
+        <v>-5.1114862226545E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.53940708587709818</v>
+        <v>-0.50150101026930494</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-5.3940708587709822E-3</v>
+        <v>-5.0150101026930497E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.49666988545089319</v>
+        <v>-0.44881481278802488</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-4.9666988545089318E-3</v>
+        <v>-4.4881481278802489E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.49503263256976249</v>
+        <v>-0.41729947289927372</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-4.9503263256976248E-3</v>
+        <v>-4.172994728992737E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.48699471027814267</v>
+        <v>-0.41190149113877106</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-4.8699471027814269E-3</v>
+        <v>-4.1190149113877108E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.37616461441471311</v>
+        <v>-0.40800382426986115</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-3.7616461441471309E-3</v>
+        <v>-4.0800382426986114E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>14</v>
+        <v>175</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.2553151023128129</v>
+        <v>-0.37745419605778052</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-2.5531510231281292E-3</v>
+        <v>-3.7745419605778054E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="13"/>
+      <c r="F73" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-0.28641687175955338</v>
+      </c>
+      <c r="H73" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.8641687175955336E-3</v>
+      </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
-      <c r="G76" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
+      <c r="G77" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
-      <c r="H78" s="1"/>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
@@ -4581,57 +4707,62 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -4657,6 +4788,9 @@
     </row>
     <row r="200" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H200" s="1"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F9A8E57-8111-474C-9B1D-A9F8A6B0FA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{676C9B0C-8BDD-6E4D-902A-B0109AD8F733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="209">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -63,510 +63,501 @@
     <t>SERIES: Trading (non-additive)</t>
   </si>
   <si>
+    <t>ETSY</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>LAUREATE EDUCATION ORD (NMS)</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>FAIR ISAAC ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>RHMG</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>4901</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>MSLYT26S</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>NICE</t>
+  </si>
+  <si>
+    <t>RCIb</t>
+  </si>
+  <si>
+    <t>T CN</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>TYL</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>WTC</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>WSP</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>TEPRF</t>
+  </si>
+  <si>
+    <t>LAUR</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>6752</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>FWONK</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>SAPG</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>MSLYT26L</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>SPHR</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
     <t>NET</t>
   </si>
   <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+    <t>QRVO</t>
+  </si>
+  <si>
+    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
+  </si>
+  <si>
+    <t>CINTAS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AUTODESK ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CANON ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>LOGITECH N ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>VERISK ANALYTICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>EQUIFAX ORD (NYS)</t>
+  </si>
+  <si>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SERVICETITAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
+  </si>
+  <si>
+    <t>RHEINMETALL ORD (GER)</t>
+  </si>
+  <si>
+    <t>EBAY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAMSARA CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MSLYT26S INDEX CFD</t>
+  </si>
+  <si>
+    <t>CROWDSTRIKE HOLDINGS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>REA GROUP ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>SANRIO ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>NICE ADR REP 1 ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
+  </si>
+  <si>
+    <t>TELUS ORD (TOR)</t>
+  </si>
+  <si>
+    <t>CDW ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WILLIAMS SONOMA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GARTNER ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SLM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SEZZLE INC (NMS)</t>
+  </si>
+  <si>
+    <t>DUOLINGO CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBERT HALF ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ARISTA NETWORKS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SYMBOTIC CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CARGURUS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ADOBE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>QUALYS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WISETECH GLOBAL ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WSP GLOBAL ORD (TOR)</t>
+  </si>
+  <si>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DATADOG CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
+    <t>STANTEC ORD (TOR)</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
+  </si>
+  <si>
+    <t>CONCENTRIX ORD (NMS)</t>
   </si>
   <si>
     <t>TELEPERFORMANCE ORD (PAR) CFD</t>
   </si>
   <si>
-    <t>Instrument</t>
-  </si>
-  <si>
-    <t>FAIR ISAAC ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>RHMG</t>
-  </si>
-  <si>
-    <t>MSLYT26S</t>
-  </si>
-  <si>
-    <t>4901</t>
-  </si>
-  <si>
-    <t>NICE</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>RCIb</t>
-  </si>
-  <si>
-    <t>CDW</t>
-  </si>
-  <si>
-    <t>TYL</t>
-  </si>
-  <si>
-    <t>T CN</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>WTC</t>
-  </si>
-  <si>
-    <t>WSP</t>
-  </si>
-  <si>
-    <t>SOFI</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>LAUR</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>STN</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>TEPRF</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>6857</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>FWONK</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>6752</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>000660</t>
-  </si>
-  <si>
-    <t>SAPG</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>STM</t>
-  </si>
-  <si>
-    <t>QRVO</t>
-  </si>
-  <si>
-    <t>MSLYT26L</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>BILL</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>SNDK</t>
-  </si>
-  <si>
-    <t>ETSY</t>
-  </si>
-  <si>
-    <t>SPHR</t>
-  </si>
-  <si>
-    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
-  </si>
-  <si>
-    <t>AUTODESK ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CINTAS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>EQUIFAX ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CANON ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>LOGITECH N ORD (NMS)</t>
-  </si>
-  <si>
-    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CROWDSTRIKE HOLDINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>VERISK ANALYTICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NEW YORK TIMES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>EBAY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
-    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SAMSARA CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RHEINMETALL ORD (GER)</t>
-  </si>
-  <si>
-    <t>MSLYT26S INDEX CFD</t>
-  </si>
-  <si>
-    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>NICE ADR REP 1 ORD (NMS)</t>
-  </si>
-  <si>
-    <t>APPLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>REA GROUP ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>GARTNER ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
-  </si>
-  <si>
-    <t>CDW ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TELUS ORD (TOR)</t>
-  </si>
-  <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SEZZLE INC (NMS)</t>
-  </si>
-  <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ARISTA NETWORKS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ADOBE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ROBERT HALF ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CARGURUS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SYMBOTIC CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>QUALYS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WISETECH GLOBAL ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>WSP GLOBAL ORD (TOR)</t>
-  </si>
-  <si>
-    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DATADOG CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WIX.COM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
-  </si>
-  <si>
-    <t>LAUREATE EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>STANTEC ORD (TOR)</t>
-  </si>
-  <si>
-    <t>CONCENTRIX ORD (NMS)</t>
-  </si>
-  <si>
     <t>BLOCK CL A ORD (NYS)</t>
   </si>
   <si>
@@ -579,60 +570,54 @@
     <t>AMAZON COM ORD (NMS)</t>
   </si>
   <si>
+    <t>AT&amp;T ORD (NYS)</t>
+  </si>
+  <si>
+    <t>MAPLEBEAR ORD (NMS)</t>
+  </si>
+  <si>
     <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
   </si>
   <si>
-    <t>MAPLEBEAR ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AT&amp;T ORD (NYS)</t>
+    <t>EATON ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ADVANTEST ORD (TYO) CFD</t>
   </si>
   <si>
     <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
-  </si>
-  <si>
     <t>AUTO1 GROUP ORD (GER)</t>
   </si>
   <si>
+    <t>PANASONIC HLDG ORD (TYO) CFD</t>
+  </si>
+  <si>
     <t>ROCKET COMPANIES CL A ORD (NYS)</t>
   </si>
   <si>
+    <t>IRON MOUNTAIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBLOX CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LYFT CL A ORD (NMS)</t>
+  </si>
+  <si>
     <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
   </si>
   <si>
-    <t>IRON MOUNTAIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LYFT CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ORACLE ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBLOX CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TESLA ORD (NMS)</t>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
+    <t>DRAFTKINGS CL A ORD (NMS)</t>
   </si>
   <si>
     <t>TRIMBLE ORD (NMS)</t>
   </si>
   <si>
-    <t>PANASONIC HLDG ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>EATON ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (NYS)</t>
-  </si>
-  <si>
-    <t>DRAFTKINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
     <t>SK HYNIX ORD (KSC) CFD_USD</t>
   </si>
   <si>
@@ -642,46 +627,43 @@
     <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
   </si>
   <si>
+    <t>STMICROELECTRONICS ADR (NYS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
     <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>STMICROELECTRONICS ADR (NYS)</t>
+    <t>MSLYT26L INDEX CFD</t>
+  </si>
+  <si>
+    <t>WAYFAIR CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>BILL HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SANDISK ORD (NMS)</t>
+  </si>
+  <si>
+    <t>EVERPURE CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CLOUDFLARE CL A ORD (NYS)</t>
   </si>
   <si>
     <t>QORVO ORD (NMS)</t>
   </si>
   <si>
-    <t>MSLYT26L INDEX CFD</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (MIL)</t>
-  </si>
-  <si>
-    <t>WAYFAIR CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>BILL HOLDINGS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>DYNATRACE ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EVERPURE CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SANDISK ORD (NMS)</t>
-  </si>
-  <si>
     <t>ETSY ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CLOUDFLARE CL A ORD (NYS)</t>
   </si>
 </sst>
 </file>
@@ -1308,21 +1290,21 @@
         <v>79</v>
       </c>
       <c r="C11" s="10">
-        <v>10.114913123044515</v>
+        <v>9.3676345958810714</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D48" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10114913123044515</v>
+        <f t="shared" ref="D11:D45" si="0">IF(B11="","",(C11/100))</f>
+        <v>9.3676345958810719E-2</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-7.0254505788774777</v>
+        <v>-6.6747511166068776</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-7.0254505788774776E-2</v>
+        <v>-6.6747511166068779E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -1346,21 +1328,21 @@
         <v>80</v>
       </c>
       <c r="C12" s="10">
-        <v>7.4234234046912162</v>
+        <v>7.178295390076145</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.4234234046912165E-2</v>
+        <v>7.1782953900761448E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.1423608203890385</v>
+        <v>-5.1257189854440615</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1423608203890386E-2</v>
+        <v>-5.1257189854440617E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1374,21 +1356,21 @@
         <v>81</v>
       </c>
       <c r="C13" s="10">
-        <v>6.8676479221103426</v>
+        <v>5.0098197800339523</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>6.8676479221103426E-2</v>
+        <v>5.0098197800339521E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-5.0438911761510656</v>
+        <v>-5.0593808269021654</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0438911761510656E-2</v>
+        <v>-5.0593808269021656E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1397,21 +1379,21 @@
         <v>82</v>
       </c>
       <c r="C14" s="10">
-        <v>5.7637035126237404</v>
+        <v>4.9893411504096523</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>5.7637035126237406E-2</v>
+        <v>4.989341150409652E-2</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.7271739906737658</v>
+        <v>-4.7845448503728001</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7271739906737657E-2</v>
+        <v>-4.7845448503728003E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1420,21 +1402,21 @@
         <v>83</v>
       </c>
       <c r="C15" s="10">
-        <v>5.0984983719649195</v>
+        <v>4.8934917789138455</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>5.0984983719649192E-2</v>
+        <v>4.8934917789138457E-2</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.6162214322468786</v>
+        <v>-4.2526844426100716</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.6162214322468788E-2</v>
+        <v>-4.2526844426100718E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1443,21 +1425,21 @@
         <v>84</v>
       </c>
       <c r="C16" s="10">
-        <v>4.8088529399076929</v>
+        <v>4.7956028569605618</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.8088529399076929E-2</v>
+        <v>4.7956028569605617E-2</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-4.0816463521898836</v>
+        <v>-3.7538715318079805</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0816463521898834E-2</v>
+        <v>-3.7538715318079806E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1466,21 +1448,21 @@
         <v>85</v>
       </c>
       <c r="C17" s="10">
-        <v>4.4356524193573295</v>
+        <v>4.6320517671014345</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.4356524193573298E-2</v>
+        <v>4.6320517671014347E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.7471572765923411</v>
+        <v>-3.5028928974400122</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.747157276592341E-2</v>
+        <v>-3.5028928974400124E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1488,21 +1470,21 @@
         <v>86</v>
       </c>
       <c r="C18" s="10">
-        <v>4.2134059992904564</v>
+        <v>4.5539753980328364</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.2134059992904566E-2</v>
+        <v>4.5539753980328362E-2</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.6985352047410642</v>
+        <v>-3.4100075996797381</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6985352047410644E-2</v>
+        <v>-3.4100075996797381E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -1510,21 +1492,21 @@
         <v>87</v>
       </c>
       <c r="C19" s="10">
-        <v>4.0626808900841747</v>
+        <v>4.1488266383129728</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>4.0626808900841749E-2</v>
+        <v>4.1488266383129725E-2</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.5731192105080143</v>
+        <v>-3.2883526862952359</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5731192105080141E-2</v>
+        <v>-3.2883526862952359E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
@@ -1532,21 +1514,21 @@
         <v>88</v>
       </c>
       <c r="C20" s="10">
-        <v>3.9255443710187592</v>
+        <v>3.9941428681304529</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.925544371018759E-2</v>
+        <v>3.9941428681304528E-2</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.4767550578903101</v>
+        <v>-3.2377588228208172</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.47675505789031E-2</v>
+        <v>-3.2377588228208173E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1554,21 +1536,21 @@
         <v>89</v>
       </c>
       <c r="C21" s="10">
-        <v>3.7466845055356335</v>
+        <v>3.960998571869724</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.7466845055356336E-2</v>
+        <v>3.9609985718697241E-2</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-3.3787963458236683</v>
+        <v>-2.9534394867720826</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3787963458236682E-2</v>
+        <v>-2.9534394867720824E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -1576,21 +1558,21 @@
         <v>90</v>
       </c>
       <c r="C22" s="10">
-        <v>3.621485491156577</v>
+        <v>3.6679107565062949</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.6214854911565772E-2</v>
+        <v>3.667910756506295E-2</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-3.2867573111023902</v>
+        <v>-2.8758244405332403</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2867573111023902E-2</v>
+        <v>-2.8758244405332402E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
@@ -1598,21 +1580,21 @@
         <v>91</v>
       </c>
       <c r="C23" s="10">
-        <v>3.5857433479229086</v>
+        <v>3.3901254552592754</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.5857433479229088E-2</v>
+        <v>3.3901254552592755E-2</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.9874661452109144</v>
+        <v>-2.8675313674108578</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9874661452109142E-2</v>
+        <v>-2.8675313674108579E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -1620,21 +1602,21 @@
         <v>92</v>
       </c>
       <c r="C24" s="10">
-        <v>3.4417504543854469</v>
+        <v>3.3536380206432495</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.441750454385447E-2</v>
+        <v>3.3536380206432494E-2</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.9113669260193382</v>
+        <v>-2.5902503120703009</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9113669260193382E-2</v>
+        <v>-2.590250312070301E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -1642,21 +1624,21 @@
         <v>93</v>
       </c>
       <c r="C25" s="10">
-        <v>3.2804380186953459</v>
+        <v>3.2000877018935543</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>3.2804380186953461E-2</v>
+        <v>3.2000877018935545E-2</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.873761068289765</v>
+        <v>-2.5047802005457753</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8737610682897648E-2</v>
+        <v>-2.5047802005457753E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
@@ -1664,21 +1646,21 @@
         <v>94</v>
       </c>
       <c r="C26" s="10">
-        <v>3.2750090472635747</v>
+        <v>3.1627821872447059</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>3.2750090472635746E-2</v>
+        <v>3.1627821872447059E-2</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.6738666363436119</v>
+        <v>-2.4719791999441085</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.6738666363436119E-2</v>
+        <v>-2.4719791999441087E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -1686,21 +1668,21 @@
         <v>95</v>
       </c>
       <c r="C27" s="10">
-        <v>2.8824728500031798</v>
+        <v>3.0505612112986151</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.8824728500031798E-2</v>
+        <v>3.050561211298615E-2</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.5441864922387301</v>
+        <v>-2.4280737722724806</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.54418649223873E-2</v>
+        <v>-2.4280737722724807E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -1708,21 +1690,21 @@
         <v>96</v>
       </c>
       <c r="C28" s="10">
-        <v>2.7187939303252557</v>
+        <v>2.9758227955613918</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.7187939303252556E-2</v>
+        <v>2.975822795561392E-2</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.5030046864978872</v>
+        <v>-2.209426104135249</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5030046864978873E-2</v>
+        <v>-2.2094261041352491E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -1730,21 +1712,21 @@
         <v>97</v>
       </c>
       <c r="C29" s="10">
-        <v>2.6809664494920611</v>
+        <v>2.5098554346299311</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.6809664494920612E-2</v>
+        <v>2.5098554346299311E-2</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.4950477813923095</v>
+        <v>-2.1433936519179007</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4950477813923094E-2</v>
+        <v>-2.1433936519179006E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -1752,21 +1734,21 @@
         <v>98</v>
       </c>
       <c r="C30" s="10">
-        <v>2.6409346567269854</v>
+        <v>2.4321920966956521</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.6409346567269853E-2</v>
+        <v>2.4321920966956522E-2</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.3917355855546796</v>
+        <v>-2.1271937672668861</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3917355855546794E-2</v>
+        <v>-2.1271937672668863E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -1774,21 +1756,21 @@
         <v>99</v>
       </c>
       <c r="C31" s="10">
-        <v>2.5432508064299917</v>
+        <v>2.2075253833059327</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.5432508064299916E-2</v>
+        <v>2.2075253833059326E-2</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.3720434192695605</v>
+        <v>-2.0435843613963227</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3720434192695605E-2</v>
+        <v>-2.0435843613963226E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -1796,21 +1778,21 @@
         <v>100</v>
       </c>
       <c r="C32" s="10">
-        <v>2.4041281311605101</v>
+        <v>2.0981973233901021</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.4041281311605101E-2</v>
+        <v>2.0981973233901021E-2</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.3455525958721712</v>
+        <v>-2.0210862608719604</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3455525958721711E-2</v>
+        <v>-2.0210862608719606E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -1818,21 +1800,21 @@
         <v>101</v>
       </c>
       <c r="C33" s="10">
-        <v>2.3916356095522637</v>
+        <v>2.0850481380747117</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.3916356095522638E-2</v>
+        <v>2.0850481380747118E-2</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-2.2866895573398907</v>
+        <v>-1.9955531802970969</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2866895573398906E-2</v>
+        <v>-1.995553180297097E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -1840,21 +1822,21 @@
         <v>102</v>
       </c>
       <c r="C34" s="10">
-        <v>2.3033102552226299</v>
+        <v>2.0104689250012719</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.3033102552226299E-2</v>
+        <v>2.0104689250012721E-2</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-2.2422848980240557</v>
+        <v>-1.9941591425575136</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2422848980240558E-2</v>
+        <v>-1.9941591425575136E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -1862,21 +1844,21 @@
         <v>103</v>
       </c>
       <c r="C35" s="10">
-        <v>2.2605761987862927</v>
+        <v>1.9481978272974623</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>2.2605761987862925E-2</v>
+        <v>1.9481978272974623E-2</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-2.2004985408639794</v>
+        <v>-1.9119858208758242</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2004985408639793E-2</v>
+        <v>-1.9119858208758243E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -1884,21 +1866,21 @@
         <v>104</v>
       </c>
       <c r="C36" s="10">
-        <v>2.0950895939814607</v>
+        <v>1.7446904333315016</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>2.0950895939814605E-2</v>
+        <v>1.7446904333315017E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-2.1038836536332797</v>
+        <v>-1.7937745156034437</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1038836536332796E-2</v>
+        <v>-1.7937745156034437E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -1906,21 +1888,21 @@
         <v>105</v>
       </c>
       <c r="C37" s="10">
-        <v>2.0406048397746366</v>
+        <v>1.6067850405688737</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>2.0406048397746367E-2</v>
+        <v>1.6067850405688738E-2</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-2.0180739639787797</v>
+        <v>-1.7896264676777158</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0180739639787795E-2</v>
+        <v>-1.7896264676777157E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
@@ -1928,21 +1910,21 @@
         <v>106</v>
       </c>
       <c r="C38" s="10">
-        <v>1.8995888328409045</v>
+        <v>1.4968446417390027</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.8995888328409045E-2</v>
+        <v>1.4968446417390027E-2</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.7971220988040524</v>
+        <v>-1.7321728084499362</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7971220988040524E-2</v>
+        <v>-1.732172808449936E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
@@ -1950,21 +1932,21 @@
         <v>107</v>
       </c>
       <c r="C39" s="10">
-        <v>1.7761936685728725</v>
+        <v>0.98481520791170696</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.7761936685728726E-2</v>
+        <v>9.8481520791170694E-3</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.7404444461107103</v>
+        <v>-1.6089367918507707</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7404444461107102E-2</v>
+        <v>-1.6089367918507708E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -1972,21 +1954,21 @@
         <v>108</v>
       </c>
       <c r="C40" s="10">
-        <v>1.7027350005289228</v>
+        <v>0.94212419763022948</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.7027350005289228E-2</v>
+        <v>9.4212419763022946E-3</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.6860273057321093</v>
+        <v>-1.494577307054914</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6860273057321094E-2</v>
+        <v>-1.494577307054914E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -1994,21 +1976,21 @@
         <v>109</v>
       </c>
       <c r="C41" s="10">
-        <v>1.2796350413276278</v>
+        <v>0.74655664930348975</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.2796350413276279E-2</v>
+        <v>7.4655664930348975E-3</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.6768660654297989</v>
+        <v>-1.4765597546543652</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6768660654297989E-2</v>
+        <v>-1.4765597546543652E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -2016,21 +1998,21 @@
         <v>110</v>
       </c>
       <c r="C42" s="10">
-        <v>1.0959681448661063</v>
+        <v>0.72041709585217106</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>1.0959681448661062E-2</v>
+        <v>7.204170958521711E-3</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.5780082917113729</v>
+        <v>-1.4492896285598154</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.578008291711373E-2</v>
+        <v>-1.4492896285598154E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
@@ -2038,21 +2020,21 @@
         <v>111</v>
       </c>
       <c r="C43" s="10">
-        <v>0.91552807501435485</v>
+        <v>0.6712714794526613</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>9.155280750143548E-3</v>
+        <v>6.7127147945266127E-3</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.4966184349352989</v>
+        <v>-1.3909880938269175</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.496618434935299E-2</v>
+        <v>-1.3909880938269175E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -2060,315 +2042,288 @@
         <v>112</v>
       </c>
       <c r="C44" s="10">
-        <v>0.87235924622549432</v>
+        <v>0.61628335957250424</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>8.7235924622549432E-3</v>
+        <v>6.1628335957250426E-3</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.4711429747531979</v>
+        <v>-1.3884102113419121</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.4711429747531979E-2</v>
+        <v>-1.3884102113419122E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="C45" s="10">
-        <v>0.80161459435984606</v>
+        <v>0.54435032429445362</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>8.0161459435984603E-3</v>
+        <v>5.4435032429445366E-3</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.458038876591176</v>
+        <v>-1.3074682183127213</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.4580388765911761E-2</v>
+        <v>-1.3074682183127214E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46" s="10">
-        <v>0.54827879937659163</v>
-      </c>
-      <c r="D46" s="10">
-        <f t="shared" si="0"/>
-        <v>5.4827879937659162E-3</v>
-      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
       <c r="F46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.3870569443397152</v>
+        <v>-1.3069378013300608</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3870569443397152E-2</v>
+        <v>-1.3069378013300608E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" s="10">
-        <v>0.52653546359103776</v>
-      </c>
-      <c r="D47" s="10">
-        <f t="shared" si="0"/>
-        <v>5.2653546359103772E-3</v>
-      </c>
       <c r="F47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.3723734746438416</v>
+        <v>-1.3040521026412208</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3723734746438416E-2</v>
+        <v>-1.3040521026412209E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="10">
-        <v>0.5086438044303534</v>
-      </c>
-      <c r="D48" s="10">
-        <f t="shared" si="0"/>
-        <v>5.0864380443035343E-3</v>
-      </c>
       <c r="F48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.3436569571637658</v>
+        <v>-1.2845994016584155</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3436569571637658E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="9"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
+        <v>-1.2845994016584155E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F49" s="11" t="s">
         <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.2440525418550425</v>
+        <v>-1.2806145811026568</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2440525418550426E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-1.2806145811026569E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F50" s="11" t="s">
         <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.1840062613288505</v>
+        <v>-1.2733598873867638</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-1.1840062613288505E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-1.2733598873867637E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D51" s="1"/>
       <c r="F51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-1.0002671278713637</v>
+        <v>-1.2325645600528132</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0002671278713637E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-1.2325645600528132E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D52" s="1"/>
       <c r="F52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.9459196239568739</v>
+        <v>-0.98810854320703134</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4591962395687394E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-9.8810854320703131E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D53" s="1"/>
       <c r="F53" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.92470578535174563</v>
+        <v>-0.94154124273748196</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-9.2470578535174559E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-9.4154124273748193E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D54" s="1"/>
       <c r="F54" s="11" t="s">
         <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.91374020936421363</v>
+        <v>-0.89393254013237</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-9.1374020936421368E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.9393254013236997E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.88606621620990911</v>
+        <v>-0.85959217876515093</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-8.8606621620990911E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.5959217876515094E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
         <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.85118947218790486</v>
+        <v>-0.83076110098309497</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.5118947218790486E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.3076110098309498E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.84885910669806452</v>
+        <v>-0.82131867111538226</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4885910669806452E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.2131867111538224E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
         <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.84172281386665282</v>
+        <v>-0.79351820000791196</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4172281386665285E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.9351820000791197E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
         <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.80320460287803819</v>
+        <v>-0.78645940792387792</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-8.0320460287803819E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.8645940792387795E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.78316461545734595</v>
+        <v>-0.76066545316329681</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8316461545734593E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.6066545316329677E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
         <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.77703891819948889</v>
+        <v>-0.73616695371993224</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7703891819948887E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.3616695371993227E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.74128160519666764</v>
+        <v>-0.7106220142592159</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4128160519666766E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.1062201425921593E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
         <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.73504018427127416</v>
+        <v>-0.69770510126098817</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-7.3504018427127419E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-6.9770510126098816E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.66278148523870672</v>
+        <v>-0.69122760876568512</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.6278148523870673E-3</v>
+        <v>-6.9122760876568516E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
@@ -2377,11 +2332,11 @@
         <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.64423842481688998</v>
+        <v>-0.63807820273744953</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.4423842481689001E-3</v>
+        <v>-6.3807820273744957E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
@@ -2390,11 +2345,11 @@
         <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.51114862226544999</v>
+        <v>-0.56896397532157073</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-5.1114862226545E-3</v>
+        <v>-5.6896397532157075E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
@@ -2403,11 +2358,11 @@
         <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.50150101026930494</v>
+        <v>-0.41722081673939365</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-5.0150101026930497E-3</v>
+        <v>-4.1722081673939366E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
@@ -2416,11 +2371,11 @@
         <v>74</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.41729947289927372</v>
+        <v>-0.3938261891657775</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-4.172994728992737E-3</v>
+        <v>-3.9382618916577747E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
@@ -2429,11 +2384,11 @@
         <v>75</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.41190149113877106</v>
+        <v>-0.39343732974725998</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-4.1190149113877108E-3</v>
+        <v>-3.9343732974726001E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
@@ -2442,11 +2397,11 @@
         <v>76</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.40800382426986115</v>
+        <v>-0.34174543086615383</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-4.0800382426986114E-3</v>
+        <v>-3.4174543086615385E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
@@ -2455,11 +2410,11 @@
         <v>77</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.37745419605778052</v>
+        <v>-0.25310390078560174</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-3.7745419605778054E-3</v>
+        <v>-2.5310390078560176E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
@@ -2468,11 +2423,11 @@
         <v>78</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.28641687175955338</v>
+        <v>-2.7968664389488827E-2</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-2.8641687175955336E-3</v>
+        <v>-2.7968664389488827E-4</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
@@ -2481,11 +2436,11 @@
         <v>9</v>
       </c>
       <c r="G73" s="10">
-        <v>-0.12149612588398988</v>
+        <v>-1.9285227398185344E-2</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2149612588398988E-3</v>
+        <v>-1.9285227398185346E-4</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
@@ -2894,60 +2849,57 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D177" s="1"/>
+    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -3100,24 +3052,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C11" s="10">
-        <v>10.114913123044515</v>
+        <v>9.3676345958810714</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D50" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10114913123044515</v>
+        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
+        <v>9.3676345958810719E-2</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-7.0254505788774777</v>
+        <v>-6.6747511166068776</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-7.0254505788774776E-2</v>
+        <v>-6.6747511166068779E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -3138,24 +3090,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C12" s="10">
-        <v>7.4234234046912162</v>
+        <v>7.178295390076145</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.4234234046912165E-2</v>
+        <v>7.1782953900761448E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.1423608203890385</v>
+        <v>-5.1257189854440615</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1423608203890386E-2</v>
+        <v>-5.1257189854440617E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3166,1126 +3118,1099 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C13" s="10">
-        <v>6.8676479221103426</v>
+        <v>5.0098197800339523</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>6.8676479221103426E-2</v>
+        <v>5.0098197800339521E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G13" s="10">
-        <v>-5.0438911761510656</v>
+        <v>-5.0593808269021654</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0438911761510656E-2</v>
+        <v>-5.0593808269021656E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C14" s="10">
-        <v>5.7637035126237404</v>
+        <v>4.9893411504096523</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>5.7637035126237406E-2</v>
+        <v>4.989341150409652E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.7271739906737658</v>
+        <v>-4.7845448503728001</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7271739906737657E-2</v>
+        <v>-4.7845448503728003E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C15" s="10">
-        <v>5.0984983719649195</v>
+        <v>4.8934917789138455</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>5.0984983719649192E-2</v>
+        <v>4.8934917789138457E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.6162214322468786</v>
+        <v>-4.2526844426100716</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.6162214322468788E-2</v>
+        <v>-4.2526844426100718E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C16" s="10">
-        <v>4.8088529399076929</v>
+        <v>4.7956028569605618</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.8088529399076929E-2</v>
+        <v>4.7956028569605617E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G16" s="10">
-        <v>-4.0816463521898836</v>
+        <v>-3.7538715318079805</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0816463521898834E-2</v>
+        <v>-3.7538715318079806E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="10">
-        <v>4.4356524193573295</v>
+        <v>4.6320517671014345</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.4356524193573298E-2</v>
+        <v>4.6320517671014347E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.7471572765923411</v>
+        <v>-3.5028928974400122</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.747157276592341E-2</v>
+        <v>-3.5028928974400124E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C18" s="10">
-        <v>4.0626808900841747</v>
+        <v>4.1488266383129728</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.0626808900841749E-2</v>
+        <v>4.1488266383129725E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.6985352047410642</v>
+        <v>-3.4100075996797381</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6985352047410644E-2</v>
+        <v>-3.4100075996797381E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C19" s="10">
-        <v>3.9255443710187592</v>
+        <v>3.9941428681304529</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.925544371018759E-2</v>
+        <v>3.9941428681304528E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.5731192105080143</v>
+        <v>-3.2883526862952359</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5731192105080141E-2</v>
+        <v>-3.2883526862952359E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C20" s="10">
-        <v>3.7466845055356335</v>
+        <v>3.960998571869724</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.7466845055356336E-2</v>
+        <v>3.9609985718697241E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.4767550578903101</v>
+        <v>-3.2377588228208172</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.47675505789031E-2</v>
+        <v>-3.2377588228208173E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C21" s="10">
-        <v>3.621485491156577</v>
+        <v>3.6679107565062949</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.6214854911565772E-2</v>
+        <v>3.667910756506295E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G21" s="10">
-        <v>-3.3787963458236683</v>
+        <v>-2.9534394867720826</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3787963458236682E-2</v>
+        <v>-2.9534394867720824E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C22" s="10">
-        <v>3.5857433479229086</v>
+        <v>3.3901254552592754</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.5857433479229088E-2</v>
+        <v>3.3901254552592755E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G22" s="10">
-        <v>-3.2867573111023902</v>
+        <v>-2.8758244405332403</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2867573111023902E-2</v>
+        <v>-2.8758244405332402E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C23" s="10">
-        <v>3.4417504543854469</v>
+        <v>3.3536380206432495</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.441750454385447E-2</v>
+        <v>3.3536380206432494E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.9874661452109144</v>
+        <v>-2.8675313674108578</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9874661452109142E-2</v>
+        <v>-2.8675313674108579E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C24" s="10">
-        <v>3.2804380186953459</v>
+        <v>3.2000877018935543</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.2804380186953461E-2</v>
+        <v>3.2000877018935545E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.9113669260193382</v>
+        <v>-2.5902503120703009</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9113669260193382E-2</v>
+        <v>-2.590250312070301E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C25" s="10">
-        <v>3.2750090472635747</v>
+        <v>3.1627821872447059</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>3.2750090472635746E-2</v>
+        <v>3.1627821872447059E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.873761068289765</v>
+        <v>-2.5047802005457753</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8737610682897648E-2</v>
+        <v>-2.5047802005457753E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C26" s="10">
-        <v>2.8824728500031798</v>
+        <v>3.0505612112986151</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.8824728500031798E-2</v>
+        <v>3.050561211298615E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.6738666363436119</v>
+        <v>-2.4719791999441085</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.6738666363436119E-2</v>
+        <v>-2.4719791999441087E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C27" s="10">
-        <v>2.7187939303252557</v>
+        <v>2.9758227955613918</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.7187939303252556E-2</v>
+        <v>2.975822795561392E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.5441864922387301</v>
+        <v>-2.4280737722724806</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.54418649223873E-2</v>
+        <v>-2.4280737722724807E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C28" s="10">
-        <v>2.6809664494920611</v>
+        <v>2.5627698903959235</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.6809664494920612E-2</v>
+        <v>2.5627698903959235E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.5030046864978872</v>
+        <v>-2.209426104135249</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5030046864978873E-2</v>
+        <v>-2.2094261041352491E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C29" s="10">
-        <v>2.6409346567269854</v>
+        <v>2.5098554346299311</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.6409346567269853E-2</v>
+        <v>2.5098554346299311E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.4950477813923095</v>
+        <v>-2.1433936519179007</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4950477813923094E-2</v>
+        <v>-2.1433936519179006E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C30" s="10">
-        <v>2.5432508064299917</v>
+        <v>2.4321920966956521</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.5432508064299916E-2</v>
+        <v>2.4321920966956522E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.3917355855546796</v>
+        <v>-2.1271937672668861</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3917355855546794E-2</v>
+        <v>-2.1271937672668863E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C31" s="10">
-        <v>2.5127136277036066</v>
+        <v>2.2075253833059327</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.5127136277036066E-2</v>
+        <v>2.2075253833059326E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.3720434192695605</v>
+        <v>-2.0435843613963227</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3720434192695605E-2</v>
+        <v>-2.0435843613963226E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C32" s="10">
-        <v>2.4041281311605101</v>
+        <v>2.0981973233901021</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.4041281311605101E-2</v>
+        <v>2.0981973233901021E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.3455525958721712</v>
+        <v>-2.0210862608719604</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3455525958721711E-2</v>
+        <v>-2.0210862608719606E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C33" s="10">
-        <v>2.3916356095522637</v>
+        <v>2.0850481380747117</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.3916356095522638E-2</v>
+        <v>2.0850481380747118E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G33" s="10">
-        <v>-2.2866895573398907</v>
+        <v>-1.9955531802970969</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2866895573398906E-2</v>
+        <v>-1.995553180297097E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C34" s="10">
-        <v>2.3033102552226299</v>
+        <v>2.0104689250012719</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.3033102552226299E-2</v>
+        <v>2.0104689250012721E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G34" s="10">
-        <v>-2.2422848980240557</v>
+        <v>-1.9941591425575136</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2422848980240558E-2</v>
+        <v>-1.9941591425575136E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="10">
-        <v>2.2605761987862927</v>
+        <v>1.9912055076369131</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>2.2605761987862925E-2</v>
+        <v>1.9912055076369131E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G35" s="10">
-        <v>-2.2004985408639794</v>
+        <v>-1.9119858208758242</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2004985408639793E-2</v>
+        <v>-1.9119858208758243E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C36" s="10">
-        <v>2.0950895939814607</v>
+        <v>1.9481978272974623</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>2.0950895939814605E-2</v>
+        <v>1.9481978272974623E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G36" s="10">
-        <v>-2.1038836536332797</v>
+        <v>-1.7937745156034437</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1038836536332796E-2</v>
+        <v>-1.7937745156034437E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C37" s="10">
-        <v>2.0406048397746366</v>
+        <v>1.7446904333315016</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>2.0406048397746367E-2</v>
+        <v>1.7446904333315017E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G37" s="10">
-        <v>-2.0180739639787797</v>
+        <v>-1.7896264676777158</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0180739639787795E-2</v>
+        <v>-1.7896264676777157E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C38" s="10">
-        <v>1.8995888328409045</v>
+        <v>1.6067850405688737</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.8995888328409045E-2</v>
+        <v>1.6067850405688738E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.7971220988040524</v>
+        <v>-1.7321728084499362</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7971220988040524E-2</v>
+        <v>-1.732172808449936E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C39" s="10">
-        <v>1.7761936685728725</v>
+        <v>1.4968446417390027</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.7761936685728726E-2</v>
+        <v>1.4968446417390027E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.7404444461107103</v>
+        <v>-1.6089367918507707</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7404444461107102E-2</v>
+        <v>-1.6089367918507708E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C40" s="10">
-        <v>1.7027350005289228</v>
+        <v>0.98481520791170696</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.7027350005289228E-2</v>
+        <v>9.8481520791170694E-3</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.6860273057321093</v>
+        <v>-1.494577307054914</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6860273057321094E-2</v>
+        <v>-1.494577307054914E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C41" s="10">
-        <v>1.70069237158685</v>
+        <v>0.94212419763022948</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.70069237158685E-2</v>
+        <v>9.4212419763022946E-3</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.6768660654297989</v>
+        <v>-1.4765597546543652</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6768660654297989E-2</v>
+        <v>-1.4765597546543652E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C42" s="10">
-        <v>1.2796350413276278</v>
+        <v>0.74655664930348975</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>1.2796350413276279E-2</v>
+        <v>7.4655664930348975E-3</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.5780082917113729</v>
+        <v>-1.4492896285598154</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.578008291711373E-2</v>
+        <v>-1.4492896285598154E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C43" s="10">
-        <v>1.0959681448661063</v>
+        <v>0.72041709585217106</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>1.0959681448661062E-2</v>
+        <v>7.204170958521711E-3</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.4966184349352989</v>
+        <v>-1.3909880938269175</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.496618434935299E-2</v>
+        <v>-1.3909880938269175E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C44" s="10">
-        <v>0.91552807501435485</v>
+        <v>0.6712714794526613</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>9.155280750143548E-3</v>
+        <v>6.7127147945266127E-3</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.4711429747531979</v>
+        <v>-1.3884102113419121</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.4711429747531979E-2</v>
+        <v>-1.3884102113419122E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C45" s="10">
-        <v>0.87235924622549432</v>
+        <v>0.61628335957250424</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>8.7235924622549432E-3</v>
+        <v>6.1628335957250426E-3</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.458038876591176</v>
+        <v>-1.3074682183127213</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.4580388765911761E-2</v>
+        <v>-1.3074682183127214E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C46" s="10">
-        <v>0.80161459435984606</v>
+        <v>0.54435032429445362</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>8.0161459435984603E-3</v>
+        <v>5.4435032429445366E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.3870569443397152</v>
+        <v>-1.3069378013300608</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3870569443397152E-2</v>
+        <v>-1.3069378013300608E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>212</v>
+        <v>13</v>
       </c>
       <c r="C47" s="10">
-        <v>0.54827879937659163</v>
+        <v>0.35372342663835893</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="0"/>
-        <v>5.4827879937659162E-3</v>
+        <v>3.5372342663835894E-3</v>
       </c>
       <c r="F47" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1.3040521026412208</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3040521026412209E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="F48" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-1.2845994016584155</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2845994016584155E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F49" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-1.2806145811026568</v>
+      </c>
+      <c r="H49" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2806145811026569E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F50" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="G47" s="10">
-        <v>-1.3723734746438416</v>
-      </c>
-      <c r="H47" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.3723734746438416E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" s="10">
-        <v>0.52653546359103776</v>
-      </c>
-      <c r="D48" s="10">
-        <f t="shared" si="0"/>
-        <v>5.2653546359103772E-3</v>
-      </c>
-      <c r="F48" s="11" t="s">
+      <c r="G50" s="10">
+        <v>-1.2733598873867638</v>
+      </c>
+      <c r="H50" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2733598873867637E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F51" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G48" s="10">
-        <v>-1.3436569571637658</v>
-      </c>
-      <c r="H48" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.3436569571637658E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C49" s="10">
-        <v>0.5086438044303534</v>
-      </c>
-      <c r="D49" s="10">
-        <f t="shared" si="0"/>
-        <v>5.0864380443035343E-3</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="G51" s="10">
+        <v>-1.2325645600528132</v>
+      </c>
+      <c r="H51" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2325645600528132E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F52" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G49" s="10">
-        <v>-1.2440525418550425</v>
-      </c>
-      <c r="H49" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.2440525418550426E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="10">
-        <v>0.32731868690403498</v>
-      </c>
-      <c r="D50" s="10">
-        <f t="shared" si="0"/>
-        <v>3.2731868690403496E-3</v>
-      </c>
-      <c r="F50" s="11" t="s">
+      <c r="G52" s="10">
+        <v>-0.98810854320703134</v>
+      </c>
+      <c r="H52" s="12">
+        <f t="shared" si="2"/>
+        <v>-9.8810854320703131E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D53" s="1"/>
+      <c r="F53" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G50" s="10">
-        <v>-1.1840062613288505</v>
-      </c>
-      <c r="H50" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.1840062613288505E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="9"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="F51" s="11" t="s">
+      <c r="G53" s="10">
+        <v>-0.94154124273748196</v>
+      </c>
+      <c r="H53" s="12">
+        <f t="shared" si="2"/>
+        <v>-9.4154124273748193E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D54" s="1"/>
+      <c r="F54" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G51" s="10">
-        <v>-1.0002671278713637</v>
-      </c>
-      <c r="H51" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.0002671278713637E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F52" s="11" t="s">
+      <c r="G54" s="10">
+        <v>-0.89393254013237</v>
+      </c>
+      <c r="H54" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.9393254013236997E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D55" s="1"/>
+      <c r="F55" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="G52" s="10">
-        <v>-0.9459196239568739</v>
-      </c>
-      <c r="H52" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.4591962395687394E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F53" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="G53" s="10">
-        <v>-0.92470578535174563</v>
-      </c>
-      <c r="H53" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.2470578535174559E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F54" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="G54" s="10">
-        <v>-0.91374020936421363</v>
-      </c>
-      <c r="H54" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.1374020936421368E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F55" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="G55" s="10">
-        <v>-0.88606621620990911</v>
+        <v>-0.85959217876515093</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-8.8606621620990911E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.5959217876515094E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.85118947218790486</v>
+        <v>-0.83076110098309497</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.5118947218790486E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.3076110098309498E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.84885910669806452</v>
+        <v>-0.82131867111538226</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4885910669806452E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.2131867111538224E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.84172281386665282</v>
+        <v>-0.79351820000791196</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4172281386665285E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.9351820000791197E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.80320460287803819</v>
+        <v>-0.78645940792387792</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-8.0320460287803819E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.8645940792387795E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.78316461545734595</v>
+        <v>-0.76066545316329681</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8316461545734593E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.6066545316329677E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.77703891819948889</v>
+        <v>-0.73616695371993224</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7703891819948887E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.3616695371993227E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.74128160519666764</v>
+        <v>-0.7106220142592159</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4128160519666766E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.1062201425921593E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.73504018427127416</v>
+        <v>-0.69770510126098817</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-7.3504018427127419E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-6.9770510126098816E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.66278148523870672</v>
+        <v>-0.69122760876568512</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.6278148523870673E-3</v>
+        <v>-6.9122760876568516E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.64423842481688998</v>
+        <v>-0.63807820273744953</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.4423842481689001E-3</v>
+        <v>-6.3807820273744957E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.51114862226544999</v>
+        <v>-0.56896397532157073</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-5.1114862226545E-3</v>
+        <v>-5.6896397532157075E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.50150101026930494</v>
+        <v>-0.41722081673939365</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-5.0150101026930497E-3</v>
+        <v>-4.1722081673939366E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.44881481278802488</v>
+        <v>-0.3938261891657775</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-4.4881481278802489E-3</v>
+        <v>-3.9382618916577747E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.41729947289927372</v>
+        <v>-0.39343732974725998</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-4.172994728992737E-3</v>
+        <v>-3.9343732974726001E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.41190149113877106</v>
+        <v>-0.37300865403654426</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-4.1190149113877108E-3</v>
+        <v>-3.7300865403654426E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.40800382426986115</v>
+        <v>-0.34174543086615383</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-4.0800382426986114E-3</v>
+        <v>-3.4174543086615385E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.37745419605778052</v>
+        <v>-0.25310390078560174</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-3.7745419605778054E-3</v>
+        <v>-2.5310390078560176E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
@@ -4294,11 +4219,11 @@
         <v>14</v>
       </c>
       <c r="G73" s="10">
-        <v>-0.28641687175955338</v>
+        <v>-2.7968664389488827E-2</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>-2.8641687175955336E-3</v>
+        <v>-2.7968664389488827E-4</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
@@ -4714,55 +4639,52 @@
       <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D177" s="1"/>
+    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D178" s="1"/>
+    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D179" s="1"/>
+    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">

--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{676C9B0C-8BDD-6E4D-902A-B0109AD8F733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAA3B71C-6C9E-2849-99DA-1638F5A4A96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issuer" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="240">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -63,204 +63,228 @@
     <t>SERIES: Trading (non-additive)</t>
   </si>
   <si>
-    <t>ETSY</t>
+    <t>LION</t>
+  </si>
+  <si>
+    <t>AAOI</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>APPLIED OPTOELECTRONICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>FAIR ISAAC ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>4901</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>RHMG</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>NICE</t>
+  </si>
+  <si>
+    <t>TYL</t>
+  </si>
+  <si>
+    <t>T CN</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>RDDT</t>
+  </si>
+  <si>
+    <t>RCIb</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>BCE</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>WTC</t>
+  </si>
+  <si>
+    <t>CBOE</t>
+  </si>
+  <si>
+    <t>WSP</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>NBIS</t>
+  </si>
+  <si>
+    <t>CRWV</t>
   </si>
   <si>
     <t>DASH</t>
   </si>
   <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
-  </si>
-  <si>
-    <t>LAUREATE EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>Instrument</t>
-  </si>
-  <si>
-    <t>FAIR ISAAC ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>RHMG</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>4901</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>MSLYT26S</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>NICE</t>
-  </si>
-  <si>
-    <t>RCIb</t>
-  </si>
-  <si>
-    <t>T CN</t>
-  </si>
-  <si>
-    <t>CDW</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>TYL</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>WTC</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>WSP</t>
-  </si>
-  <si>
-    <t>SOFI</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
     <t>3034</t>
   </si>
   <si>
@@ -270,10 +294,22 @@
     <t>CNXC</t>
   </si>
   <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>NOKIA</t>
+  </si>
+  <si>
     <t>TEPRF</t>
   </si>
   <si>
-    <t>LAUR</t>
+    <t>META</t>
   </si>
   <si>
     <t>XYZ</t>
@@ -282,279 +318,324 @@
     <t>TSM</t>
   </si>
   <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
     <t>GOOG</t>
   </si>
   <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>T</t>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>6752</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>FWONK</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>APP</t>
   </si>
   <si>
     <t>CART</t>
   </si>
   <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>6857</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>6752</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>FWONK</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>000660</t>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>NOD</t>
   </si>
   <si>
     <t>SAPG</t>
   </si>
   <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>STM</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>MSLYT26L</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>SPHR</t>
   </si>
   <si>
     <t>BILL</t>
   </si>
   <si>
+    <t>NXPI</t>
+  </si>
+  <si>
+    <t>CMCSA</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
     <t>SNDK</t>
   </si>
   <si>
+    <t>NET</t>
+  </si>
+  <si>
     <t>P</t>
   </si>
   <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>QRVO</t>
+    <t>CINTAS ORD (NMS)</t>
   </si>
   <si>
     <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
   </si>
   <si>
-    <t>CINTAS ORD (NMS)</t>
-  </si>
-  <si>
     <t>AUTODESK ORD (NMS)</t>
   </si>
   <si>
     <t>CANON ORD (TYO) CFD</t>
   </si>
   <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>VERISK ANALYTICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
     <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
   </si>
   <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
+    <t>SAMSARA CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SERVICETITAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PINTEREST CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EXPEDIA GROUP ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
   </si>
   <si>
     <t>LOGITECH N ORD (NMS)</t>
   </si>
   <si>
-    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>VERISK ANALYTICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>APPLE ORD (NMS)</t>
+    <t>SANRIO ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>RHEINMETALL ORD (GER)</t>
+  </si>
+  <si>
+    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
   </si>
   <si>
     <t>EQUIFAX ORD (NYS)</t>
   </si>
   <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NEW YORK TIMES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RHEINMETALL ORD (GER)</t>
+    <t>WILLIAMS SONOMA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>REA GROUP ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>SLM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>NVIDIA ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NICE ADR REP 1 ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TELUS ORD (TOR)</t>
+  </si>
+  <si>
+    <t>QUALYS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>REDDIT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
   </si>
   <si>
     <t>EBAY ORD (NMS)</t>
   </si>
   <si>
-    <t>SAMSARA CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>MSLYT26S INDEX CFD</t>
-  </si>
-  <si>
-    <t>CROWDSTRIKE HOLDINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>REA GROUP ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>NICE ADR REP 1 ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
-  </si>
-  <si>
-    <t>TELUS ORD (TOR)</t>
-  </si>
-  <si>
-    <t>CDW ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WILLIAMS SONOMA ORD (NYS)</t>
-  </si>
-  <si>
     <t>GARTNER ORD (NYS)</t>
   </si>
   <si>
-    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
+    <t>DUOLINGO CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ARISTA NETWORKS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBERT HALF ORD (NYS)</t>
   </si>
   <si>
     <t>SEZZLE INC (NMS)</t>
   </si>
   <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
+    <t>CARGURUS CL A ORD (NMS)</t>
   </si>
   <si>
     <t>GRAND CANYON EDUCATION ORD (NMS)</t>
   </si>
   <si>
+    <t>COINBASE GLOBAL CL A ORD (NMS)</t>
+  </si>
+  <si>
     <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
   </si>
   <si>
-    <t>ROBERT HALF ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARISTA NETWORKS ORD (NYS)</t>
-  </si>
-  <si>
     <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
   </si>
   <si>
     <t>SYMBOTIC CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>CARGURUS CL A ORD (NMS)</t>
+    <t>BCE ORD (TOR)</t>
+  </si>
+  <si>
+    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
   </si>
   <si>
     <t>ADOBE ORD (NMS)</t>
   </si>
   <si>
-    <t>QUALYS ORD (NMS)</t>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
   </si>
   <si>
     <t>WISETECH GLOBAL ORD (ASX) CFD</t>
   </si>
   <si>
+    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
+  </si>
+  <si>
+    <t>CBOE GLOBAL MARKETS ORD (BAT)</t>
+  </si>
+  <si>
+    <t>WSP GLOBAL ORD (TOR)</t>
+  </si>
+  <si>
+    <t>CIENA ORD (NYS)</t>
+  </si>
+  <si>
     <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
   </si>
   <si>
-    <t>WSP GLOBAL ORD (TOR)</t>
-  </si>
-  <si>
-    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
     <t>DATADOG CL A ORD (NMS)</t>
   </si>
   <si>
+    <t>NEBIUS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>COREWEAVE CL A ORD (NMS)</t>
+  </si>
+  <si>
     <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
   </si>
   <si>
     <t>STANTEC ORD (TOR)</t>
   </si>
   <si>
-    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
-  </si>
-  <si>
     <t>CONCENTRIX ORD (NMS)</t>
   </si>
   <si>
+    <t>LUMENTUM HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SITIME ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>NOKIA ADR REPSG 1 SER A ORD (NYS)</t>
+  </si>
+  <si>
     <t>TELEPERFORMANCE ORD (PAR) CFD</t>
   </si>
   <si>
@@ -564,106 +645,118 @@
     <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
   </si>
   <si>
+    <t>AT&amp;T ORD (NYS)</t>
+  </si>
+  <si>
+    <t>AMAZON COM ORD (NMS)</t>
+  </si>
+  <si>
     <t>ALPHABET CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>AMAZON COM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AT&amp;T ORD (NYS)</t>
+    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WAYFAIR CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EATON ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>AUTO1 GROUP ORD (GER)</t>
+  </si>
+  <si>
+    <t>PANASONIC HLDG ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>LYFT CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ADVANTEST ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>IRON MOUNTAIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBLOX CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SK HYNIX ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>TRIMBLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DRAFTKINGS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
+  </si>
+  <si>
+    <t>APPLOVIN CL A ORD (NMS)</t>
   </si>
   <si>
     <t>MAPLEBEAR ORD (NMS)</t>
   </si>
   <si>
-    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>EATON ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AUTO1 GROUP ORD (GER)</t>
-  </si>
-  <si>
-    <t>PANASONIC HLDG ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>IRON MOUNTAIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBLOX CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LYFT CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (NYS)</t>
-  </si>
-  <si>
-    <t>DRAFTKINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TRIMBLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SK HYNIX ORD (KSC) CFD_USD</t>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
+    <t>STMICROELECTRONICS ADR (NYS)</t>
+  </si>
+  <si>
+    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
   </si>
   <si>
     <t>SAP ORD (GER)</t>
   </si>
   <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
-  </si>
-  <si>
-    <t>STMICROELECTRONICS ADR (NYS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (MIL)</t>
-  </si>
-  <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>MSLYT26L INDEX CFD</t>
-  </si>
-  <si>
-    <t>WAYFAIR CL A ORD (NYS)</t>
-  </si>
-  <si>
     <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
   </si>
   <si>
     <t>BILL HOLDINGS ORD (NYS)</t>
   </si>
   <si>
+    <t>NXP SEMICONDUCTORS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>COMCAST CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NETAPP ORD (NMS)</t>
+  </si>
+  <si>
     <t>SANDISK ORD (NMS)</t>
   </si>
   <si>
+    <t>CLOUDFLARE CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>META US 01/15/27 P620 OTC (META 1/15/27 P620 OTC)</t>
+  </si>
+  <si>
     <t>EVERPURE CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>CLOUDFLARE CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>QORVO ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ETSY ORD (NYS)</t>
+    <t>LIONSGATE STUDIOS ORD (NYS)</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1287,24 +1380,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C11" s="10">
-        <v>9.3676345958810714</v>
+        <v>10.64005596812768</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D45" si="0">IF(B11="","",(C11/100))</f>
-        <v>9.3676345958810719E-2</v>
+        <f t="shared" ref="D11:D48" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10640055968127679</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-6.6747511166068776</v>
+        <v>-6.4259951438552427</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-6.6747511166068779E-2</v>
+        <v>-6.4259951438552426E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -1325,24 +1418,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C12" s="10">
-        <v>7.178295390076145</v>
+        <v>7.1950650992045766</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.1782953900761448E-2</v>
+        <v>7.195065099204577E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.1257189854440615</v>
+        <v>-5.2216320699761347</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1257189854440617E-2</v>
+        <v>-5.221632069976135E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1353,977 +1446,1004 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C13" s="10">
-        <v>5.0098197800339523</v>
+        <v>5.2547784652781599</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.0098197800339521E-2</v>
+        <v>5.25477846527816E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-5.0593808269021654</v>
+        <v>-4.365073485393987</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0593808269021656E-2</v>
+        <v>-4.3650734853939867E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C14" s="10">
-        <v>4.9893411504096523</v>
+        <v>4.9119947853290071</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.989341150409652E-2</v>
+        <v>4.9119947853290075E-2</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.7845448503728001</v>
+        <v>-4.3408345472357777</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7845448503728003E-2</v>
+        <v>-4.3408345472357779E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C15" s="10">
-        <v>4.8934917789138455</v>
+        <v>4.879267170305237</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.8934917789138457E-2</v>
+        <v>4.8792671703052369E-2</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.2526844426100716</v>
+        <v>-3.8140152582354738</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2526844426100718E-2</v>
+        <v>-3.8140152582354737E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C16" s="10">
-        <v>4.7956028569605618</v>
+        <v>4.7918802751980447</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.7956028569605617E-2</v>
+        <v>4.7918802751980447E-2</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.7538715318079805</v>
+        <v>-3.6106726835593657</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7538715318079806E-2</v>
+        <v>-3.6106726835593655E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C17" s="10">
-        <v>4.6320517671014345</v>
+        <v>4.7381546652776985</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.6320517671014347E-2</v>
+        <v>4.7381546652776982E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.5028928974400122</v>
+        <v>-3.5520112268146975</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5028928974400124E-2</v>
+        <v>-3.5520112268146976E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C18" s="10">
-        <v>4.5539753980328364</v>
+        <v>4.3307314974614863</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.5539753980328362E-2</v>
+        <v>4.3307314974614861E-2</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.4100075996797381</v>
+        <v>-3.4496143935110948</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4100075996797381E-2</v>
+        <v>-3.4496143935110947E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C19" s="10">
-        <v>4.1488266383129728</v>
+        <v>4.1460580439357262</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>4.1488266383129725E-2</v>
+        <v>4.1460580439357263E-2</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.2883526862952359</v>
+        <v>-3.4211573857452673</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2883526862952359E-2</v>
+        <v>-3.4211573857452673E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C20" s="10">
-        <v>3.9941428681304529</v>
+        <v>4.1216441647674635</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.9941428681304528E-2</v>
+        <v>4.1216441647674636E-2</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.2377588228208172</v>
+        <v>-3.0710882033923217</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2377588228208173E-2</v>
+        <v>-3.0710882033923217E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C21" s="10">
-        <v>3.960998571869724</v>
+        <v>4.0422262295122326</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.9609985718697241E-2</v>
+        <v>4.042226229512233E-2</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.9534394867720826</v>
+        <v>-3.0473678223257492</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9534394867720824E-2</v>
+        <v>-3.0473678223257493E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C22" s="10">
-        <v>3.6679107565062949</v>
+        <v>3.5991535325953463</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.667910756506295E-2</v>
+        <v>3.5991535325953464E-2</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.8758244405332403</v>
+        <v>-3.0344210290871141</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8758244405332402E-2</v>
+        <v>-3.034421029087114E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C23" s="10">
-        <v>3.3901254552592754</v>
+        <v>3.3814452225683911</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.3901254552592755E-2</v>
+        <v>3.3814452225683911E-2</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.8675313674108578</v>
+        <v>-3.0047060322135644</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8675313674108579E-2</v>
+        <v>-3.0047060322135645E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C24" s="10">
-        <v>3.3536380206432495</v>
+        <v>3.3235701789410972</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.3536380206432494E-2</v>
+        <v>3.3235701789410974E-2</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.5902503120703009</v>
+        <v>-2.846663571898902</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.590250312070301E-2</v>
+        <v>-2.8466635718989018E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C25" s="10">
-        <v>3.2000877018935543</v>
+        <v>3.3115135890385243</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>3.2000877018935545E-2</v>
+        <v>3.3115135890385242E-2</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.5047802005457753</v>
+        <v>-2.5229770882784228</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5047802005457753E-2</v>
+        <v>-2.522977088278423E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C26" s="10">
-        <v>3.1627821872447059</v>
+        <v>3.2683840292570423</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>3.1627821872447059E-2</v>
+        <v>3.2683840292570425E-2</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.4719791999441085</v>
+        <v>-2.3856987210331826</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4719791999441087E-2</v>
+        <v>-2.3856987210331825E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C27" s="10">
-        <v>3.0505612112986151</v>
+        <v>3.0222359078790135</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>3.050561211298615E-2</v>
+        <v>3.0222359078790135E-2</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.4280737722724806</v>
+        <v>-2.3761832582530054</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4280737722724807E-2</v>
+        <v>-2.3761832582530052E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C28" s="10">
-        <v>2.9758227955613918</v>
+        <v>2.8433870771432437</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.975822795561392E-2</v>
+        <v>2.8433870771432435E-2</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.209426104135249</v>
+        <v>-2.3540382862818929</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2094261041352491E-2</v>
+        <v>-2.3540382862818929E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C29" s="10">
-        <v>2.5098554346299311</v>
+        <v>2.7046177195658769</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.5098554346299311E-2</v>
+        <v>2.7046177195658768E-2</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.1433936519179007</v>
+        <v>-2.3165984967731266</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1433936519179006E-2</v>
+        <v>-2.3165984967731267E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C30" s="10">
-        <v>2.4321920966956521</v>
+        <v>2.3384310105678714</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.4321920966956522E-2</v>
+        <v>2.3384310105678714E-2</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1271937672668861</v>
+        <v>-2.2906035669978437</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1271937672668863E-2</v>
+        <v>-2.2906035669978439E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C31" s="10">
-        <v>2.2075253833059327</v>
+        <v>2.2703685525546646</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.2075253833059326E-2</v>
+        <v>2.2703685525546646E-2</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0435843613963227</v>
+        <v>-2.2171344338401728</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0435843613963226E-2</v>
+        <v>-2.2171344338401729E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C32" s="10">
-        <v>2.0981973233901021</v>
+        <v>2.2584248608532977</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.0981973233901021E-2</v>
+        <v>2.2584248608532979E-2</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.0210862608719604</v>
+        <v>-2.0650361555785475</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0210862608719606E-2</v>
+        <v>-2.0650361555785476E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C33" s="10">
-        <v>2.0850481380747117</v>
+        <v>2.2387676595398327</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.0850481380747118E-2</v>
+        <v>2.2387676595398327E-2</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9955531802970969</v>
+        <v>-1.9827602150565788</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.995553180297097E-2</v>
+        <v>-1.9827602150565789E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C34" s="10">
-        <v>2.0104689250012719</v>
+        <v>2.1941851726367463</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.0104689250012721E-2</v>
+        <v>2.1941851726367465E-2</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.9941591425575136</v>
+        <v>-1.9602637021482971</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9941591425575136E-2</v>
+        <v>-1.9602637021482971E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C35" s="10">
-        <v>1.9481978272974623</v>
+        <v>2.1727092295605615</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.9481978272974623E-2</v>
+        <v>2.1727092295605613E-2</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.9119858208758242</v>
+        <v>-1.8487967456276129</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9119858208758243E-2</v>
+        <v>-1.8487967456276129E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C36" s="10">
-        <v>1.7446904333315016</v>
+        <v>1.8923947547785789</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.7446904333315017E-2</v>
+        <v>1.8923947547785789E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.7937745156034437</v>
+        <v>-1.7851622624583465</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7937745156034437E-2</v>
+        <v>-1.7851622624583466E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C37" s="10">
-        <v>1.6067850405688737</v>
+        <v>1.8376374279430556</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.6067850405688738E-2</v>
+        <v>1.8376374279430556E-2</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.7896264676777158</v>
+        <v>-1.7103975527725646</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7896264676777157E-2</v>
+        <v>-1.7103975527725645E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C38" s="10">
-        <v>1.4968446417390027</v>
+        <v>1.8052287869531423</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.4968446417390027E-2</v>
+        <v>1.8052287869531423E-2</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.7321728084499362</v>
+        <v>-1.5565238467242555</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.732172808449936E-2</v>
+        <v>-1.5565238467242554E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C39" s="10">
-        <v>0.98481520791170696</v>
+        <v>1.7885051185863587</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>9.8481520791170694E-3</v>
+        <v>1.7885051185863587E-2</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.6089367918507707</v>
+        <v>-1.546089004395887</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6089367918507708E-2</v>
+        <v>-1.5460890043958871E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C40" s="10">
-        <v>0.94212419763022948</v>
+        <v>1.1734697487598551</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>9.4212419763022946E-3</v>
+        <v>1.1734697487598551E-2</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.494577307054914</v>
+        <v>-1.5430879921263745</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.494577307054914E-2</v>
+        <v>-1.5430879921263746E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C41" s="10">
-        <v>0.74655664930348975</v>
+        <v>1.1247678708981241</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>7.4655664930348975E-3</v>
+        <v>1.1247678708981241E-2</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.4765597546543652</v>
+        <v>-1.4811772286335634</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4765597546543652E-2</v>
+        <v>-1.4811772286335633E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C42" s="10">
-        <v>0.72041709585217106</v>
+        <v>0.97437978627921507</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>7.204170958521711E-3</v>
+        <v>9.7437978627921504E-3</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.4492896285598154</v>
+        <v>-1.3918029071695248</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4492896285598154E-2</v>
+        <v>-1.3918029071695249E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C43" s="10">
-        <v>0.6712714794526613</v>
+        <v>0.95525050810167356</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>6.7127147945266127E-3</v>
+        <v>9.5525050810167361E-3</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.3909880938269175</v>
+        <v>-1.3439701619380315</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.3909880938269175E-2</v>
+        <v>-1.3439701619380316E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C44" s="10">
-        <v>0.61628335957250424</v>
+        <v>0.86489775821718662</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>6.1628335957250426E-3</v>
+        <v>8.6489775821718667E-3</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.3884102113419121</v>
+        <v>-1.3329396474390769</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3884102113419122E-2</v>
+        <v>-1.3329396474390768E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="C45" s="10">
-        <v>0.54435032429445362</v>
+        <v>0.78258783268582433</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>5.4435032429445366E-3</v>
+        <v>7.8258783268582433E-3</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.3074682183127213</v>
+        <v>-1.302842523119903</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3074682183127214E-2</v>
+        <v>-1.302842523119903E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="9"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
+      <c r="B46" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0.7564468353401671</v>
+      </c>
+      <c r="D46" s="10">
+        <f t="shared" si="0"/>
+        <v>7.5644683534016712E-3</v>
+      </c>
       <c r="F46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.3069378013300608</v>
+        <v>-1.2861151014962608</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3069378013300608E-2</v>
+        <v>-1.2861151014962609E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.4816872103436059</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>4.816872103436059E-3</v>
+      </c>
       <c r="F47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.3040521026412208</v>
+        <v>-1.2512477732885505</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3040521026412209E-2</v>
+        <v>-1.2512477732885505E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.2768825325933561</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="0"/>
+        <v>2.7688253259335609E-3</v>
+      </c>
       <c r="F48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.2845994016584155</v>
+        <v>-1.245197897856299</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2845994016584155E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.245197897856299E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="9"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
       <c r="F49" s="11" t="s">
         <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.2806145811026568</v>
+        <v>-1.1713001457601533</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2806145811026569E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.1713001457601534E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F50" s="11" t="s">
         <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.2733598873867638</v>
+        <v>-1.1605663203932066</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2733598873867637E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D51" s="1"/>
+        <v>-1.1605663203932066E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-1.2325645600528132</v>
+        <v>-1.1509750922079443</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2325645600528132E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D52" s="1"/>
+        <v>-1.1509750922079443E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.98810854320703134</v>
+        <v>-1.0709084280107859</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-9.8810854320703131E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D53" s="1"/>
+        <v>-1.0709084280107859E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.94154124273748196</v>
+        <v>-1.0610580769480413</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4154124273748193E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.0610580769480413E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D54" s="1"/>
       <c r="F54" s="11" t="s">
         <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.89393254013237</v>
+        <v>-1.0207023736332841</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-8.9393254013236997E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.0207023736332841E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.85959217876515093</v>
+        <v>-0.98033362007491975</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-8.5959217876515094E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.8033362007491978E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
         <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.83076110098309497</v>
+        <v>-0.9644062055724083</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.3076110098309498E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.6440620557240835E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.82131867111538226</v>
+        <v>-0.92358035363769697</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.2131867111538224E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.2358035363769696E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
         <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.79351820000791196</v>
+        <v>-0.91996570803856947</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-7.9351820000791197E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.1996570803856946E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
         <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.78645940792387792</v>
+        <v>-0.89122288634373958</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8645940792387795E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.9122288634373957E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.76066545316329681</v>
+        <v>-0.88366122175361306</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.6066545316329677E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.8366122175361304E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
         <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.73616695371993224</v>
+        <v>-0.85920520117370169</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.3616695371993227E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.5920520117370169E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.7106220142592159</v>
+        <v>-0.83451957787032593</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.1062201425921593E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.3451957787032596E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
         <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.69770510126098817</v>
+        <v>-0.78195496384089247</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9770510126098816E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.819549638408925E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.69122760876568512</v>
+        <v>-0.75481416200005946</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9122760876568516E-3</v>
+        <v>-7.5481416200005947E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
@@ -2332,11 +2452,11 @@
         <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.63807820273744953</v>
+        <v>-0.67829021780682441</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.3807820273744957E-3</v>
+        <v>-6.7829021780682446E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
@@ -2345,11 +2465,11 @@
         <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.56896397532157073</v>
+        <v>-0.6310523461797608</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-5.6896397532157075E-3</v>
+        <v>-6.3105234617976081E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
@@ -2358,11 +2478,11 @@
         <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.41722081673939365</v>
+        <v>-0.63061754196957609</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-4.1722081673939366E-3</v>
+        <v>-6.3061754196957606E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
@@ -2371,11 +2491,11 @@
         <v>74</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.3938261891657775</v>
+        <v>-0.56071187298688574</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-3.9382618916577747E-3</v>
+        <v>-5.6071187298688575E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
@@ -2384,11 +2504,11 @@
         <v>75</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.39343732974725998</v>
+        <v>-0.56007034541067402</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-3.9343732974726001E-3</v>
+        <v>-5.6007034541067403E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
@@ -2397,11 +2517,11 @@
         <v>76</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.34174543086615383</v>
+        <v>-0.49515880009730046</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-3.4174543086615385E-3</v>
+        <v>-4.9515880009730045E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
@@ -2410,11 +2530,11 @@
         <v>77</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.25310390078560174</v>
+        <v>-0.48492530203864975</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-2.5310390078560176E-3</v>
+        <v>-4.8492530203864976E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
@@ -2423,94 +2543,202 @@
         <v>78</v>
       </c>
       <c r="G72" s="10">
-        <v>-2.7968664389488827E-2</v>
+        <v>-0.46923884125274068</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-2.7968664389488827E-4</v>
+        <v>-4.6923884125274068E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
       <c r="F73" s="11" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="G73" s="10">
-        <v>-1.9285227398185344E-2</v>
+        <v>-0.46173053312736234</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>-1.9285227398185346E-4</v>
+        <v>-4.6173053312736235E-3</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="13"/>
+      <c r="F74" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-0.44554891075458514</v>
+      </c>
+      <c r="H74" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.4554891075458515E-3</v>
+      </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
+      <c r="F75" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-0.3679944396176823</v>
+      </c>
+      <c r="H75" s="12">
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-3.6799443961768232E-3</v>
+      </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
+      <c r="F76" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-0.35606298251969726</v>
+      </c>
+      <c r="H76" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.5606298251969724E-3</v>
+      </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
-      <c r="G77" t="s">
-        <v>5</v>
+      <c r="F77" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-0.34449675752917985</v>
+      </c>
+      <c r="H77" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.4449675752917987E-3</v>
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
+      <c r="F78" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-0.27875728165155722</v>
+      </c>
+      <c r="H78" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.787572816515572E-3</v>
+      </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
-      <c r="H79" s="1"/>
+      <c r="F79" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-0.24921887088681788</v>
+      </c>
+      <c r="H79" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.4921887088681788E-3</v>
+      </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
-      <c r="H80" s="1"/>
+      <c r="F80" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-0.23320955251166742</v>
+      </c>
+      <c r="H80" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.3320955251166743E-3</v>
+      </c>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
+      <c r="F81" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G81" s="10">
+        <v>-0.23178456106778422</v>
+      </c>
+      <c r="H81" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.3178456106778423E-3</v>
+      </c>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
+      <c r="F82" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G82" s="10">
+        <v>-0.23062227374651528</v>
+      </c>
+      <c r="H82" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.3062227374651529E-3</v>
+      </c>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
+      <c r="F83" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G83" s="10">
+        <v>-0.2198304019835241</v>
+      </c>
+      <c r="H83" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.198304019835241E-3</v>
+      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="H84" s="1"/>
+      <c r="F84" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-0.21575192897618961</v>
+      </c>
+      <c r="H84" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.157519289761896E-3</v>
+      </c>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
-      <c r="H85" s="1"/>
+      <c r="F85" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" s="10">
+        <v>-0.17906361599513917</v>
+      </c>
+      <c r="H85" s="12">
+        <f t="shared" si="3"/>
+        <v>-1.7906361599513917E-3</v>
+      </c>
     </row>
     <row r="86" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D86" s="1"/>
-      <c r="H86" s="1"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="13"/>
     </row>
     <row r="87" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D87" s="1"/>
-      <c r="H87" s="1"/>
     </row>
     <row r="88" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D88" s="1"/>
-      <c r="H88" s="1"/>
     </row>
     <row r="89" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
-      <c r="H89" s="1"/>
+      <c r="G89" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="90" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
-      <c r="H90" s="1"/>
     </row>
     <row r="91" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
@@ -2849,57 +3077,60 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -2928,6 +3159,42 @@
     </row>
     <row r="201" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="1"/>
+    </row>
+    <row r="208" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H208" s="1"/>
+    </row>
+    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H209" s="1"/>
+    </row>
+    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H210" s="1"/>
+    </row>
+    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H211" s="1"/>
+    </row>
+    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H212" s="1"/>
+    </row>
+    <row r="213" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H213" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2937,7 +3204,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -3052,24 +3319,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C11" s="10">
-        <v>9.3676345958810714</v>
+        <v>10.64005596812768</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
-        <v>9.3676345958810719E-2</v>
+        <f t="shared" ref="D11:D51" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10640055968127679</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-6.6747511166068776</v>
+        <v>-6.4259951438552427</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-6.6747511166068779E-2</v>
+        <v>-6.4259951438552426E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -3090,24 +3357,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C12" s="10">
-        <v>7.178295390076145</v>
+        <v>7.1950650992045766</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.1782953900761448E-2</v>
+        <v>7.195065099204577E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.1257189854440615</v>
+        <v>-5.2216320699761347</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1257189854440617E-2</v>
+        <v>-5.221632069976135E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3118,1182 +3385,1326 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C13" s="10">
-        <v>5.0098197800339523</v>
+        <v>5.2547784652781599</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.0098197800339521E-2</v>
+        <v>5.25477846527816E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G13" s="10">
-        <v>-5.0593808269021654</v>
+        <v>-4.365073485393987</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0593808269021656E-2</v>
+        <v>-4.3650734853939867E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C14" s="10">
-        <v>4.9893411504096523</v>
+        <v>4.9119947853290071</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.989341150409652E-2</v>
+        <v>4.9119947853290075E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.7845448503728001</v>
+        <v>-4.3408345472357777</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7845448503728003E-2</v>
+        <v>-4.3408345472357779E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C15" s="10">
-        <v>4.8934917789138455</v>
+        <v>4.7918802751980447</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.8934917789138457E-2</v>
+        <v>4.7918802751980447E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.2526844426100716</v>
+        <v>-3.8140152582354738</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2526844426100718E-2</v>
+        <v>-3.8140152582354737E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C16" s="10">
-        <v>4.7956028569605618</v>
+        <v>4.7381546652776985</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.7956028569605617E-2</v>
+        <v>4.7381546652776982E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.7538715318079805</v>
+        <v>-3.6106726835593657</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7538715318079806E-2</v>
+        <v>-3.6106726835593655E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C17" s="10">
-        <v>4.6320517671014345</v>
+        <v>4.3307314974614863</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.6320517671014347E-2</v>
+        <v>4.3307314974614861E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.5028928974400122</v>
+        <v>-3.5520112268146975</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5028928974400124E-2</v>
+        <v>-3.5520112268146976E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C18" s="10">
-        <v>4.1488266383129728</v>
+        <v>4.1460580439357262</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.1488266383129725E-2</v>
+        <v>4.1460580439357263E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.4100075996797381</v>
+        <v>-3.4496143935110948</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4100075996797381E-2</v>
+        <v>-3.4496143935110947E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C19" s="10">
-        <v>3.9941428681304529</v>
+        <v>4.1216441647674635</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.9941428681304528E-2</v>
+        <v>4.1216441647674636E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.2883526862952359</v>
+        <v>-3.4211573857452673</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2883526862952359E-2</v>
+        <v>-3.4211573857452673E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C20" s="10">
-        <v>3.960998571869724</v>
+        <v>4.0422262295122326</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.9609985718697241E-2</v>
+        <v>4.042226229512233E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.2377588228208172</v>
+        <v>-3.0710882033923217</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2377588228208173E-2</v>
+        <v>-3.0710882033923217E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C21" s="10">
-        <v>3.6679107565062949</v>
+        <v>3.5991535325953463</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.667910756506295E-2</v>
+        <v>3.5991535325953464E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.9534394867720826</v>
+        <v>-3.0473678223257492</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9534394867720824E-2</v>
+        <v>-3.0473678223257493E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C22" s="10">
-        <v>3.3901254552592754</v>
+        <v>3.3814452225683911</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.3901254552592755E-2</v>
+        <v>3.3814452225683911E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.8758244405332403</v>
+        <v>-3.0344210290871141</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8758244405332402E-2</v>
+        <v>-3.034421029087114E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C23" s="10">
-        <v>3.3536380206432495</v>
+        <v>3.3235701789410972</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.3536380206432494E-2</v>
+        <v>3.3235701789410974E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.8675313674108578</v>
+        <v>-3.0047060322135644</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8675313674108579E-2</v>
+        <v>-3.0047060322135645E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C24" s="10">
-        <v>3.2000877018935543</v>
+        <v>3.3115135890385243</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.2000877018935545E-2</v>
+        <v>3.3115135890385242E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.5902503120703009</v>
+        <v>-2.846663571898902</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.590250312070301E-2</v>
+        <v>-2.8466635718989018E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C25" s="10">
-        <v>3.1627821872447059</v>
+        <v>3.2683840292570423</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>3.1627821872447059E-2</v>
+        <v>3.2683840292570425E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.5047802005457753</v>
+        <v>-2.5229770882784228</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5047802005457753E-2</v>
+        <v>-2.522977088278423E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C26" s="10">
-        <v>3.0505612112986151</v>
+        <v>3.0222359078790135</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>3.050561211298615E-2</v>
+        <v>3.0222359078790135E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.4719791999441085</v>
+        <v>-2.3856987210331826</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4719791999441087E-2</v>
+        <v>-2.3856987210331825E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C27" s="10">
-        <v>2.9758227955613918</v>
+        <v>2.8705033083184657</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.975822795561392E-2</v>
+        <v>2.8705033083184658E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.4280737722724806</v>
+        <v>-2.3761832582530054</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4280737722724807E-2</v>
+        <v>-2.3761832582530052E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="C28" s="10">
-        <v>2.5627698903959235</v>
+        <v>2.8433870771432437</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.5627698903959235E-2</v>
+        <v>2.8433870771432435E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.209426104135249</v>
+        <v>-2.3540382862818929</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2094261041352491E-2</v>
+        <v>-2.3540382862818929E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C29" s="10">
-        <v>2.5098554346299311</v>
+        <v>2.7046177195658769</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.5098554346299311E-2</v>
+        <v>2.7046177195658768E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.1433936519179007</v>
+        <v>-2.3165984967731266</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1433936519179006E-2</v>
+        <v>-2.3165984967731267E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C30" s="10">
-        <v>2.4321920966956521</v>
+        <v>2.3384310105678714</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.4321920966956522E-2</v>
+        <v>2.3384310105678714E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1271937672668861</v>
+        <v>-2.2906035669978437</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1271937672668863E-2</v>
+        <v>-2.2906035669978439E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C31" s="10">
-        <v>2.2075253833059327</v>
+        <v>2.2703685525546646</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.2075253833059326E-2</v>
+        <v>2.2703685525546646E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0435843613963227</v>
+        <v>-2.2171344338401728</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0435843613963226E-2</v>
+        <v>-2.2171344338401729E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="C32" s="10">
-        <v>2.0981973233901021</v>
+        <v>2.2584248608532977</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.0981973233901021E-2</v>
+        <v>2.2584248608532979E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.0210862608719604</v>
+        <v>-2.0650361555785475</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0210862608719606E-2</v>
+        <v>-2.0650361555785476E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C33" s="10">
-        <v>2.0850481380747117</v>
+        <v>2.2387676595398327</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.0850481380747118E-2</v>
+        <v>2.2387676595398327E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9955531802970969</v>
+        <v>-1.9827602150565788</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.995553180297097E-2</v>
+        <v>-1.9827602150565789E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C34" s="10">
-        <v>2.0104689250012719</v>
+        <v>2.1941851726367463</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.0104689250012721E-2</v>
+        <v>2.1941851726367465E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.9941591425575136</v>
+        <v>-1.9602637021482971</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9941591425575136E-2</v>
+        <v>-1.9602637021482971E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C35" s="10">
-        <v>1.9912055076369131</v>
+        <v>2.1727092295605615</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.9912055076369131E-2</v>
+        <v>2.1727092295605613E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.9119858208758242</v>
+        <v>-1.8487967456276129</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9119858208758243E-2</v>
+        <v>-1.8487967456276129E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C36" s="10">
-        <v>1.9481978272974623</v>
+        <v>2.0087638619867709</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.9481978272974623E-2</v>
+        <v>2.0087638619867711E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.7937745156034437</v>
+        <v>-1.7851622624583465</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7937745156034437E-2</v>
+        <v>-1.7851622624583466E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="C37" s="10">
-        <v>1.7446904333315016</v>
+        <v>1.8923947547785789</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.7446904333315017E-2</v>
+        <v>1.8923947547785789E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.7896264676777158</v>
+        <v>-1.7103975527725646</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7896264676777157E-2</v>
+        <v>-1.7103975527725645E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="C38" s="10">
-        <v>1.6067850405688737</v>
+        <v>1.8376374279430556</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.6067850405688738E-2</v>
+        <v>1.8376374279430556E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.7321728084499362</v>
+        <v>-1.5565238467242555</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.732172808449936E-2</v>
+        <v>-1.5565238467242554E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C39" s="10">
-        <v>1.4968446417390027</v>
+        <v>1.8052287869531423</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.4968446417390027E-2</v>
+        <v>1.8052287869531423E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.6089367918507707</v>
+        <v>-1.546089004395887</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6089367918507708E-2</v>
+        <v>-1.5460890043958871E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C40" s="10">
-        <v>0.98481520791170696</v>
+        <v>1.7885051185863587</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>9.8481520791170694E-3</v>
+        <v>1.7885051185863587E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.494577307054914</v>
+        <v>-1.5430879921263745</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.494577307054914E-2</v>
+        <v>-1.5430879921263746E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C41" s="10">
-        <v>0.94212419763022948</v>
+        <v>1.1734697487598551</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>9.4212419763022946E-3</v>
+        <v>1.1734697487598551E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.4765597546543652</v>
+        <v>-1.4811772286335634</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4765597546543652E-2</v>
+        <v>-1.4811772286335633E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="C42" s="10">
-        <v>0.74655664930348975</v>
+        <v>1.1247678708981241</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>7.4655664930348975E-3</v>
+        <v>1.1247678708981241E-2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.4492896285598154</v>
+        <v>-1.3918029071695248</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4492896285598154E-2</v>
+        <v>-1.3918029071695249E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C43" s="10">
-        <v>0.72041709585217106</v>
+        <v>0.97437978627921507</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>7.204170958521711E-3</v>
+        <v>9.7437978627921504E-3</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.3909880938269175</v>
+        <v>-1.3439701619380315</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.3909880938269175E-2</v>
+        <v>-1.3439701619380316E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C44" s="10">
-        <v>0.6712714794526613</v>
+        <v>0.95525050810167356</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>6.7127147945266127E-3</v>
+        <v>9.5525050810167361E-3</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.3884102113419121</v>
+        <v>-1.3329396474390769</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3884102113419122E-2</v>
+        <v>-1.3329396474390768E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C45" s="10">
-        <v>0.61628335957250424</v>
+        <v>0.86489775821718662</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>6.1628335957250426E-3</v>
+        <v>8.6489775821718667E-3</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.3074682183127213</v>
+        <v>-1.302842523119903</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3074682183127214E-2</v>
+        <v>-1.302842523119903E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C46" s="10">
-        <v>0.54435032429445362</v>
+        <v>0.78258783268582433</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>5.4435032429445366E-3</v>
+        <v>7.8258783268582433E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.3069378013300608</v>
+        <v>-1.2861151014962608</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3069378013300608E-2</v>
+        <v>-1.2861151014962609E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.7564468353401671</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>7.5644683534016712E-3</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1.2512477732885505</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2512477732885505E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.51170005183948308</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="0"/>
+        <v>5.1170005183948306E-3</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-1.245197897856299</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.245197897856299E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C49" s="10">
+        <v>0.4816872103436059</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="0"/>
+        <v>4.816872103436059E-3</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-1.1713001457601533</v>
+      </c>
+      <c r="H49" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.1713001457601534E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="10">
+        <v>0.2768825325933561</v>
+      </c>
+      <c r="D50" s="10">
+        <f t="shared" si="0"/>
+        <v>2.7688253259335609E-3</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G50" s="10">
+        <v>-1.1605663203932066</v>
+      </c>
+      <c r="H50" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.1605663203932066E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="10">
-        <v>0.35372342663835893</v>
-      </c>
-      <c r="D47" s="10">
-        <f t="shared" si="0"/>
-        <v>3.5372342663835894E-3</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G47" s="10">
-        <v>-1.3040521026412208</v>
-      </c>
-      <c r="H47" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.3040521026412209E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="F48" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="G48" s="10">
-        <v>-1.2845994016584155</v>
-      </c>
-      <c r="H48" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.2845994016584155E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="F49" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G49" s="10">
-        <v>-1.2806145811026568</v>
-      </c>
-      <c r="H49" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.2806145811026569E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="F50" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G50" s="10">
-        <v>-1.2733598873867638</v>
-      </c>
-      <c r="H50" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.2733598873867637E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="C51" s="10">
+        <v>0.22678088016471215</v>
+      </c>
+      <c r="D51" s="10">
+        <f t="shared" si="0"/>
+        <v>2.2678088016471216E-3</v>
+      </c>
       <c r="F51" s="11" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G51" s="10">
-        <v>-1.2325645600528132</v>
+        <v>-1.1509750922079443</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2325645600528132E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.1509750922079443E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="9"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
       <c r="F52" s="11" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.98810854320703134</v>
+        <v>-1.0709084280107859</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-9.8810854320703131E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D53" s="1"/>
+        <v>-1.0709084280107859E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.94154124273748196</v>
+        <v>-1.0610580769480413</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4154124273748193E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D54" s="1"/>
+        <v>-1.0610580769480413E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F54" s="11" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.89393254013237</v>
+        <v>-1.0207023736332841</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-8.9393254013236997E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D55" s="1"/>
+        <v>-1.0207023736332841E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F55" s="11" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.85959217876515093</v>
+        <v>-0.98033362007491975</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-8.5959217876515094E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D56" s="1"/>
+        <v>-9.8033362007491978E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F56" s="11" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.83076110098309497</v>
+        <v>-0.9644062055724083</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.3076110098309498E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.6440620557240835E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.82131867111538226</v>
+        <v>-0.92358035363769697</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.2131867111538224E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.2358035363769696E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.79351820000791196</v>
+        <v>-0.91996570803856947</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-7.9351820000791197E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.1996570803856946E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.78645940792387792</v>
+        <v>-0.89122288634373958</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8645940792387795E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.9122288634373957E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.76066545316329681</v>
+        <v>-0.88366122175361306</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.6066545316329677E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.8366122175361304E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.73616695371993224</v>
+        <v>-0.85920520117370169</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.3616695371993227E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.5920520117370169E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.7106220142592159</v>
+        <v>-0.83451957787032593</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.1062201425921593E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.3451957787032596E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.69770510126098817</v>
+        <v>-0.78195496384089247</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9770510126098816E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.819549638408925E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.69122760876568512</v>
+        <v>-0.75481416200005946</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9122760876568516E-3</v>
+        <v>-7.5481416200005947E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.63807820273744953</v>
+        <v>-0.72745198081567264</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.3807820273744957E-3</v>
+        <v>-7.2745198081567266E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.56896397532157073</v>
+        <v>-0.67829021780682441</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-5.6896397532157075E-3</v>
+        <v>-6.7829021780682446E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.41722081673939365</v>
+        <v>-0.6310523461797608</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-4.1722081673939366E-3</v>
+        <v>-6.3105234617976081E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.3938261891657775</v>
+        <v>-0.63061754196957609</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-3.9382618916577747E-3</v>
+        <v>-6.3061754196957606E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.39343732974725998</v>
+        <v>-0.59477531978239451</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-3.9343732974726001E-3</v>
+        <v>-5.9477531978239448E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.37300865403654426</v>
+        <v>-0.56071187298688574</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-3.7300865403654426E-3</v>
+        <v>-5.6071187298688575E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.34174543086615383</v>
+        <v>-0.56007034541067402</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-3.4174543086615385E-3</v>
+        <v>-5.6007034541067403E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.25310390078560174</v>
+        <v>-0.49515880009730046</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-2.5310390078560176E-3</v>
+        <v>-4.9515880009730045E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
       <c r="F73" s="11" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="G73" s="10">
-        <v>-2.7968664389488827E-2</v>
+        <v>-0.48492530203864975</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>-2.7968664389488827E-4</v>
+        <v>-4.8492530203864976E-3</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="13"/>
+      <c r="F74" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-0.46923884125274068</v>
+      </c>
+      <c r="H74" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.6923884125274068E-3</v>
+      </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
+      <c r="F75" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-0.46173053312736234</v>
+      </c>
+      <c r="H75" s="12">
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-4.6173053312736235E-3</v>
+      </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
+      <c r="F76" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-0.44554891075458514</v>
+      </c>
+      <c r="H76" s="12">
+        <f t="shared" si="3"/>
+        <v>-4.4554891075458515E-3</v>
+      </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
-      <c r="G77" t="s">
-        <v>5</v>
+      <c r="F77" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-0.35606298251969726</v>
+      </c>
+      <c r="H77" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.5606298251969724E-3</v>
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
+      <c r="F78" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-0.34449675752917985</v>
+      </c>
+      <c r="H78" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.4449675752917987E-3</v>
+      </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
-      <c r="H79" s="1"/>
+      <c r="F79" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-0.27875728165155722</v>
+      </c>
+      <c r="H79" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.787572816515572E-3</v>
+      </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
-      <c r="H80" s="1"/>
+      <c r="F80" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-0.24921887088681788</v>
+      </c>
+      <c r="H80" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.4921887088681788E-3</v>
+      </c>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
+      <c r="F81" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G81" s="10">
+        <v>-0.23320955251166742</v>
+      </c>
+      <c r="H81" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.3320955251166743E-3</v>
+      </c>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
+      <c r="F82" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="G82" s="10">
+        <v>-0.23178456106778422</v>
+      </c>
+      <c r="H82" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.3178456106778423E-3</v>
+      </c>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
+      <c r="F83" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" s="10">
+        <v>-0.23062227374651528</v>
+      </c>
+      <c r="H83" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.3062227374651529E-3</v>
+      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="H84" s="1"/>
+      <c r="F84" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-0.2198304019835241</v>
+      </c>
+      <c r="H84" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.198304019835241E-3</v>
+      </c>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
-      <c r="H85" s="1"/>
+      <c r="F85" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" s="10">
+        <v>-0.17906361599513917</v>
+      </c>
+      <c r="H85" s="12">
+        <f t="shared" si="3"/>
+        <v>-1.7906361599513917E-3</v>
+      </c>
     </row>
     <row r="86" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D86" s="1"/>
-      <c r="H86" s="1"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="13"/>
     </row>
     <row r="87" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D87" s="1"/>
-      <c r="H87" s="1"/>
     </row>
     <row r="88" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D88" s="1"/>
-      <c r="H88" s="1"/>
     </row>
     <row r="89" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
-      <c r="H89" s="1"/>
+      <c r="G89" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="90" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
-      <c r="H90" s="1"/>
     </row>
     <row r="91" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
@@ -4639,52 +5050,56 @@
       <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -4713,6 +5128,42 @@
     </row>
     <row r="201" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="1"/>
+    </row>
+    <row r="208" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H208" s="1"/>
+    </row>
+    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H209" s="1"/>
+    </row>
+    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H210" s="1"/>
+    </row>
+    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H211" s="1"/>
+    </row>
+    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H212" s="1"/>
+    </row>
+    <row r="213" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H213" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAA3B71C-6C9E-2849-99DA-1638F5A4A96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C15AEC2-F406-1446-9754-79E95F1F8E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C15AEC2-F406-1446-9754-79E95F1F8E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4585D-9012-644E-8B8B-1131810FA6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issuer" sheetId="1" r:id="rId1"/>
-    <sheet name="Instrument" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="123">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -78,21 +77,6 @@
     <t>Manticore Master Fund</t>
   </si>
   <si>
-    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
-  </si>
-  <si>
-    <t>APPLIED OPTOELECTRONICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>Instrument</t>
-  </si>
-  <si>
-    <t>FAIR ISAAC ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
-  </si>
-  <si>
     <t>LAMR</t>
   </si>
   <si>
@@ -421,342 +405,6 @@
   </si>
   <si>
     <t>P</t>
-  </si>
-  <si>
-    <t>CINTAS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
-  </si>
-  <si>
-    <t>AUTODESK ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CANON ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>VERISK ANALYTICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>APPLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SAMSARA CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PINTEREST CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EXPEDIA GROUP ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NEW YORK TIMES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LOGITECH N ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
-    <t>RHEINMETALL ORD (GER)</t>
-  </si>
-  <si>
-    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>EQUIFAX ORD (NYS)</t>
-  </si>
-  <si>
-    <t>WILLIAMS SONOMA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>REA GROUP ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NVIDIA ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NICE ADR REP 1 ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TELUS ORD (TOR)</t>
-  </si>
-  <si>
-    <t>QUALYS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>REDDIT CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
-  </si>
-  <si>
-    <t>EBAY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GARTNER ORD (NYS)</t>
-  </si>
-  <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ARISTA NETWORKS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBERT HALF ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SEZZLE INC (NMS)</t>
-  </si>
-  <si>
-    <t>CARGURUS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>COINBASE GLOBAL CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SYMBOTIC CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>BCE ORD (TOR)</t>
-  </si>
-  <si>
-    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
-  </si>
-  <si>
-    <t>ADOBE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WISETECH GLOBAL ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
-  </si>
-  <si>
-    <t>CBOE GLOBAL MARKETS ORD (BAT)</t>
-  </si>
-  <si>
-    <t>WSP GLOBAL ORD (TOR)</t>
-  </si>
-  <si>
-    <t>CIENA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DATADOG CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NEBIUS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>COREWEAVE CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>STANTEC ORD (TOR)</t>
-  </si>
-  <si>
-    <t>CONCENTRIX ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LUMENTUM HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SITIME ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NOKIA ADR REPSG 1 SER A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>BLOCK CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>AT&amp;T ORD (NYS)</t>
-  </si>
-  <si>
-    <t>AMAZON COM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ALPHABET CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WAYFAIR CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EATON ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>AUTO1 GROUP ORD (GER)</t>
-  </si>
-  <si>
-    <t>PANASONIC HLDG ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>LYFT CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>IRON MOUNTAIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBLOX CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SK HYNIX ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>TRIMBLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DRAFTKINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
-  </si>
-  <si>
-    <t>APPLOVIN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>MAPLEBEAR ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (MIL)</t>
-  </si>
-  <si>
-    <t>STMICROELECTRONICS ADR (NYS)</t>
-  </si>
-  <si>
-    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
-  </si>
-  <si>
-    <t>SAP ORD (GER)</t>
-  </si>
-  <si>
-    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>BILL HOLDINGS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NXP SEMICONDUCTORS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>COMCAST CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NETAPP ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SANDISK ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CLOUDFLARE CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>META US 01/15/27 P620 OTC (META 1/15/27 P620 OTC)</t>
-  </si>
-  <si>
-    <t>EVERPURE CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LIONSGATE STUDIOS ORD (NYS)</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1028,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C11" s="10">
         <v>10.64005596812768</v>
@@ -1418,7 +1066,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C12" s="10">
         <v>7.1950650992045766</v>
@@ -1428,7 +1076,7 @@
         <v>7.195065099204577E-2</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G12" s="10">
         <v>-5.2216320699761347</v>
@@ -1446,7 +1094,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C13" s="10">
         <v>5.2547784652781599</v>
@@ -1456,7 +1104,7 @@
         <v>5.25477846527816E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G13" s="10">
         <v>-4.365073485393987</v>
@@ -1469,7 +1117,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C14" s="10">
         <v>4.9119947853290071</v>
@@ -1479,7 +1127,7 @@
         <v>4.9119947853290075E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G14" s="10">
         <v>-4.3408345472357777</v>
@@ -1492,7 +1140,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C15" s="10">
         <v>4.879267170305237</v>
@@ -1502,7 +1150,7 @@
         <v>4.8792671703052369E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G15" s="10">
         <v>-3.8140152582354738</v>
@@ -1515,7 +1163,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C16" s="10">
         <v>4.7918802751980447</v>
@@ -1525,7 +1173,7 @@
         <v>4.7918802751980447E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G16" s="10">
         <v>-3.6106726835593657</v>
@@ -1538,7 +1186,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C17" s="10">
         <v>4.7381546652776985</v>
@@ -1548,7 +1196,7 @@
         <v>4.7381546652776982E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G17" s="10">
         <v>-3.5520112268146975</v>
@@ -1560,7 +1208,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C18" s="10">
         <v>4.3307314974614863</v>
@@ -1570,7 +1218,7 @@
         <v>4.3307314974614861E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G18" s="10">
         <v>-3.4496143935110948</v>
@@ -1582,7 +1230,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C19" s="10">
         <v>4.1460580439357262</v>
@@ -1592,7 +1240,7 @@
         <v>4.1460580439357263E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G19" s="10">
         <v>-3.4211573857452673</v>
@@ -1604,7 +1252,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C20" s="10">
         <v>4.1216441647674635</v>
@@ -1614,7 +1262,7 @@
         <v>4.1216441647674636E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G20" s="10">
         <v>-3.0710882033923217</v>
@@ -1626,7 +1274,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C21" s="10">
         <v>4.0422262295122326</v>
@@ -1636,7 +1284,7 @@
         <v>4.042226229512233E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G21" s="10">
         <v>-3.0473678223257492</v>
@@ -1648,7 +1296,7 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C22" s="10">
         <v>3.5991535325953463</v>
@@ -1658,7 +1306,7 @@
         <v>3.5991535325953464E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G22" s="10">
         <v>-3.0344210290871141</v>
@@ -1670,7 +1318,7 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C23" s="10">
         <v>3.3814452225683911</v>
@@ -1680,7 +1328,7 @@
         <v>3.3814452225683911E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G23" s="10">
         <v>-3.0047060322135644</v>
@@ -1692,7 +1340,7 @@
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C24" s="10">
         <v>3.3235701789410972</v>
@@ -1702,7 +1350,7 @@
         <v>3.3235701789410974E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G24" s="10">
         <v>-2.846663571898902</v>
@@ -1714,7 +1362,7 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C25" s="10">
         <v>3.3115135890385243</v>
@@ -1724,7 +1372,7 @@
         <v>3.3115135890385242E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G25" s="10">
         <v>-2.5229770882784228</v>
@@ -1736,7 +1384,7 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C26" s="10">
         <v>3.2683840292570423</v>
@@ -1746,7 +1394,7 @@
         <v>3.2683840292570425E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G26" s="10">
         <v>-2.3856987210331826</v>
@@ -1758,7 +1406,7 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C27" s="10">
         <v>3.0222359078790135</v>
@@ -1768,7 +1416,7 @@
         <v>3.0222359078790135E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G27" s="10">
         <v>-2.3761832582530054</v>
@@ -1780,7 +1428,7 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C28" s="10">
         <v>2.8433870771432437</v>
@@ -1790,7 +1438,7 @@
         <v>2.8433870771432435E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G28" s="10">
         <v>-2.3540382862818929</v>
@@ -1802,7 +1450,7 @@
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C29" s="10">
         <v>2.7046177195658769</v>
@@ -1812,7 +1460,7 @@
         <v>2.7046177195658768E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G29" s="10">
         <v>-2.3165984967731266</v>
@@ -1824,7 +1472,7 @@
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C30" s="10">
         <v>2.3384310105678714</v>
@@ -1834,7 +1482,7 @@
         <v>2.3384310105678714E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G30" s="10">
         <v>-2.2906035669978437</v>
@@ -1846,7 +1494,7 @@
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C31" s="10">
         <v>2.2703685525546646</v>
@@ -1856,7 +1504,7 @@
         <v>2.2703685525546646E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G31" s="10">
         <v>-2.2171344338401728</v>
@@ -1868,7 +1516,7 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C32" s="10">
         <v>2.2584248608532977</v>
@@ -1878,7 +1526,7 @@
         <v>2.2584248608532979E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G32" s="10">
         <v>-2.0650361555785475</v>
@@ -1890,7 +1538,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C33" s="10">
         <v>2.2387676595398327</v>
@@ -1900,7 +1548,7 @@
         <v>2.2387676595398327E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G33" s="10">
         <v>-1.9827602150565788</v>
@@ -1912,7 +1560,7 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C34" s="10">
         <v>2.1941851726367463</v>
@@ -1922,7 +1570,7 @@
         <v>2.1941851726367465E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G34" s="10">
         <v>-1.9602637021482971</v>
@@ -1934,7 +1582,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C35" s="10">
         <v>2.1727092295605615</v>
@@ -1944,7 +1592,7 @@
         <v>2.1727092295605613E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G35" s="10">
         <v>-1.8487967456276129</v>
@@ -1956,7 +1604,7 @@
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C36" s="10">
         <v>1.8923947547785789</v>
@@ -1966,7 +1614,7 @@
         <v>1.8923947547785789E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G36" s="10">
         <v>-1.7851622624583465</v>
@@ -1978,7 +1626,7 @@
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C37" s="10">
         <v>1.8376374279430556</v>
@@ -1988,7 +1636,7 @@
         <v>1.8376374279430556E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G37" s="10">
         <v>-1.7103975527725646</v>
@@ -2000,7 +1648,7 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C38" s="10">
         <v>1.8052287869531423</v>
@@ -2010,7 +1658,7 @@
         <v>1.8052287869531423E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G38" s="10">
         <v>-1.5565238467242555</v>
@@ -2022,7 +1670,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C39" s="10">
         <v>1.7885051185863587</v>
@@ -2032,7 +1680,7 @@
         <v>1.7885051185863587E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G39" s="10">
         <v>-1.546089004395887</v>
@@ -2044,7 +1692,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C40" s="10">
         <v>1.1734697487598551</v>
@@ -2054,7 +1702,7 @@
         <v>1.1734697487598551E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G40" s="10">
         <v>-1.5430879921263745</v>
@@ -2066,7 +1714,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C41" s="10">
         <v>1.1247678708981241</v>
@@ -2076,7 +1724,7 @@
         <v>1.1247678708981241E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G41" s="10">
         <v>-1.4811772286335634</v>
@@ -2088,7 +1736,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C42" s="10">
         <v>0.97437978627921507</v>
@@ -2098,7 +1746,7 @@
         <v>9.7437978627921504E-3</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G42" s="10">
         <v>-1.3918029071695248</v>
@@ -2110,7 +1758,7 @@
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C43" s="10">
         <v>0.95525050810167356</v>
@@ -2120,7 +1768,7 @@
         <v>9.5525050810167361E-3</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G43" s="10">
         <v>-1.3439701619380315</v>
@@ -2132,7 +1780,7 @@
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C44" s="10">
         <v>0.86489775821718662</v>
@@ -2142,7 +1790,7 @@
         <v>8.6489775821718667E-3</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G44" s="10">
         <v>-1.3329396474390769</v>
@@ -2154,7 +1802,7 @@
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C45" s="10">
         <v>0.78258783268582433</v>
@@ -2164,7 +1812,7 @@
         <v>7.8258783268582433E-3</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G45" s="10">
         <v>-1.302842523119903</v>
@@ -2176,7 +1824,7 @@
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C46" s="10">
         <v>0.7564468353401671</v>
@@ -2186,7 +1834,7 @@
         <v>7.5644683534016712E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G46" s="10">
         <v>-1.2861151014962608</v>
@@ -2198,7 +1846,7 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C47" s="10">
         <v>0.4816872103436059</v>
@@ -2208,7 +1856,7 @@
         <v>4.816872103436059E-3</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G47" s="10">
         <v>-1.2512477732885505</v>
@@ -2230,7 +1878,7 @@
         <v>2.7688253259335609E-3</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G48" s="10">
         <v>-1.245197897856299</v>
@@ -2245,7 +1893,7 @@
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
       <c r="F49" s="11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G49" s="10">
         <v>-1.1713001457601533</v>
@@ -2257,7 +1905,7 @@
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F50" s="11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G50" s="10">
         <v>-1.1605663203932066</v>
@@ -2269,7 +1917,7 @@
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F51" s="11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G51" s="10">
         <v>-1.1509750922079443</v>
@@ -2281,7 +1929,7 @@
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G52" s="10">
         <v>-1.0709084280107859</v>
@@ -2293,7 +1941,7 @@
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G53" s="10">
         <v>-1.0610580769480413</v>
@@ -2306,7 +1954,7 @@
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D54" s="1"/>
       <c r="F54" s="11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G54" s="10">
         <v>-1.0207023736332841</v>
@@ -2319,7 +1967,7 @@
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G55" s="10">
         <v>-0.98033362007491975</v>
@@ -2332,7 +1980,7 @@
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G56" s="10">
         <v>-0.9644062055724083</v>
@@ -2345,7 +1993,7 @@
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G57" s="10">
         <v>-0.92358035363769697</v>
@@ -2358,7 +2006,7 @@
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G58" s="10">
         <v>-0.91996570803856947</v>
@@ -2371,7 +2019,7 @@
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G59" s="10">
         <v>-0.89122288634373958</v>
@@ -2384,7 +2032,7 @@
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G60" s="10">
         <v>-0.88366122175361306</v>
@@ -2397,7 +2045,7 @@
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G61" s="10">
         <v>-0.85920520117370169</v>
@@ -2410,7 +2058,7 @@
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G62" s="10">
         <v>-0.83451957787032593</v>
@@ -2423,7 +2071,7 @@
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G63" s="10">
         <v>-0.78195496384089247</v>
@@ -2436,7 +2084,7 @@
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G64" s="10">
         <v>-0.75481416200005946</v>
@@ -2449,7 +2097,7 @@
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G65" s="10">
         <v>-0.67829021780682441</v>
@@ -2462,7 +2110,7 @@
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G66" s="10">
         <v>-0.6310523461797608</v>
@@ -2475,7 +2123,7 @@
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G67" s="10">
         <v>-0.63061754196957609</v>
@@ -2488,7 +2136,7 @@
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G68" s="10">
         <v>-0.56071187298688574</v>
@@ -2501,7 +2149,7 @@
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G69" s="10">
         <v>-0.56007034541067402</v>
@@ -2514,7 +2162,7 @@
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G70" s="10">
         <v>-0.49515880009730046</v>
@@ -2527,7 +2175,7 @@
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G71" s="10">
         <v>-0.48492530203864975</v>
@@ -2540,7 +2188,7 @@
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G72" s="10">
         <v>-0.46923884125274068</v>
@@ -2553,7 +2201,7 @@
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
       <c r="F73" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G73" s="10">
         <v>-0.46173053312736234</v>
@@ -2566,7 +2214,7 @@
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
       <c r="F74" s="11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G74" s="10">
         <v>-0.44554891075458514</v>
@@ -2579,20 +2227,20 @@
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
       <c r="F75" s="11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G75" s="10">
         <v>-0.3679944396176823</v>
       </c>
       <c r="H75" s="12">
-        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <f t="shared" ref="H75:H85" si="3">IF(F75="","",G75/100)</f>
         <v>-3.6799443961768232E-3</v>
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
       <c r="F76" s="11" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G76" s="10">
         <v>-0.35606298251969726</v>
@@ -2605,7 +2253,7 @@
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
       <c r="F77" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G77" s="10">
         <v>-0.34449675752917985</v>
@@ -2618,7 +2266,7 @@
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
       <c r="F78" s="11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G78" s="10">
         <v>-0.27875728165155722</v>
@@ -2631,7 +2279,7 @@
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
       <c r="F79" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G79" s="10">
         <v>-0.24921887088681788</v>
@@ -2644,7 +2292,7 @@
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
       <c r="F80" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G80" s="10">
         <v>-0.23320955251166742</v>
@@ -2657,7 +2305,7 @@
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
       <c r="F81" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G81" s="10">
         <v>-0.23178456106778422</v>
@@ -2670,7 +2318,7 @@
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
       <c r="F82" s="11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G82" s="10">
         <v>-0.23062227374651528</v>
@@ -2683,7 +2331,7 @@
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
       <c r="F83" s="11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G83" s="10">
         <v>-0.2198304019835241</v>
@@ -2696,7 +2344,7 @@
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
       <c r="F84" s="11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G84" s="10">
         <v>-0.21575192897618961</v>
@@ -3200,1976 +2848,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q213"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="28.5" customWidth="1"/>
-    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.5" customWidth="1"/>
-    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.5" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.5" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="8"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="10">
-        <v>10.64005596812768</v>
-      </c>
-      <c r="D11" s="10">
-        <f t="shared" ref="D11:D51" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10640055968127679</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="10">
-        <v>-6.4259951438552427</v>
-      </c>
-      <c r="H11" s="12">
-        <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-6.4259951438552426E-2</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="10" t="str">
-        <f>IF(L11="","",L11/100)</f>
-        <v/>
-      </c>
-      <c r="O11" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="12" t="str">
-        <f>IF(P11="","",P11/100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B12" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" s="10">
-        <v>7.1950650992045766</v>
-      </c>
-      <c r="D12" s="10">
-        <f t="shared" si="0"/>
-        <v>7.195065099204577E-2</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="10">
-        <v>-5.2216320699761347</v>
-      </c>
-      <c r="H12" s="12">
-        <f t="shared" si="1"/>
-        <v>-5.221632069976135E-2</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="13"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5.2547784652781599</v>
-      </c>
-      <c r="D13" s="10">
-        <f t="shared" si="0"/>
-        <v>5.25477846527816E-2</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="10">
-        <v>-4.365073485393987</v>
-      </c>
-      <c r="H13" s="12">
-        <f t="shared" si="1"/>
-        <v>-4.3650734853939867E-2</v>
-      </c>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="10">
-        <v>4.9119947853290071</v>
-      </c>
-      <c r="D14" s="10">
-        <f t="shared" si="0"/>
-        <v>4.9119947853290075E-2</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="G14" s="10">
-        <v>-4.3408345472357777</v>
-      </c>
-      <c r="H14" s="12">
-        <f t="shared" si="1"/>
-        <v>-4.3408345472357779E-2</v>
-      </c>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="10">
-        <v>4.7918802751980447</v>
-      </c>
-      <c r="D15" s="10">
-        <f t="shared" si="0"/>
-        <v>4.7918802751980447E-2</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" s="10">
-        <v>-3.8140152582354738</v>
-      </c>
-      <c r="H15" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.8140152582354737E-2</v>
-      </c>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C16" s="10">
-        <v>4.7381546652776985</v>
-      </c>
-      <c r="D16" s="10">
-        <f t="shared" si="0"/>
-        <v>4.7381546652776982E-2</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="10">
-        <v>-3.6106726835593657</v>
-      </c>
-      <c r="H16" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.6106726835593655E-2</v>
-      </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C17" s="10">
-        <v>4.3307314974614863</v>
-      </c>
-      <c r="D17" s="10">
-        <f t="shared" si="0"/>
-        <v>4.3307314974614861E-2</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="10">
-        <v>-3.5520112268146975</v>
-      </c>
-      <c r="H17" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.5520112268146976E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C18" s="10">
-        <v>4.1460580439357262</v>
-      </c>
-      <c r="D18" s="10">
-        <f t="shared" si="0"/>
-        <v>4.1460580439357263E-2</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="10">
-        <v>-3.4496143935110948</v>
-      </c>
-      <c r="H18" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.4496143935110947E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B19" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="10">
-        <v>4.1216441647674635</v>
-      </c>
-      <c r="D19" s="10">
-        <f t="shared" si="0"/>
-        <v>4.1216441647674636E-2</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19" s="10">
-        <v>-3.4211573857452673</v>
-      </c>
-      <c r="H19" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.4211573857452673E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C20" s="10">
-        <v>4.0422262295122326</v>
-      </c>
-      <c r="D20" s="10">
-        <f t="shared" si="0"/>
-        <v>4.042226229512233E-2</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="10">
-        <v>-3.0710882033923217</v>
-      </c>
-      <c r="H20" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.0710882033923217E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C21" s="10">
-        <v>3.5991535325953463</v>
-      </c>
-      <c r="D21" s="10">
-        <f t="shared" si="0"/>
-        <v>3.5991535325953464E-2</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="10">
-        <v>-3.0473678223257492</v>
-      </c>
-      <c r="H21" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.0473678223257493E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C22" s="10">
-        <v>3.3814452225683911</v>
-      </c>
-      <c r="D22" s="10">
-        <f t="shared" si="0"/>
-        <v>3.3814452225683911E-2</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" s="10">
-        <v>-3.0344210290871141</v>
-      </c>
-      <c r="H22" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.034421029087114E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C23" s="10">
-        <v>3.3235701789410972</v>
-      </c>
-      <c r="D23" s="10">
-        <f t="shared" si="0"/>
-        <v>3.3235701789410974E-2</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="10">
-        <v>-3.0047060322135644</v>
-      </c>
-      <c r="H23" s="12">
-        <f t="shared" si="1"/>
-        <v>-3.0047060322135645E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="C24" s="10">
-        <v>3.3115135890385243</v>
-      </c>
-      <c r="D24" s="10">
-        <f t="shared" si="0"/>
-        <v>3.3115135890385242E-2</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="G24" s="10">
-        <v>-2.846663571898902</v>
-      </c>
-      <c r="H24" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.8466635718989018E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C25" s="10">
-        <v>3.2683840292570423</v>
-      </c>
-      <c r="D25" s="10">
-        <f t="shared" si="0"/>
-        <v>3.2683840292570425E-2</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G25" s="10">
-        <v>-2.5229770882784228</v>
-      </c>
-      <c r="H25" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.522977088278423E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C26" s="10">
-        <v>3.0222359078790135</v>
-      </c>
-      <c r="D26" s="10">
-        <f t="shared" si="0"/>
-        <v>3.0222359078790135E-2</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="G26" s="10">
-        <v>-2.3856987210331826</v>
-      </c>
-      <c r="H26" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.3856987210331825E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" s="10">
-        <v>2.8705033083184657</v>
-      </c>
-      <c r="D27" s="10">
-        <f t="shared" si="0"/>
-        <v>2.8705033083184658E-2</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" s="10">
-        <v>-2.3761832582530054</v>
-      </c>
-      <c r="H27" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.3761832582530052E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B28" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C28" s="10">
-        <v>2.8433870771432437</v>
-      </c>
-      <c r="D28" s="10">
-        <f t="shared" si="0"/>
-        <v>2.8433870771432435E-2</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="G28" s="10">
-        <v>-2.3540382862818929</v>
-      </c>
-      <c r="H28" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.3540382862818929E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="C29" s="10">
-        <v>2.7046177195658769</v>
-      </c>
-      <c r="D29" s="10">
-        <f t="shared" si="0"/>
-        <v>2.7046177195658768E-2</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G29" s="10">
-        <v>-2.3165984967731266</v>
-      </c>
-      <c r="H29" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.3165984967731267E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C30" s="10">
-        <v>2.3384310105678714</v>
-      </c>
-      <c r="D30" s="10">
-        <f t="shared" si="0"/>
-        <v>2.3384310105678714E-2</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G30" s="10">
-        <v>-2.2906035669978437</v>
-      </c>
-      <c r="H30" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.2906035669978439E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="C31" s="10">
-        <v>2.2703685525546646</v>
-      </c>
-      <c r="D31" s="10">
-        <f t="shared" si="0"/>
-        <v>2.2703685525546646E-2</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G31" s="10">
-        <v>-2.2171344338401728</v>
-      </c>
-      <c r="H31" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.2171344338401729E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C32" s="10">
-        <v>2.2584248608532977</v>
-      </c>
-      <c r="D32" s="10">
-        <f t="shared" si="0"/>
-        <v>2.2584248608532979E-2</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G32" s="10">
-        <v>-2.0650361555785475</v>
-      </c>
-      <c r="H32" s="12">
-        <f t="shared" si="1"/>
-        <v>-2.0650361555785476E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33" s="10">
-        <v>2.2387676595398327</v>
-      </c>
-      <c r="D33" s="10">
-        <f t="shared" si="0"/>
-        <v>2.2387676595398327E-2</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="G33" s="10">
-        <v>-1.9827602150565788</v>
-      </c>
-      <c r="H33" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.9827602150565789E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C34" s="10">
-        <v>2.1941851726367463</v>
-      </c>
-      <c r="D34" s="10">
-        <f t="shared" si="0"/>
-        <v>2.1941851726367465E-2</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G34" s="10">
-        <v>-1.9602637021482971</v>
-      </c>
-      <c r="H34" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.9602637021482971E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C35" s="10">
-        <v>2.1727092295605615</v>
-      </c>
-      <c r="D35" s="10">
-        <f t="shared" si="0"/>
-        <v>2.1727092295605613E-2</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35" s="10">
-        <v>-1.8487967456276129</v>
-      </c>
-      <c r="H35" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.8487967456276129E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C36" s="10">
-        <v>2.0087638619867709</v>
-      </c>
-      <c r="D36" s="10">
-        <f t="shared" si="0"/>
-        <v>2.0087638619867711E-2</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G36" s="10">
-        <v>-1.7851622624583465</v>
-      </c>
-      <c r="H36" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.7851622624583466E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C37" s="10">
-        <v>1.8923947547785789</v>
-      </c>
-      <c r="D37" s="10">
-        <f t="shared" si="0"/>
-        <v>1.8923947547785789E-2</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="G37" s="10">
-        <v>-1.7103975527725646</v>
-      </c>
-      <c r="H37" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.7103975527725645E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C38" s="10">
-        <v>1.8376374279430556</v>
-      </c>
-      <c r="D38" s="10">
-        <f t="shared" si="0"/>
-        <v>1.8376374279430556E-2</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="G38" s="10">
-        <v>-1.5565238467242555</v>
-      </c>
-      <c r="H38" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.5565238467242554E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B39" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C39" s="10">
-        <v>1.8052287869531423</v>
-      </c>
-      <c r="D39" s="10">
-        <f t="shared" si="0"/>
-        <v>1.8052287869531423E-2</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G39" s="10">
-        <v>-1.546089004395887</v>
-      </c>
-      <c r="H39" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.5460890043958871E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="C40" s="10">
-        <v>1.7885051185863587</v>
-      </c>
-      <c r="D40" s="10">
-        <f t="shared" si="0"/>
-        <v>1.7885051185863587E-2</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="G40" s="10">
-        <v>-1.5430879921263745</v>
-      </c>
-      <c r="H40" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.5430879921263746E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B41" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C41" s="10">
-        <v>1.1734697487598551</v>
-      </c>
-      <c r="D41" s="10">
-        <f t="shared" si="0"/>
-        <v>1.1734697487598551E-2</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="G41" s="10">
-        <v>-1.4811772286335634</v>
-      </c>
-      <c r="H41" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.4811772286335633E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C42" s="10">
-        <v>1.1247678708981241</v>
-      </c>
-      <c r="D42" s="10">
-        <f t="shared" si="0"/>
-        <v>1.1247678708981241E-2</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="G42" s="10">
-        <v>-1.3918029071695248</v>
-      </c>
-      <c r="H42" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.3918029071695249E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="10">
-        <v>0.97437978627921507</v>
-      </c>
-      <c r="D43" s="10">
-        <f t="shared" si="0"/>
-        <v>9.7437978627921504E-3</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="G43" s="10">
-        <v>-1.3439701619380315</v>
-      </c>
-      <c r="H43" s="12">
-        <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.3439701619380316E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C44" s="10">
-        <v>0.95525050810167356</v>
-      </c>
-      <c r="D44" s="10">
-        <f t="shared" si="0"/>
-        <v>9.5525050810167361E-3</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="G44" s="10">
-        <v>-1.3329396474390769</v>
-      </c>
-      <c r="H44" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.3329396474390768E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C45" s="10">
-        <v>0.86489775821718662</v>
-      </c>
-      <c r="D45" s="10">
-        <f t="shared" si="0"/>
-        <v>8.6489775821718667E-3</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="G45" s="10">
-        <v>-1.302842523119903</v>
-      </c>
-      <c r="H45" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.302842523119903E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C46" s="10">
-        <v>0.78258783268582433</v>
-      </c>
-      <c r="D46" s="10">
-        <f t="shared" si="0"/>
-        <v>7.8258783268582433E-3</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="G46" s="10">
-        <v>-1.2861151014962608</v>
-      </c>
-      <c r="H46" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.2861151014962609E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="10">
-        <v>0.7564468353401671</v>
-      </c>
-      <c r="D47" s="10">
-        <f t="shared" si="0"/>
-        <v>7.5644683534016712E-3</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G47" s="10">
-        <v>-1.2512477732885505</v>
-      </c>
-      <c r="H47" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.2512477732885505E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="C48" s="10">
-        <v>0.51170005183948308</v>
-      </c>
-      <c r="D48" s="10">
-        <f t="shared" si="0"/>
-        <v>5.1170005183948306E-3</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G48" s="10">
-        <v>-1.245197897856299</v>
-      </c>
-      <c r="H48" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.245197897856299E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C49" s="10">
-        <v>0.4816872103436059</v>
-      </c>
-      <c r="D49" s="10">
-        <f t="shared" si="0"/>
-        <v>4.816872103436059E-3</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="G49" s="10">
-        <v>-1.1713001457601533</v>
-      </c>
-      <c r="H49" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.1713001457601534E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="10">
-        <v>0.2768825325933561</v>
-      </c>
-      <c r="D50" s="10">
-        <f t="shared" si="0"/>
-        <v>2.7688253259335609E-3</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="G50" s="10">
-        <v>-1.1605663203932066</v>
-      </c>
-      <c r="H50" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.1605663203932066E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="10">
-        <v>0.22678088016471215</v>
-      </c>
-      <c r="D51" s="10">
-        <f t="shared" si="0"/>
-        <v>2.2678088016471216E-3</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G51" s="10">
-        <v>-1.1509750922079443</v>
-      </c>
-      <c r="H51" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.1509750922079443E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="9"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="F52" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G52" s="10">
-        <v>-1.0709084280107859</v>
-      </c>
-      <c r="H52" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.0709084280107859E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F53" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="G53" s="10">
-        <v>-1.0610580769480413</v>
-      </c>
-      <c r="H53" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.0610580769480413E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F54" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="G54" s="10">
-        <v>-1.0207023736332841</v>
-      </c>
-      <c r="H54" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.0207023736332841E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F55" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G55" s="10">
-        <v>-0.98033362007491975</v>
-      </c>
-      <c r="H55" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.8033362007491978E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F56" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="G56" s="10">
-        <v>-0.9644062055724083</v>
-      </c>
-      <c r="H56" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.6440620557240835E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D57" s="1"/>
-      <c r="F57" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G57" s="10">
-        <v>-0.92358035363769697</v>
-      </c>
-      <c r="H57" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.2358035363769696E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D58" s="1"/>
-      <c r="F58" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="G58" s="10">
-        <v>-0.91996570803856947</v>
-      </c>
-      <c r="H58" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.1996570803856946E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D59" s="1"/>
-      <c r="F59" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="G59" s="10">
-        <v>-0.89122288634373958</v>
-      </c>
-      <c r="H59" s="12">
-        <f t="shared" si="2"/>
-        <v>-8.9122288634373957E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D60" s="1"/>
-      <c r="F60" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="G60" s="10">
-        <v>-0.88366122175361306</v>
-      </c>
-      <c r="H60" s="12">
-        <f t="shared" si="2"/>
-        <v>-8.8366122175361304E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D61" s="1"/>
-      <c r="F61" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="G61" s="10">
-        <v>-0.85920520117370169</v>
-      </c>
-      <c r="H61" s="12">
-        <f t="shared" si="2"/>
-        <v>-8.5920520117370169E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D62" s="1"/>
-      <c r="F62" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="G62" s="10">
-        <v>-0.83451957787032593</v>
-      </c>
-      <c r="H62" s="12">
-        <f t="shared" si="2"/>
-        <v>-8.3451957787032596E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D63" s="1"/>
-      <c r="F63" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G63" s="10">
-        <v>-0.78195496384089247</v>
-      </c>
-      <c r="H63" s="12">
-        <f t="shared" si="2"/>
-        <v>-7.819549638408925E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D64" s="1"/>
-      <c r="F64" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="G64" s="10">
-        <v>-0.75481416200005946</v>
-      </c>
-      <c r="H64" s="12">
-        <f t="shared" si="2"/>
-        <v>-7.5481416200005947E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D65" s="1"/>
-      <c r="F65" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="G65" s="10">
-        <v>-0.72745198081567264</v>
-      </c>
-      <c r="H65" s="12">
-        <f t="shared" si="2"/>
-        <v>-7.2745198081567266E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D66" s="1"/>
-      <c r="F66" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="G66" s="10">
-        <v>-0.67829021780682441</v>
-      </c>
-      <c r="H66" s="12">
-        <f t="shared" si="2"/>
-        <v>-6.7829021780682446E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D67" s="1"/>
-      <c r="F67" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G67" s="10">
-        <v>-0.6310523461797608</v>
-      </c>
-      <c r="H67" s="12">
-        <f t="shared" si="2"/>
-        <v>-6.3105234617976081E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D68" s="1"/>
-      <c r="F68" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="G68" s="10">
-        <v>-0.63061754196957609</v>
-      </c>
-      <c r="H68" s="12">
-        <f t="shared" si="2"/>
-        <v>-6.3061754196957606E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D69" s="1"/>
-      <c r="F69" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="G69" s="10">
-        <v>-0.59477531978239451</v>
-      </c>
-      <c r="H69" s="12">
-        <f t="shared" si="2"/>
-        <v>-5.9477531978239448E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D70" s="1"/>
-      <c r="F70" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="G70" s="10">
-        <v>-0.56071187298688574</v>
-      </c>
-      <c r="H70" s="12">
-        <f t="shared" si="2"/>
-        <v>-5.6071187298688575E-3</v>
-      </c>
-    </row>
-    <row r="71" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D71" s="1"/>
-      <c r="F71" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="G71" s="10">
-        <v>-0.56007034541067402</v>
-      </c>
-      <c r="H71" s="12">
-        <f t="shared" si="2"/>
-        <v>-5.6007034541067403E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D72" s="1"/>
-      <c r="F72" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="G72" s="10">
-        <v>-0.49515880009730046</v>
-      </c>
-      <c r="H72" s="12">
-        <f t="shared" si="2"/>
-        <v>-4.9515880009730045E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D73" s="1"/>
-      <c r="F73" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G73" s="10">
-        <v>-0.48492530203864975</v>
-      </c>
-      <c r="H73" s="12">
-        <f t="shared" si="2"/>
-        <v>-4.8492530203864976E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D74" s="1"/>
-      <c r="F74" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="G74" s="10">
-        <v>-0.46923884125274068</v>
-      </c>
-      <c r="H74" s="12">
-        <f t="shared" si="2"/>
-        <v>-4.6923884125274068E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D75" s="1"/>
-      <c r="F75" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="G75" s="10">
-        <v>-0.46173053312736234</v>
-      </c>
-      <c r="H75" s="12">
-        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
-        <v>-4.6173053312736235E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D76" s="1"/>
-      <c r="F76" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="G76" s="10">
-        <v>-0.44554891075458514</v>
-      </c>
-      <c r="H76" s="12">
-        <f t="shared" si="3"/>
-        <v>-4.4554891075458515E-3</v>
-      </c>
-    </row>
-    <row r="77" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D77" s="1"/>
-      <c r="F77" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="G77" s="10">
-        <v>-0.35606298251969726</v>
-      </c>
-      <c r="H77" s="12">
-        <f t="shared" si="3"/>
-        <v>-3.5606298251969724E-3</v>
-      </c>
-    </row>
-    <row r="78" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D78" s="1"/>
-      <c r="F78" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="G78" s="10">
-        <v>-0.34449675752917985</v>
-      </c>
-      <c r="H78" s="12">
-        <f t="shared" si="3"/>
-        <v>-3.4449675752917987E-3</v>
-      </c>
-    </row>
-    <row r="79" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D79" s="1"/>
-      <c r="F79" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="G79" s="10">
-        <v>-0.27875728165155722</v>
-      </c>
-      <c r="H79" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.787572816515572E-3</v>
-      </c>
-    </row>
-    <row r="80" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D80" s="1"/>
-      <c r="F80" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="G80" s="10">
-        <v>-0.24921887088681788</v>
-      </c>
-      <c r="H80" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.4921887088681788E-3</v>
-      </c>
-    </row>
-    <row r="81" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D81" s="1"/>
-      <c r="F81" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="G81" s="10">
-        <v>-0.23320955251166742</v>
-      </c>
-      <c r="H81" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.3320955251166743E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D82" s="1"/>
-      <c r="F82" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="G82" s="10">
-        <v>-0.23178456106778422</v>
-      </c>
-      <c r="H82" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.3178456106778423E-3</v>
-      </c>
-    </row>
-    <row r="83" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D83" s="1"/>
-      <c r="F83" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="G83" s="10">
-        <v>-0.23062227374651528</v>
-      </c>
-      <c r="H83" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.3062227374651529E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D84" s="1"/>
-      <c r="F84" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="G84" s="10">
-        <v>-0.2198304019835241</v>
-      </c>
-      <c r="H84" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.198304019835241E-3</v>
-      </c>
-    </row>
-    <row r="85" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D85" s="1"/>
-      <c r="F85" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G85" s="10">
-        <v>-0.17906361599513917</v>
-      </c>
-      <c r="H85" s="12">
-        <f t="shared" si="3"/>
-        <v>-1.7906361599513917E-3</v>
-      </c>
-    </row>
-    <row r="86" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D86" s="1"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="13"/>
-    </row>
-    <row r="87" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D87" s="1"/>
-    </row>
-    <row r="88" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D88" s="1"/>
-    </row>
-    <row r="89" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D89" s="1"/>
-      <c r="G89" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D90" s="1"/>
-    </row>
-    <row r="91" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D91" s="1"/>
-      <c r="H91" s="1"/>
-    </row>
-    <row r="92" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D92" s="1"/>
-      <c r="H92" s="1"/>
-    </row>
-    <row r="93" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D93" s="1"/>
-      <c r="H93" s="1"/>
-    </row>
-    <row r="94" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D94" s="1"/>
-      <c r="H94" s="1"/>
-    </row>
-    <row r="95" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D95" s="1"/>
-      <c r="H95" s="1"/>
-    </row>
-    <row r="96" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D96" s="1"/>
-      <c r="H96" s="1"/>
-    </row>
-    <row r="97" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D97" s="1"/>
-      <c r="H97" s="1"/>
-    </row>
-    <row r="98" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D98" s="1"/>
-      <c r="H98" s="1"/>
-    </row>
-    <row r="99" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D99" s="1"/>
-      <c r="H99" s="1"/>
-    </row>
-    <row r="100" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D100" s="1"/>
-      <c r="H100" s="1"/>
-    </row>
-    <row r="101" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D101" s="1"/>
-      <c r="H101" s="1"/>
-    </row>
-    <row r="102" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D102" s="1"/>
-      <c r="H102" s="1"/>
-    </row>
-    <row r="103" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D103" s="1"/>
-      <c r="H103" s="1"/>
-    </row>
-    <row r="104" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D104" s="1"/>
-      <c r="H104" s="1"/>
-    </row>
-    <row r="105" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D105" s="1"/>
-      <c r="H105" s="1"/>
-    </row>
-    <row r="106" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D106" s="1"/>
-      <c r="H106" s="1"/>
-    </row>
-    <row r="107" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D107" s="1"/>
-      <c r="H107" s="1"/>
-    </row>
-    <row r="108" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D108" s="1"/>
-      <c r="H108" s="1"/>
-    </row>
-    <row r="109" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D109" s="1"/>
-      <c r="H109" s="1"/>
-    </row>
-    <row r="110" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D110" s="1"/>
-      <c r="H110" s="1"/>
-    </row>
-    <row r="111" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D111" s="1"/>
-      <c r="H111" s="1"/>
-    </row>
-    <row r="112" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D112" s="1"/>
-      <c r="H112" s="1"/>
-    </row>
-    <row r="113" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D113" s="1"/>
-      <c r="H113" s="1"/>
-    </row>
-    <row r="114" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D114" s="1"/>
-      <c r="H114" s="1"/>
-    </row>
-    <row r="115" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D115" s="1"/>
-      <c r="H115" s="1"/>
-    </row>
-    <row r="116" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D116" s="1"/>
-      <c r="H116" s="1"/>
-    </row>
-    <row r="117" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D117" s="1"/>
-      <c r="H117" s="1"/>
-    </row>
-    <row r="118" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D118" s="1"/>
-      <c r="H118" s="1"/>
-    </row>
-    <row r="119" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D119" s="1"/>
-      <c r="H119" s="1"/>
-    </row>
-    <row r="120" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D120" s="1"/>
-      <c r="H120" s="1"/>
-    </row>
-    <row r="121" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D121" s="1"/>
-      <c r="H121" s="1"/>
-    </row>
-    <row r="122" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D122" s="1"/>
-      <c r="H122" s="1"/>
-    </row>
-    <row r="123" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D123" s="1"/>
-      <c r="H123" s="1"/>
-    </row>
-    <row r="124" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D124" s="1"/>
-      <c r="H124" s="1"/>
-    </row>
-    <row r="125" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D125" s="1"/>
-      <c r="H125" s="1"/>
-    </row>
-    <row r="126" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D126" s="1"/>
-      <c r="H126" s="1"/>
-    </row>
-    <row r="127" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D127" s="1"/>
-      <c r="H127" s="1"/>
-    </row>
-    <row r="128" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D128" s="1"/>
-      <c r="H128" s="1"/>
-    </row>
-    <row r="129" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D129" s="1"/>
-      <c r="H129" s="1"/>
-    </row>
-    <row r="130" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D130" s="1"/>
-      <c r="H130" s="1"/>
-    </row>
-    <row r="131" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D131" s="1"/>
-      <c r="H131" s="1"/>
-    </row>
-    <row r="132" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D132" s="1"/>
-      <c r="H132" s="1"/>
-    </row>
-    <row r="133" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D133" s="1"/>
-      <c r="H133" s="1"/>
-    </row>
-    <row r="134" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D134" s="1"/>
-      <c r="H134" s="1"/>
-    </row>
-    <row r="135" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D135" s="1"/>
-      <c r="H135" s="1"/>
-    </row>
-    <row r="136" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D136" s="1"/>
-      <c r="H136" s="1"/>
-    </row>
-    <row r="137" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D137" s="1"/>
-      <c r="H137" s="1"/>
-    </row>
-    <row r="138" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D138" s="1"/>
-      <c r="H138" s="1"/>
-    </row>
-    <row r="139" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D139" s="1"/>
-      <c r="H139" s="1"/>
-    </row>
-    <row r="140" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D140" s="1"/>
-      <c r="H140" s="1"/>
-    </row>
-    <row r="141" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D141" s="1"/>
-      <c r="H141" s="1"/>
-    </row>
-    <row r="142" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D142" s="1"/>
-      <c r="H142" s="1"/>
-    </row>
-    <row r="143" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D143" s="1"/>
-      <c r="H143" s="1"/>
-    </row>
-    <row r="144" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D144" s="1"/>
-      <c r="H144" s="1"/>
-    </row>
-    <row r="145" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D145" s="1"/>
-      <c r="H145" s="1"/>
-    </row>
-    <row r="146" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D146" s="1"/>
-      <c r="H146" s="1"/>
-    </row>
-    <row r="147" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D147" s="1"/>
-      <c r="H147" s="1"/>
-    </row>
-    <row r="148" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D148" s="1"/>
-      <c r="H148" s="1"/>
-    </row>
-    <row r="149" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D149" s="1"/>
-      <c r="H149" s="1"/>
-    </row>
-    <row r="150" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D150" s="1"/>
-      <c r="H150" s="1"/>
-    </row>
-    <row r="151" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D151" s="1"/>
-      <c r="H151" s="1"/>
-    </row>
-    <row r="152" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D152" s="1"/>
-      <c r="H152" s="1"/>
-    </row>
-    <row r="153" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D153" s="1"/>
-      <c r="H153" s="1"/>
-    </row>
-    <row r="154" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D154" s="1"/>
-      <c r="H154" s="1"/>
-    </row>
-    <row r="155" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D155" s="1"/>
-      <c r="H155" s="1"/>
-    </row>
-    <row r="156" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D156" s="1"/>
-      <c r="H156" s="1"/>
-    </row>
-    <row r="157" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D157" s="1"/>
-      <c r="H157" s="1"/>
-    </row>
-    <row r="158" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D158" s="1"/>
-      <c r="H158" s="1"/>
-    </row>
-    <row r="159" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D159" s="1"/>
-      <c r="H159" s="1"/>
-    </row>
-    <row r="160" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D160" s="1"/>
-      <c r="H160" s="1"/>
-    </row>
-    <row r="161" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D161" s="1"/>
-      <c r="H161" s="1"/>
-    </row>
-    <row r="162" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D162" s="1"/>
-      <c r="H162" s="1"/>
-    </row>
-    <row r="163" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D163" s="1"/>
-      <c r="H163" s="1"/>
-    </row>
-    <row r="164" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D164" s="1"/>
-      <c r="H164" s="1"/>
-    </row>
-    <row r="165" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D165" s="1"/>
-      <c r="H165" s="1"/>
-    </row>
-    <row r="166" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D166" s="1"/>
-      <c r="H166" s="1"/>
-    </row>
-    <row r="167" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D167" s="1"/>
-      <c r="H167" s="1"/>
-    </row>
-    <row r="168" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D168" s="1"/>
-      <c r="H168" s="1"/>
-    </row>
-    <row r="169" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D169" s="1"/>
-      <c r="H169" s="1"/>
-    </row>
-    <row r="170" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D170" s="1"/>
-      <c r="H170" s="1"/>
-    </row>
-    <row r="171" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D171" s="1"/>
-      <c r="H171" s="1"/>
-    </row>
-    <row r="172" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D172" s="1"/>
-      <c r="H172" s="1"/>
-    </row>
-    <row r="173" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D173" s="1"/>
-      <c r="H173" s="1"/>
-    </row>
-    <row r="174" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D174" s="1"/>
-      <c r="H174" s="1"/>
-    </row>
-    <row r="175" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D175" s="1"/>
-      <c r="H175" s="1"/>
-    </row>
-    <row r="176" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D176" s="1"/>
-      <c r="H176" s="1"/>
-    </row>
-    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D177" s="1"/>
-      <c r="H177" s="1"/>
-    </row>
-    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D178" s="1"/>
-      <c r="H178" s="1"/>
-    </row>
-    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D179" s="1"/>
-      <c r="H179" s="1"/>
-    </row>
-    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D180" s="1"/>
-      <c r="H180" s="1"/>
-    </row>
-    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H181" s="1"/>
-    </row>
-    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H182" s="1"/>
-    </row>
-    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H183" s="1"/>
-    </row>
-    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H184" s="1"/>
-    </row>
-    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H185" s="1"/>
-    </row>
-    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H186" s="1"/>
-    </row>
-    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H187" s="1"/>
-    </row>
-    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H188" s="1"/>
-    </row>
-    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H189" s="1"/>
-    </row>
-    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H190" s="1"/>
-    </row>
-    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H191" s="1"/>
-    </row>
-    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="H192" s="1"/>
-    </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H193" s="1"/>
-    </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H194" s="1"/>
-    </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H195" s="1"/>
-    </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H196" s="1"/>
-    </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H197" s="1"/>
-    </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H198" s="1"/>
-    </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H199" s="1"/>
-    </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H200" s="1"/>
-    </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H201" s="1"/>
-    </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H202" s="1"/>
-    </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H203" s="1"/>
-    </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H204" s="1"/>
-    </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H205" s="1"/>
-    </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H206" s="1"/>
-    </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H207" s="1"/>
-    </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H208" s="1"/>
-    </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H209" s="1"/>
-    </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H210" s="1"/>
-    </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H211" s="1"/>
-    </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H212" s="1"/>
-    </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H213" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="77" orientation="portrait" r:id="rId1"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="8" max="11" man="1"/>
-  </colBreaks>
-</worksheet>
 </file>
--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4585D-9012-644E-8B8B-1131810FA6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A21B6170-BDBA-1D4D-B196-5F3A2F0EA98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30900" yWindow="1120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issuer" sheetId="1" r:id="rId1"/>
+    <sheet name="Instrument" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="224">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -62,349 +63,652 @@
     <t>SERIES: Trading (non-additive)</t>
   </si>
   <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>LAUREATE EDUCATION ORD (NMS)</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>FAIR ISAAC ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>RHMG</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>4901</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>NICE</t>
+  </si>
+  <si>
+    <t>RCIb</t>
+  </si>
+  <si>
+    <t>T CN</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>TYL</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>WTC</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>WSP</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>TEPRF</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>6752</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>FWONK</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>SAPG</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>SPHR</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
+  </si>
+  <si>
+    <t>CINTAS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AUTODESK ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CANON ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>LOGITECH N ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>VERISK ANALYTICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>EQUIFAX ORD (NYS)</t>
+  </si>
+  <si>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SERVICETITAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
+  </si>
+  <si>
+    <t>RHEINMETALL ORD (GER)</t>
+  </si>
+  <si>
+    <t>EBAY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAMSARA CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MSLYT26S INDEX CFD</t>
+  </si>
+  <si>
+    <t>CROWDSTRIKE HOLDINGS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>REA GROUP ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>SANRIO ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>NICE ADR REP 1 ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
+  </si>
+  <si>
+    <t>TELUS ORD (TOR)</t>
+  </si>
+  <si>
+    <t>CDW ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WILLIAMS SONOMA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GARTNER ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TYLER TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SLM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SEZZLE INC (NMS)</t>
+  </si>
+  <si>
+    <t>DUOLINGO CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBERT HALF ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ARISTA NETWORKS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SYMBOTIC CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CARGURUS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ADOBE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>QUALYS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WISETECH GLOBAL ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WSP GLOBAL ORD (TOR)</t>
+  </si>
+  <si>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DATADOG CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
+    <t>STANTEC ORD (TOR)</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
+  </si>
+  <si>
+    <t>CONCENTRIX ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>BLOCK CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
+    <t>ALPHABET CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AMAZON COM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AT&amp;T ORD (NYS)</t>
+  </si>
+  <si>
+    <t>MAPLEBEAR ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>EATON ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ADVANTEST ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AUTO1 GROUP ORD (GER)</t>
+  </si>
+  <si>
+    <t>PANASONIC HLDG ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>IRON MOUNTAIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBLOX CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LYFT CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
+    <t>DRAFTKINGS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TRIMBLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SK HYNIX ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>SAP ORD (GER)</t>
+  </si>
+  <si>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
+  </si>
+  <si>
+    <t>STMICROELECTRONICS ADR (NYS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>MSLYT26L INDEX CFD</t>
+  </si>
+  <si>
+    <t>WAYFAIR CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>BILL HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SANDISK ORD (NMS)</t>
+  </si>
+  <si>
+    <t>EVERPURE CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CLOUDFLARE CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>QORVO ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ETSY ORD (NYS)</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>NXPI</t>
+  </si>
+  <si>
+    <t>CMCSA</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
     <t>LION</t>
   </si>
   <si>
+    <t>RDDT</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>BCE</t>
+  </si>
+  <si>
+    <t>CBOE</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>NBIS</t>
+  </si>
+  <si>
+    <t>CRWV</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>NOKIA</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
     <t>AAOI</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>4901</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>RHMG</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>NICE</t>
-  </si>
-  <si>
-    <t>TYL</t>
-  </si>
-  <si>
-    <t>T CN</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>RDDT</t>
-  </si>
-  <si>
-    <t>RCIb</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>BCE</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>SOFI</t>
-  </si>
-  <si>
-    <t>WTC</t>
-  </si>
-  <si>
-    <t>CBOE</t>
-  </si>
-  <si>
-    <t>WSP</t>
-  </si>
-  <si>
-    <t>CIEN</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>NBIS</t>
-  </si>
-  <si>
-    <t>CRWV</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>STN</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>LITE</t>
-  </si>
-  <si>
-    <t>SITM</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>NOKIA</t>
-  </si>
-  <si>
-    <t>TEPRF</t>
-  </si>
-  <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>6752</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>FWONK</t>
-  </si>
-  <si>
-    <t>6857</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>000660</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>STM</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>SAPG</t>
-  </si>
-  <si>
-    <t>SPHR</t>
-  </si>
-  <si>
-    <t>BILL</t>
-  </si>
-  <si>
-    <t>NXPI</t>
-  </si>
-  <si>
-    <t>CMCSA</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>SNDK</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>P</t>
   </si>
 </sst>
 </file>
@@ -917,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q213"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
@@ -937,7 +1241,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -1028,7 +1332,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C11" s="10">
         <v>10.64005596812768</v>
@@ -1038,17 +1342,17 @@
         <v>0.10640055968127679</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" s="10">
         <v>-6.4259951438552427</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
+        <f t="shared" ref="H11:H74" si="1">IF(F11="","",G11/100)</f>
         <v>-6.4259951438552426E-2</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
@@ -1056,7 +1360,7 @@
         <v/>
       </c>
       <c r="O11" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="12" t="str">
@@ -1066,7 +1370,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C12" s="10">
         <v>7.1950650992045766</v>
@@ -1076,7 +1380,7 @@
         <v>7.195065099204577E-2</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G12" s="10">
         <v>-5.2216320699761347</v>
@@ -1094,7 +1398,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C13" s="10">
         <v>5.2547784652781599</v>
@@ -1104,7 +1408,7 @@
         <v>5.25477846527816E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G13" s="10">
         <v>-4.365073485393987</v>
@@ -1117,7 +1421,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C14" s="10">
         <v>4.9119947853290071</v>
@@ -1127,7 +1431,7 @@
         <v>4.9119947853290075E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G14" s="10">
         <v>-4.3408345472357777</v>
@@ -1140,7 +1444,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C15" s="10">
         <v>4.879267170305237</v>
@@ -1150,7 +1454,7 @@
         <v>4.8792671703052369E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G15" s="10">
         <v>-3.8140152582354738</v>
@@ -1163,7 +1467,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C16" s="10">
         <v>4.7918802751980447</v>
@@ -1173,7 +1477,7 @@
         <v>4.7918802751980447E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G16" s="10">
         <v>-3.6106726835593657</v>
@@ -1186,7 +1490,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C17" s="10">
         <v>4.7381546652776985</v>
@@ -1196,7 +1500,7 @@
         <v>4.7381546652776982E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G17" s="10">
         <v>-3.5520112268146975</v>
@@ -1208,7 +1512,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C18" s="10">
         <v>4.3307314974614863</v>
@@ -1218,7 +1522,7 @@
         <v>4.3307314974614861E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G18" s="10">
         <v>-3.4496143935110948</v>
@@ -1230,7 +1534,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C19" s="10">
         <v>4.1460580439357262</v>
@@ -1240,7 +1544,7 @@
         <v>4.1460580439357263E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G19" s="10">
         <v>-3.4211573857452673</v>
@@ -1252,7 +1556,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C20" s="10">
         <v>4.1216441647674635</v>
@@ -1262,7 +1566,7 @@
         <v>4.1216441647674636E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G20" s="10">
         <v>-3.0710882033923217</v>
@@ -1274,7 +1578,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C21" s="10">
         <v>4.0422262295122326</v>
@@ -1284,7 +1588,7 @@
         <v>4.042226229512233E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G21" s="10">
         <v>-3.0473678223257492</v>
@@ -1296,7 +1600,7 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C22" s="10">
         <v>3.5991535325953463</v>
@@ -1306,7 +1610,7 @@
         <v>3.5991535325953464E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G22" s="10">
         <v>-3.0344210290871141</v>
@@ -1318,7 +1622,7 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C23" s="10">
         <v>3.3814452225683911</v>
@@ -1328,7 +1632,7 @@
         <v>3.3814452225683911E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G23" s="10">
         <v>-3.0047060322135644</v>
@@ -1340,7 +1644,7 @@
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C24" s="10">
         <v>3.3235701789410972</v>
@@ -1350,7 +1654,7 @@
         <v>3.3235701789410974E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G24" s="10">
         <v>-2.846663571898902</v>
@@ -1362,7 +1666,7 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C25" s="10">
         <v>3.3115135890385243</v>
@@ -1372,7 +1676,7 @@
         <v>3.3115135890385242E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G25" s="10">
         <v>-2.5229770882784228</v>
@@ -1384,7 +1688,7 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C26" s="10">
         <v>3.2683840292570423</v>
@@ -1394,7 +1698,7 @@
         <v>3.2683840292570425E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G26" s="10">
         <v>-2.3856987210331826</v>
@@ -1406,7 +1710,7 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C27" s="10">
         <v>3.0222359078790135</v>
@@ -1416,7 +1720,7 @@
         <v>3.0222359078790135E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G27" s="10">
         <v>-2.3761832582530054</v>
@@ -1428,7 +1732,7 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="C28" s="10">
         <v>2.8433870771432437</v>
@@ -1438,7 +1742,7 @@
         <v>2.8433870771432435E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G28" s="10">
         <v>-2.3540382862818929</v>
@@ -1450,7 +1754,7 @@
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C29" s="10">
         <v>2.7046177195658769</v>
@@ -1460,7 +1764,7 @@
         <v>2.7046177195658768E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G29" s="10">
         <v>-2.3165984967731266</v>
@@ -1472,7 +1776,7 @@
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C30" s="10">
         <v>2.3384310105678714</v>
@@ -1482,7 +1786,7 @@
         <v>2.3384310105678714E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>31</v>
+        <v>202</v>
       </c>
       <c r="G30" s="10">
         <v>-2.2906035669978437</v>
@@ -1494,7 +1798,7 @@
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C31" s="10">
         <v>2.2703685525546646</v>
@@ -1504,7 +1808,7 @@
         <v>2.2703685525546646E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="G31" s="10">
         <v>-2.2171344338401728</v>
@@ -1516,7 +1820,7 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C32" s="10">
         <v>2.2584248608532977</v>
@@ -1526,7 +1830,7 @@
         <v>2.2584248608532979E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G32" s="10">
         <v>-2.0650361555785475</v>
@@ -1538,7 +1842,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="C33" s="10">
         <v>2.2387676595398327</v>
@@ -1548,7 +1852,7 @@
         <v>2.2387676595398327E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G33" s="10">
         <v>-1.9827602150565788</v>
@@ -1560,7 +1864,7 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="C34" s="10">
         <v>2.1941851726367463</v>
@@ -1570,7 +1874,7 @@
         <v>2.1941851726367465E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G34" s="10">
         <v>-1.9602637021482971</v>
@@ -1582,7 +1886,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="C35" s="10">
         <v>2.1727092295605615</v>
@@ -1592,7 +1896,7 @@
         <v>2.1727092295605613E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G35" s="10">
         <v>-1.8487967456276129</v>
@@ -1604,7 +1908,7 @@
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C36" s="10">
         <v>1.8923947547785789</v>
@@ -1614,7 +1918,7 @@
         <v>1.8923947547785789E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G36" s="10">
         <v>-1.7851622624583465</v>
@@ -1626,7 +1930,7 @@
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C37" s="10">
         <v>1.8376374279430556</v>
@@ -1636,7 +1940,7 @@
         <v>1.8376374279430556E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G37" s="10">
         <v>-1.7103975527725646</v>
@@ -1648,7 +1952,7 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C38" s="10">
         <v>1.8052287869531423</v>
@@ -1658,7 +1962,7 @@
         <v>1.8052287869531423E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G38" s="10">
         <v>-1.5565238467242555</v>
@@ -1670,7 +1974,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="C39" s="10">
         <v>1.7885051185863587</v>
@@ -1680,7 +1984,7 @@
         <v>1.7885051185863587E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G39" s="10">
         <v>-1.546089004395887</v>
@@ -1692,7 +1996,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C40" s="10">
         <v>1.1734697487598551</v>
@@ -1702,7 +2006,7 @@
         <v>1.1734697487598551E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G40" s="10">
         <v>-1.5430879921263745</v>
@@ -1714,7 +2018,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C41" s="10">
         <v>1.1247678708981241</v>
@@ -1724,7 +2028,7 @@
         <v>1.1247678708981241E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G41" s="10">
         <v>-1.4811772286335634</v>
@@ -1736,7 +2040,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="C42" s="10">
         <v>0.97437978627921507</v>
@@ -1746,7 +2050,7 @@
         <v>9.7437978627921504E-3</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G42" s="10">
         <v>-1.3918029071695248</v>
@@ -1758,7 +2062,7 @@
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>118</v>
+        <v>207</v>
       </c>
       <c r="C43" s="10">
         <v>0.95525050810167356</v>
@@ -1768,19 +2072,19 @@
         <v>9.5525050810167361E-3</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G43" s="10">
         <v>-1.3439701619380315</v>
       </c>
       <c r="H43" s="12">
-        <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
+        <f t="shared" si="1"/>
         <v>-1.3439701619380316E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="C44" s="10">
         <v>0.86489775821718662</v>
@@ -1790,19 +2094,19 @@
         <v>8.6489775821718667E-3</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G44" s="10">
         <v>-1.3329396474390769</v>
       </c>
       <c r="H44" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.3329396474390768E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C45" s="10">
         <v>0.78258783268582433</v>
@@ -1812,19 +2116,19 @@
         <v>7.8258783268582433E-3</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="G45" s="10">
         <v>-1.302842523119903</v>
       </c>
       <c r="H45" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.302842523119903E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C46" s="10">
         <v>0.7564468353401671</v>
@@ -1834,19 +2138,19 @@
         <v>7.5644683534016712E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G46" s="10">
         <v>-1.2861151014962608</v>
       </c>
       <c r="H46" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.2861151014962609E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C47" s="10">
         <v>0.4816872103436059</v>
@@ -1856,19 +2160,19 @@
         <v>4.816872103436059E-3</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G47" s="10">
         <v>-1.2512477732885505</v>
       </c>
       <c r="H47" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.2512477732885505E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="C48" s="10">
         <v>0.2768825325933561</v>
@@ -1878,13 +2182,13 @@
         <v>2.7688253259335609E-3</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G48" s="10">
         <v>-1.245197897856299</v>
       </c>
       <c r="H48" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.245197897856299E-2</v>
       </c>
     </row>
@@ -1893,61 +2197,61 @@
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
       <c r="F49" s="11" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G49" s="10">
         <v>-1.1713001457601533</v>
       </c>
       <c r="H49" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.1713001457601534E-2</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F50" s="11" t="s">
-        <v>51</v>
+        <v>211</v>
       </c>
       <c r="G50" s="10">
         <v>-1.1605663203932066</v>
       </c>
       <c r="H50" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.1605663203932066E-2</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F51" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G51" s="10">
         <v>-1.1509750922079443</v>
       </c>
       <c r="H51" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.1509750922079443E-2</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G52" s="10">
         <v>-1.0709084280107859</v>
       </c>
       <c r="H52" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.0709084280107859E-2</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G53" s="10">
         <v>-1.0610580769480413</v>
       </c>
       <c r="H53" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.0610580769480413E-2</v>
       </c>
     </row>
@@ -1960,410 +2264,410 @@
         <v>-1.0207023736332841</v>
       </c>
       <c r="H54" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-1.0207023736332841E-2</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G55" s="10">
         <v>-0.98033362007491975</v>
       </c>
       <c r="H55" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-9.8033362007491978E-3</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G56" s="10">
         <v>-0.9644062055724083</v>
       </c>
       <c r="H56" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-9.6440620557240835E-3</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G57" s="10">
         <v>-0.92358035363769697</v>
       </c>
       <c r="H57" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-9.2358035363769696E-3</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G58" s="10">
         <v>-0.91996570803856947</v>
       </c>
       <c r="H58" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-9.1996570803856946E-3</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G59" s="10">
         <v>-0.89122288634373958</v>
       </c>
       <c r="H59" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-8.9122288634373957E-3</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>61</v>
+        <v>212</v>
       </c>
       <c r="G60" s="10">
         <v>-0.88366122175361306</v>
       </c>
       <c r="H60" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-8.8366122175361304E-3</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G61" s="10">
         <v>-0.85920520117370169</v>
       </c>
       <c r="H61" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-8.5920520117370169E-3</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G62" s="10">
         <v>-0.83451957787032593</v>
       </c>
       <c r="H62" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-8.3451957787032596E-3</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G63" s="10">
         <v>-0.78195496384089247</v>
       </c>
       <c r="H63" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-7.819549638408925E-3</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>65</v>
+        <v>213</v>
       </c>
       <c r="G64" s="10">
         <v>-0.75481416200005946</v>
       </c>
       <c r="H64" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-7.5481416200005947E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G65" s="10">
         <v>-0.67829021780682441</v>
       </c>
       <c r="H65" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-6.7829021780682446E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G66" s="10">
         <v>-0.6310523461797608</v>
       </c>
       <c r="H66" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-6.3105234617976081E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G67" s="10">
         <v>-0.63061754196957609</v>
       </c>
       <c r="H67" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-6.3061754196957606E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="G68" s="10">
         <v>-0.56071187298688574</v>
       </c>
       <c r="H68" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-5.6071187298688575E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G69" s="10">
         <v>-0.56007034541067402</v>
       </c>
       <c r="H69" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-5.6007034541067403E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="G70" s="10">
         <v>-0.49515880009730046</v>
       </c>
       <c r="H70" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-4.9515880009730045E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G71" s="10">
         <v>-0.48492530203864975</v>
       </c>
       <c r="H71" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-4.8492530203864976E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G72" s="10">
         <v>-0.46923884125274068</v>
       </c>
       <c r="H72" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-4.6923884125274068E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
       <c r="F73" s="11" t="s">
-        <v>74</v>
+        <v>216</v>
       </c>
       <c r="G73" s="10">
         <v>-0.46173053312736234</v>
       </c>
       <c r="H73" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-4.6173053312736235E-3</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
       <c r="F74" s="11" t="s">
-        <v>75</v>
+        <v>217</v>
       </c>
       <c r="G74" s="10">
         <v>-0.44554891075458514</v>
       </c>
       <c r="H74" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-4.4554891075458515E-3</v>
       </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
       <c r="F75" s="11" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="G75" s="10">
         <v>-0.3679944396176823</v>
       </c>
       <c r="H75" s="12">
-        <f t="shared" ref="H75:H85" si="3">IF(F75="","",G75/100)</f>
+        <f t="shared" ref="H75:H85" si="2">IF(F75="","",G75/100)</f>
         <v>-3.6799443961768232E-3</v>
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
       <c r="F76" s="11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G76" s="10">
         <v>-0.35606298251969726</v>
       </c>
       <c r="H76" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-3.5606298251969724E-3</v>
       </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
       <c r="F77" s="11" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G77" s="10">
         <v>-0.34449675752917985</v>
       </c>
       <c r="H77" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-3.4449675752917987E-3</v>
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
       <c r="F78" s="11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G78" s="10">
         <v>-0.27875728165155722</v>
       </c>
       <c r="H78" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-2.787572816515572E-3</v>
       </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
       <c r="F79" s="11" t="s">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="G79" s="10">
         <v>-0.24921887088681788</v>
       </c>
       <c r="H79" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-2.4921887088681788E-3</v>
       </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
       <c r="F80" s="11" t="s">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="G80" s="10">
         <v>-0.23320955251166742</v>
       </c>
       <c r="H80" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-2.3320955251166743E-3</v>
       </c>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
       <c r="F81" s="11" t="s">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="G81" s="10">
         <v>-0.23178456106778422</v>
       </c>
       <c r="H81" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-2.3178456106778423E-3</v>
       </c>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
       <c r="F82" s="11" t="s">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="G82" s="10">
         <v>-0.23062227374651528</v>
       </c>
       <c r="H82" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-2.3062227374651529E-3</v>
       </c>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
       <c r="F83" s="11" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="G83" s="10">
         <v>-0.2198304019835241</v>
       </c>
       <c r="H83" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-2.198304019835241E-3</v>
       </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
       <c r="F84" s="11" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="G84" s="10">
         <v>-0.21575192897618961</v>
       </c>
       <c r="H84" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-2.157519289761896E-3</v>
       </c>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
       <c r="F85" s="11" t="s">
-        <v>9</v>
+        <v>223</v>
       </c>
       <c r="G85" s="10">
         <v>-0.17906361599513917</v>
       </c>
       <c r="H85" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-1.7906361599513917E-3</v>
       </c>
     </row>
@@ -2725,60 +3029,57 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D177" s="1"/>
+    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -2807,45 +3108,1797 @@
     </row>
     <row r="201" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H201" s="1"/>
-    </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H202" s="1"/>
-    </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H203" s="1"/>
-    </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H204" s="1"/>
-    </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H205" s="1"/>
-    </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H206" s="1"/>
-    </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H207" s="1"/>
-    </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H208" s="1"/>
-    </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H209" s="1"/>
-    </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H210" s="1"/>
-    </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H211" s="1"/>
-    </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H212" s="1"/>
-    </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H213" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
+  <dimension ref="A1:Q201"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5" customWidth="1"/>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.5" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.5" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B11" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="10">
+        <v>9.3676345958810714</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
+        <v>9.3676345958810719E-2</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="10">
+        <v>-6.6747511166068776</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
+        <v>-6.6747511166068779E-2</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
+        <f>IF(L11="","",L11/100)</f>
+        <v/>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="12" t="str">
+        <f>IF(P11="","",P11/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="10">
+        <v>7.178295390076145</v>
+      </c>
+      <c r="D12" s="10">
+        <f t="shared" si="0"/>
+        <v>7.1782953900761448E-2</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="10">
+        <v>-5.1257189854440615</v>
+      </c>
+      <c r="H12" s="12">
+        <f t="shared" si="1"/>
+        <v>-5.1257189854440617E-2</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="13"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5.0098197800339523</v>
+      </c>
+      <c r="D13" s="10">
+        <f t="shared" si="0"/>
+        <v>5.0098197800339521E-2</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="10">
+        <v>-5.0593808269021654</v>
+      </c>
+      <c r="H13" s="12">
+        <f t="shared" si="1"/>
+        <v>-5.0593808269021656E-2</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B14" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="10">
+        <v>4.9893411504096523</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" si="0"/>
+        <v>4.989341150409652E-2</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="10">
+        <v>-4.7845448503728001</v>
+      </c>
+      <c r="H14" s="12">
+        <f t="shared" si="1"/>
+        <v>-4.7845448503728003E-2</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="10">
+        <v>4.8934917789138455</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="0"/>
+        <v>4.8934917789138457E-2</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="10">
+        <v>-4.2526844426100716</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>-4.2526844426100718E-2</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B16" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="10">
+        <v>4.7956028569605618</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" si="0"/>
+        <v>4.7956028569605617E-2</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="10">
+        <v>-3.7538715318079805</v>
+      </c>
+      <c r="H16" s="12">
+        <f t="shared" si="1"/>
+        <v>-3.7538715318079806E-2</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="10">
+        <v>4.6320517671014345</v>
+      </c>
+      <c r="D17" s="10">
+        <f t="shared" si="0"/>
+        <v>4.6320517671014347E-2</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-3.5028928974400122</v>
+      </c>
+      <c r="H17" s="12">
+        <f t="shared" si="1"/>
+        <v>-3.5028928974400124E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="10">
+        <v>4.1488266383129728</v>
+      </c>
+      <c r="D18" s="10">
+        <f t="shared" si="0"/>
+        <v>4.1488266383129725E-2</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-3.4100075996797381</v>
+      </c>
+      <c r="H18" s="12">
+        <f t="shared" si="1"/>
+        <v>-3.4100075996797381E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="10">
+        <v>3.9941428681304529</v>
+      </c>
+      <c r="D19" s="10">
+        <f t="shared" si="0"/>
+        <v>3.9941428681304528E-2</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="10">
+        <v>-3.2883526862952359</v>
+      </c>
+      <c r="H19" s="12">
+        <f t="shared" si="1"/>
+        <v>-3.2883526862952359E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="10">
+        <v>3.960998571869724</v>
+      </c>
+      <c r="D20" s="10">
+        <f t="shared" si="0"/>
+        <v>3.9609985718697241E-2</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="10">
+        <v>-3.2377588228208172</v>
+      </c>
+      <c r="H20" s="12">
+        <f t="shared" si="1"/>
+        <v>-3.2377588228208173E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="10">
+        <v>3.6679107565062949</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" si="0"/>
+        <v>3.667910756506295E-2</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="10">
+        <v>-2.9534394867720826</v>
+      </c>
+      <c r="H21" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.9534394867720824E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="10">
+        <v>3.3901254552592754</v>
+      </c>
+      <c r="D22" s="10">
+        <f t="shared" si="0"/>
+        <v>3.3901254552592755E-2</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="10">
+        <v>-2.8758244405332403</v>
+      </c>
+      <c r="H22" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.8758244405332402E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="10">
+        <v>3.3536380206432495</v>
+      </c>
+      <c r="D23" s="10">
+        <f t="shared" si="0"/>
+        <v>3.3536380206432494E-2</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="10">
+        <v>-2.8675313674108578</v>
+      </c>
+      <c r="H23" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.8675313674108579E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="10">
+        <v>3.2000877018935543</v>
+      </c>
+      <c r="D24" s="10">
+        <f t="shared" si="0"/>
+        <v>3.2000877018935545E-2</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="10">
+        <v>-2.5902503120703009</v>
+      </c>
+      <c r="H24" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.590250312070301E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B25" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="10">
+        <v>3.1627821872447059</v>
+      </c>
+      <c r="D25" s="10">
+        <f t="shared" si="0"/>
+        <v>3.1627821872447059E-2</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="10">
+        <v>-2.5047802005457753</v>
+      </c>
+      <c r="H25" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.5047802005457753E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B26" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="10">
+        <v>3.0505612112986151</v>
+      </c>
+      <c r="D26" s="10">
+        <f t="shared" si="0"/>
+        <v>3.050561211298615E-2</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G26" s="10">
+        <v>-2.4719791999441085</v>
+      </c>
+      <c r="H26" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.4719791999441087E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B27" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="10">
+        <v>2.9758227955613918</v>
+      </c>
+      <c r="D27" s="10">
+        <f t="shared" si="0"/>
+        <v>2.975822795561392E-2</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="10">
+        <v>-2.4280737722724806</v>
+      </c>
+      <c r="H27" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.4280737722724807E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B28" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2.5627698903959235</v>
+      </c>
+      <c r="D28" s="10">
+        <f t="shared" si="0"/>
+        <v>2.5627698903959235E-2</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="10">
+        <v>-2.209426104135249</v>
+      </c>
+      <c r="H28" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.2094261041352491E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B29" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="10">
+        <v>2.5098554346299311</v>
+      </c>
+      <c r="D29" s="10">
+        <f t="shared" si="0"/>
+        <v>2.5098554346299311E-2</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="10">
+        <v>-2.1433936519179007</v>
+      </c>
+      <c r="H29" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.1433936519179006E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2.4321920966956521</v>
+      </c>
+      <c r="D30" s="10">
+        <f t="shared" si="0"/>
+        <v>2.4321920966956522E-2</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" s="10">
+        <v>-2.1271937672668861</v>
+      </c>
+      <c r="H30" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.1271937672668863E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B31" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="10">
+        <v>2.2075253833059327</v>
+      </c>
+      <c r="D31" s="10">
+        <f t="shared" si="0"/>
+        <v>2.2075253833059326E-2</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="10">
+        <v>-2.0435843613963227</v>
+      </c>
+      <c r="H31" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.0435843613963226E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B32" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2.0981973233901021</v>
+      </c>
+      <c r="D32" s="10">
+        <f t="shared" si="0"/>
+        <v>2.0981973233901021E-2</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="10">
+        <v>-2.0210862608719604</v>
+      </c>
+      <c r="H32" s="12">
+        <f t="shared" si="1"/>
+        <v>-2.0210862608719606E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="10">
+        <v>2.0850481380747117</v>
+      </c>
+      <c r="D33" s="10">
+        <f t="shared" si="0"/>
+        <v>2.0850481380747118E-2</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" s="10">
+        <v>-1.9955531802970969</v>
+      </c>
+      <c r="H33" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.995553180297097E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="10">
+        <v>2.0104689250012719</v>
+      </c>
+      <c r="D34" s="10">
+        <f t="shared" si="0"/>
+        <v>2.0104689250012721E-2</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" s="10">
+        <v>-1.9941591425575136</v>
+      </c>
+      <c r="H34" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.9941591425575136E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="10">
+        <v>1.9912055076369131</v>
+      </c>
+      <c r="D35" s="10">
+        <f t="shared" si="0"/>
+        <v>1.9912055076369131E-2</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="10">
+        <v>-1.9119858208758242</v>
+      </c>
+      <c r="H35" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.9119858208758243E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" s="10">
+        <v>1.9481978272974623</v>
+      </c>
+      <c r="D36" s="10">
+        <f t="shared" si="0"/>
+        <v>1.9481978272974623E-2</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G36" s="10">
+        <v>-1.7937745156034437</v>
+      </c>
+      <c r="H36" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.7937745156034437E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" s="10">
+        <v>1.7446904333315016</v>
+      </c>
+      <c r="D37" s="10">
+        <f t="shared" si="0"/>
+        <v>1.7446904333315017E-2</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="10">
+        <v>-1.7896264676777158</v>
+      </c>
+      <c r="H37" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.7896264676777157E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B38" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" s="10">
+        <v>1.6067850405688737</v>
+      </c>
+      <c r="D38" s="10">
+        <f t="shared" si="0"/>
+        <v>1.6067850405688738E-2</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G38" s="10">
+        <v>-1.7321728084499362</v>
+      </c>
+      <c r="H38" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.732172808449936E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B39" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C39" s="10">
+        <v>1.4968446417390027</v>
+      </c>
+      <c r="D39" s="10">
+        <f t="shared" si="0"/>
+        <v>1.4968446417390027E-2</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" s="10">
+        <v>-1.6089367918507707</v>
+      </c>
+      <c r="H39" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.6089367918507708E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="10">
+        <v>0.98481520791170696</v>
+      </c>
+      <c r="D40" s="10">
+        <f t="shared" si="0"/>
+        <v>9.8481520791170694E-3</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" s="10">
+        <v>-1.494577307054914</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.494577307054914E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B41" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="10">
+        <v>0.94212419763022948</v>
+      </c>
+      <c r="D41" s="10">
+        <f t="shared" si="0"/>
+        <v>9.4212419763022946E-3</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="10">
+        <v>-1.4765597546543652</v>
+      </c>
+      <c r="H41" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.4765597546543652E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C42" s="10">
+        <v>0.74655664930348975</v>
+      </c>
+      <c r="D42" s="10">
+        <f t="shared" si="0"/>
+        <v>7.4655664930348975E-3</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42" s="10">
+        <v>-1.4492896285598154</v>
+      </c>
+      <c r="H42" s="12">
+        <f t="shared" si="1"/>
+        <v>-1.4492896285598154E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="10">
+        <v>0.72041709585217106</v>
+      </c>
+      <c r="D43" s="10">
+        <f t="shared" si="0"/>
+        <v>7.204170958521711E-3</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G43" s="10">
+        <v>-1.3909880938269175</v>
+      </c>
+      <c r="H43" s="12">
+        <f t="shared" ref="H43:H73" si="2">IF(F43="","",G43/100)</f>
+        <v>-1.3909880938269175E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" s="10">
+        <v>0.6712714794526613</v>
+      </c>
+      <c r="D44" s="10">
+        <f t="shared" si="0"/>
+        <v>6.7127147945266127E-3</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="10">
+        <v>-1.3884102113419121</v>
+      </c>
+      <c r="H44" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3884102113419122E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" s="10">
+        <v>0.61628335957250424</v>
+      </c>
+      <c r="D45" s="10">
+        <f t="shared" si="0"/>
+        <v>6.1628335957250426E-3</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="10">
+        <v>-1.3074682183127213</v>
+      </c>
+      <c r="H45" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3074682183127214E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0.54435032429445362</v>
+      </c>
+      <c r="D46" s="10">
+        <f t="shared" si="0"/>
+        <v>5.4435032429445366E-3</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G46" s="10">
+        <v>-1.3069378013300608</v>
+      </c>
+      <c r="H46" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3069378013300608E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.35372342663835893</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>3.5372342663835894E-3</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1.3040521026412208</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.3040521026412209E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="F48" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-1.2845994016584155</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2845994016584155E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F49" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-1.2806145811026568</v>
+      </c>
+      <c r="H49" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2806145811026569E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F50" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G50" s="10">
+        <v>-1.2733598873867638</v>
+      </c>
+      <c r="H50" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2733598873867637E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F51" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G51" s="10">
+        <v>-1.2325645600528132</v>
+      </c>
+      <c r="H51" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2325645600528132E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F52" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G52" s="10">
+        <v>-0.98810854320703134</v>
+      </c>
+      <c r="H52" s="12">
+        <f t="shared" si="2"/>
+        <v>-9.8810854320703131E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D53" s="1"/>
+      <c r="F53" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="G53" s="10">
+        <v>-0.94154124273748196</v>
+      </c>
+      <c r="H53" s="12">
+        <f t="shared" si="2"/>
+        <v>-9.4154124273748193E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D54" s="1"/>
+      <c r="F54" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G54" s="10">
+        <v>-0.89393254013237</v>
+      </c>
+      <c r="H54" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.9393254013236997E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D55" s="1"/>
+      <c r="F55" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G55" s="10">
+        <v>-0.85959217876515093</v>
+      </c>
+      <c r="H55" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.5959217876515094E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D56" s="1"/>
+      <c r="F56" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G56" s="10">
+        <v>-0.83076110098309497</v>
+      </c>
+      <c r="H56" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.3076110098309498E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D57" s="1"/>
+      <c r="F57" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" s="10">
+        <v>-0.82131867111538226</v>
+      </c>
+      <c r="H57" s="12">
+        <f t="shared" si="2"/>
+        <v>-8.2131867111538224E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D58" s="1"/>
+      <c r="F58" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G58" s="10">
+        <v>-0.79351820000791196</v>
+      </c>
+      <c r="H58" s="12">
+        <f t="shared" si="2"/>
+        <v>-7.9351820000791197E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D59" s="1"/>
+      <c r="F59" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G59" s="10">
+        <v>-0.78645940792387792</v>
+      </c>
+      <c r="H59" s="12">
+        <f t="shared" si="2"/>
+        <v>-7.8645940792387795E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D60" s="1"/>
+      <c r="F60" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="G60" s="10">
+        <v>-0.76066545316329681</v>
+      </c>
+      <c r="H60" s="12">
+        <f t="shared" si="2"/>
+        <v>-7.6066545316329677E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D61" s="1"/>
+      <c r="F61" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G61" s="10">
+        <v>-0.73616695371993224</v>
+      </c>
+      <c r="H61" s="12">
+        <f t="shared" si="2"/>
+        <v>-7.3616695371993227E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D62" s="1"/>
+      <c r="F62" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="G62" s="10">
+        <v>-0.7106220142592159</v>
+      </c>
+      <c r="H62" s="12">
+        <f t="shared" si="2"/>
+        <v>-7.1062201425921593E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D63" s="1"/>
+      <c r="F63" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G63" s="10">
+        <v>-0.69770510126098817</v>
+      </c>
+      <c r="H63" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.9770510126098816E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D64" s="1"/>
+      <c r="F64" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G64" s="10">
+        <v>-0.69122760876568512</v>
+      </c>
+      <c r="H64" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.9122760876568516E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D65" s="1"/>
+      <c r="F65" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G65" s="10">
+        <v>-0.63807820273744953</v>
+      </c>
+      <c r="H65" s="12">
+        <f t="shared" si="2"/>
+        <v>-6.3807820273744957E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D66" s="1"/>
+      <c r="F66" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G66" s="10">
+        <v>-0.56896397532157073</v>
+      </c>
+      <c r="H66" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.6896397532157075E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D67" s="1"/>
+      <c r="F67" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67" s="10">
+        <v>-0.41722081673939365</v>
+      </c>
+      <c r="H67" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.1722081673939366E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D68" s="1"/>
+      <c r="F68" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G68" s="10">
+        <v>-0.3938261891657775</v>
+      </c>
+      <c r="H68" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.9382618916577747E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D69" s="1"/>
+      <c r="F69" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G69" s="10">
+        <v>-0.39343732974725998</v>
+      </c>
+      <c r="H69" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.9343732974726001E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D70" s="1"/>
+      <c r="F70" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G70" s="10">
+        <v>-0.37300865403654426</v>
+      </c>
+      <c r="H70" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.7300865403654426E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D71" s="1"/>
+      <c r="F71" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-0.34174543086615383</v>
+      </c>
+      <c r="H71" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.4174543086615385E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D72" s="1"/>
+      <c r="F72" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-0.25310390078560174</v>
+      </c>
+      <c r="H72" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.5310390078560176E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D73" s="1"/>
+      <c r="F73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-2.7968664389488827E-2</v>
+      </c>
+      <c r="H73" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.7968664389488827E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D74" s="1"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="13"/>
+    </row>
+    <row r="75" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D77" s="1"/>
+      <c r="G77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D78" s="1"/>
+    </row>
+    <row r="79" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D79" s="1"/>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D80" s="1"/>
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D81" s="1"/>
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D83" s="1"/>
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D84" s="1"/>
+      <c r="H84" s="1"/>
+    </row>
+    <row r="85" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D85" s="1"/>
+      <c r="H85" s="1"/>
+    </row>
+    <row r="86" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D86" s="1"/>
+      <c r="H86" s="1"/>
+    </row>
+    <row r="87" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D87" s="1"/>
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D88" s="1"/>
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D89" s="1"/>
+      <c r="H89" s="1"/>
+    </row>
+    <row r="90" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D90" s="1"/>
+      <c r="H90" s="1"/>
+    </row>
+    <row r="91" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D91" s="1"/>
+      <c r="H91" s="1"/>
+    </row>
+    <row r="92" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D92" s="1"/>
+      <c r="H92" s="1"/>
+    </row>
+    <row r="93" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D93" s="1"/>
+      <c r="H93" s="1"/>
+    </row>
+    <row r="94" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D94" s="1"/>
+      <c r="H94" s="1"/>
+    </row>
+    <row r="95" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D95" s="1"/>
+      <c r="H95" s="1"/>
+    </row>
+    <row r="96" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D96" s="1"/>
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D97" s="1"/>
+      <c r="H97" s="1"/>
+    </row>
+    <row r="98" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D98" s="1"/>
+      <c r="H98" s="1"/>
+    </row>
+    <row r="99" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D99" s="1"/>
+      <c r="H99" s="1"/>
+    </row>
+    <row r="100" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D100" s="1"/>
+      <c r="H100" s="1"/>
+    </row>
+    <row r="101" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D101" s="1"/>
+      <c r="H101" s="1"/>
+    </row>
+    <row r="102" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D102" s="1"/>
+      <c r="H102" s="1"/>
+    </row>
+    <row r="103" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D103" s="1"/>
+      <c r="H103" s="1"/>
+    </row>
+    <row r="104" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D104" s="1"/>
+      <c r="H104" s="1"/>
+    </row>
+    <row r="105" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D105" s="1"/>
+      <c r="H105" s="1"/>
+    </row>
+    <row r="106" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D106" s="1"/>
+      <c r="H106" s="1"/>
+    </row>
+    <row r="107" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D107" s="1"/>
+      <c r="H107" s="1"/>
+    </row>
+    <row r="108" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D108" s="1"/>
+      <c r="H108" s="1"/>
+    </row>
+    <row r="109" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D109" s="1"/>
+      <c r="H109" s="1"/>
+    </row>
+    <row r="110" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D110" s="1"/>
+      <c r="H110" s="1"/>
+    </row>
+    <row r="111" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D111" s="1"/>
+      <c r="H111" s="1"/>
+    </row>
+    <row r="112" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D112" s="1"/>
+      <c r="H112" s="1"/>
+    </row>
+    <row r="113" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D113" s="1"/>
+      <c r="H113" s="1"/>
+    </row>
+    <row r="114" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D114" s="1"/>
+      <c r="H114" s="1"/>
+    </row>
+    <row r="115" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D115" s="1"/>
+      <c r="H115" s="1"/>
+    </row>
+    <row r="116" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D116" s="1"/>
+      <c r="H116" s="1"/>
+    </row>
+    <row r="117" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D117" s="1"/>
+      <c r="H117" s="1"/>
+    </row>
+    <row r="118" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D118" s="1"/>
+      <c r="H118" s="1"/>
+    </row>
+    <row r="119" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D119" s="1"/>
+      <c r="H119" s="1"/>
+    </row>
+    <row r="120" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D120" s="1"/>
+      <c r="H120" s="1"/>
+    </row>
+    <row r="121" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D121" s="1"/>
+      <c r="H121" s="1"/>
+    </row>
+    <row r="122" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D122" s="1"/>
+      <c r="H122" s="1"/>
+    </row>
+    <row r="123" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D123" s="1"/>
+      <c r="H123" s="1"/>
+    </row>
+    <row r="124" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D124" s="1"/>
+      <c r="H124" s="1"/>
+    </row>
+    <row r="125" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D125" s="1"/>
+      <c r="H125" s="1"/>
+    </row>
+    <row r="126" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D126" s="1"/>
+      <c r="H126" s="1"/>
+    </row>
+    <row r="127" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D127" s="1"/>
+      <c r="H127" s="1"/>
+    </row>
+    <row r="128" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D128" s="1"/>
+      <c r="H128" s="1"/>
+    </row>
+    <row r="129" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D129" s="1"/>
+      <c r="H129" s="1"/>
+    </row>
+    <row r="130" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D130" s="1"/>
+      <c r="H130" s="1"/>
+    </row>
+    <row r="131" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D131" s="1"/>
+      <c r="H131" s="1"/>
+    </row>
+    <row r="132" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D132" s="1"/>
+      <c r="H132" s="1"/>
+    </row>
+    <row r="133" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D133" s="1"/>
+      <c r="H133" s="1"/>
+    </row>
+    <row r="134" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D134" s="1"/>
+      <c r="H134" s="1"/>
+    </row>
+    <row r="135" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D135" s="1"/>
+      <c r="H135" s="1"/>
+    </row>
+    <row r="136" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D136" s="1"/>
+      <c r="H136" s="1"/>
+    </row>
+    <row r="137" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D137" s="1"/>
+      <c r="H137" s="1"/>
+    </row>
+    <row r="138" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D138" s="1"/>
+      <c r="H138" s="1"/>
+    </row>
+    <row r="139" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D139" s="1"/>
+      <c r="H139" s="1"/>
+    </row>
+    <row r="140" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D140" s="1"/>
+      <c r="H140" s="1"/>
+    </row>
+    <row r="141" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D141" s="1"/>
+      <c r="H141" s="1"/>
+    </row>
+    <row r="142" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D142" s="1"/>
+      <c r="H142" s="1"/>
+    </row>
+    <row r="143" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D143" s="1"/>
+      <c r="H143" s="1"/>
+    </row>
+    <row r="144" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D144" s="1"/>
+      <c r="H144" s="1"/>
+    </row>
+    <row r="145" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D145" s="1"/>
+      <c r="H145" s="1"/>
+    </row>
+    <row r="146" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D146" s="1"/>
+      <c r="H146" s="1"/>
+    </row>
+    <row r="147" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D147" s="1"/>
+      <c r="H147" s="1"/>
+    </row>
+    <row r="148" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D148" s="1"/>
+      <c r="H148" s="1"/>
+    </row>
+    <row r="149" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D149" s="1"/>
+      <c r="H149" s="1"/>
+    </row>
+    <row r="150" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D150" s="1"/>
+      <c r="H150" s="1"/>
+    </row>
+    <row r="151" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D151" s="1"/>
+      <c r="H151" s="1"/>
+    </row>
+    <row r="152" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D152" s="1"/>
+      <c r="H152" s="1"/>
+    </row>
+    <row r="153" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D153" s="1"/>
+      <c r="H153" s="1"/>
+    </row>
+    <row r="154" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D154" s="1"/>
+      <c r="H154" s="1"/>
+    </row>
+    <row r="155" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D155" s="1"/>
+      <c r="H155" s="1"/>
+    </row>
+    <row r="156" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D156" s="1"/>
+      <c r="H156" s="1"/>
+    </row>
+    <row r="157" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D157" s="1"/>
+      <c r="H157" s="1"/>
+    </row>
+    <row r="158" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D158" s="1"/>
+      <c r="H158" s="1"/>
+    </row>
+    <row r="159" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D159" s="1"/>
+      <c r="H159" s="1"/>
+    </row>
+    <row r="160" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D160" s="1"/>
+      <c r="H160" s="1"/>
+    </row>
+    <row r="161" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D161" s="1"/>
+      <c r="H161" s="1"/>
+    </row>
+    <row r="162" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D162" s="1"/>
+      <c r="H162" s="1"/>
+    </row>
+    <row r="163" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D163" s="1"/>
+      <c r="H163" s="1"/>
+    </row>
+    <row r="164" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D164" s="1"/>
+      <c r="H164" s="1"/>
+    </row>
+    <row r="165" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D165" s="1"/>
+      <c r="H165" s="1"/>
+    </row>
+    <row r="166" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D166" s="1"/>
+      <c r="H166" s="1"/>
+    </row>
+    <row r="167" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D167" s="1"/>
+      <c r="H167" s="1"/>
+    </row>
+    <row r="168" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D168" s="1"/>
+      <c r="H168" s="1"/>
+    </row>
+    <row r="169" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D169" s="1"/>
+      <c r="H169" s="1"/>
+    </row>
+    <row r="170" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D170" s="1"/>
+      <c r="H170" s="1"/>
+    </row>
+    <row r="171" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D171" s="1"/>
+      <c r="H171" s="1"/>
+    </row>
+    <row r="172" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D172" s="1"/>
+      <c r="H172" s="1"/>
+    </row>
+    <row r="173" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D173" s="1"/>
+      <c r="H173" s="1"/>
+    </row>
+    <row r="174" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D174" s="1"/>
+      <c r="H174" s="1"/>
+    </row>
+    <row r="175" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D175" s="1"/>
+      <c r="H175" s="1"/>
+    </row>
+    <row r="176" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D176" s="1"/>
+      <c r="H176" s="1"/>
+    </row>
+    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H177" s="1"/>
+    </row>
+    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H178" s="1"/>
+    </row>
+    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H179" s="1"/>
+    </row>
+    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H180" s="1"/>
+    </row>
+    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H181" s="1"/>
+    </row>
+    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H182" s="1"/>
+    </row>
+    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H183" s="1"/>
+    </row>
+    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H184" s="1"/>
+    </row>
+    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H185" s="1"/>
+    </row>
+    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H186" s="1"/>
+    </row>
+    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H187" s="1"/>
+    </row>
+    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H188" s="1"/>
+    </row>
+    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H189" s="1"/>
+    </row>
+    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H190" s="1"/>
+    </row>
+    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H191" s="1"/>
+    </row>
+    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H192" s="1"/>
+    </row>
+    <row r="193" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H193" s="1"/>
+    </row>
+    <row r="194" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H194" s="1"/>
+    </row>
+    <row r="195" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H195" s="1"/>
+    </row>
+    <row r="196" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H196" s="1"/>
+    </row>
+    <row r="197" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H197" s="1"/>
+    </row>
+    <row r="198" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H198" s="1"/>
+    </row>
+    <row r="199" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H199" s="1"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H200" s="1"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="77" orientation="portrait" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="8" max="11" man="1"/>
+  </colBreaks>
+</worksheet>
 </file>
--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A21B6170-BDBA-1D4D-B196-5F3A2F0EA98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C8D1A05-9822-4C44-8D39-4312AEF50A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30900" yWindow="1120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issuer" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="231">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -63,322 +63,409 @@
     <t>SERIES: Trading (non-additive)</t>
   </si>
   <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>STANTEC ORD (TOR)</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>FAIR ISAAC ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CINTAS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>4901</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>T CN</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>NICE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>RCIb</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>RDDT</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>TYL</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>BCE</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>NBIS</t>
+  </si>
+  <si>
+    <t>CRWV</t>
+  </si>
+  <si>
+    <t>WTC</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>WSP</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>TEPRF</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>NOKIA</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>RKT</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>6752</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>SAPG</t>
+  </si>
+  <si>
+    <t>FWONK</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>PCOR</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>SPHR</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>NXPI</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>LION</t>
+  </si>
+  <si>
     <t>DASH</t>
   </si>
   <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
-  </si>
-  <si>
-    <t>LAUREATE EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>Instrument</t>
-  </si>
-  <si>
-    <t>FAIR ISAAC ORD (NYS)</t>
-  </si>
-  <si>
     <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
   </si>
   <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>RHMG</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>4901</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>NICE</t>
-  </si>
-  <si>
-    <t>RCIb</t>
-  </si>
-  <si>
-    <t>T CN</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>TYL</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>WTC</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>WSP</t>
-  </si>
-  <si>
-    <t>SOFI</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>STN</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>TEPRF</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>6857</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>6752</t>
-  </si>
-  <si>
-    <t>RKT</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>FWONK</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>000660</t>
-  </si>
-  <si>
-    <t>SAPG</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>STM</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>SPHR</t>
-  </si>
-  <si>
-    <t>BILL</t>
-  </si>
-  <si>
-    <t>SNDK</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
     <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
   </si>
   <si>
-    <t>CINTAS ORD (NMS)</t>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>CANON ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
   </si>
   <si>
     <t>AUTODESK ORD (NMS)</t>
   </si>
   <si>
-    <t>CANON ORD (TYO) CFD</t>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>EXPEDIA GROUP ORD (NMS)</t>
   </si>
   <si>
     <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
   </si>
   <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
+    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PINTEREST CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>EQUIFAX ORD (NYS)</t>
   </si>
   <si>
     <t>LOGITECH N ORD (NMS)</t>
   </si>
   <si>
-    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SANRIO ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>SERVICETITAN CL A ORD (NMS)</t>
   </si>
   <si>
     <t>VERISK ANALYTICS ORD (NMS)</t>
@@ -387,328 +474,262 @@
     <t>GARMIN ORD (NYS)</t>
   </si>
   <si>
-    <t>ARAMARK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>APPLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>EQUIFAX ORD (NYS)</t>
-  </si>
-  <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NEW YORK TIMES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
+    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>SAMSARA CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WILLIAMS SONOMA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>REA GROUP ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
   </si>
   <si>
     <t>PALANTIR TECHNOLOGIES CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>BENTLEY SYSTEMS CL B ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RHEINMETALL ORD (GER)</t>
+    <t>SLM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TELUS ORD (TOR)</t>
+  </si>
+  <si>
+    <t>NVIDIA ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NICE ADR REP 1 ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARTNER ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
   </si>
   <si>
     <t>EBAY ORD (NMS)</t>
   </si>
   <si>
-    <t>SAMSARA CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FUJIFILM HOLDING ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>MSLYT26S INDEX CFD</t>
-  </si>
-  <si>
-    <t>CROWDSTRIKE HOLDINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>REA GROUP ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>NICE ADR REP 1 ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ROGERS COMMUNICATIONS CL B ORD (TOR)</t>
-  </si>
-  <si>
-    <t>TELUS ORD (TOR)</t>
-  </si>
-  <si>
-    <t>CDW ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WILLIAMS SONOMA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>GARTNER ORD (NYS)</t>
+    <t>ROBERT HALF ORD (NYS)</t>
+  </si>
+  <si>
+    <t>DUOLINGO CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>REDDIT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>BOOKING HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>QUALYS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CARGURUS CL A ORD (NMS)</t>
   </si>
   <si>
     <t>TYLER TECHNOLOGIES ORD (NYS)</t>
   </si>
   <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
+    <t>ARISTA NETWORKS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>COINBASE GLOBAL CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
   </si>
   <si>
     <t>SEZZLE INC (NMS)</t>
   </si>
   <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBERT HALF ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARISTA NETWORKS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+    <t>BCE ORD (TOR)</t>
   </si>
   <si>
     <t>SYMBOTIC CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>CARGURUS CL A ORD (NMS)</t>
-  </si>
-  <si>
     <t>ADOBE ORD (NMS)</t>
   </si>
   <si>
-    <t>QUALYS ORD (NMS)</t>
+    <t>NEBIUS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>COREWEAVE CL A ORD (NMS)</t>
   </si>
   <si>
     <t>WISETECH GLOBAL ORD (ASX) CFD</t>
   </si>
   <si>
+    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
+  </si>
+  <si>
+    <t>CIENA ORD (NYS)</t>
+  </si>
+  <si>
     <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
   </si>
   <si>
+    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
     <t>WSP GLOBAL ORD (TOR)</t>
   </si>
   <si>
-    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DATADOG CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>STANTEC ORD (TOR)</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 C200 OTC (DASH 1/15/27 C200 OTC)</t>
-  </si>
-  <si>
     <t>CONCENTRIX ORD (NMS)</t>
   </si>
   <si>
     <t>TELEPERFORMANCE ORD (PAR) CFD</t>
   </si>
   <si>
+    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SITIME ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NOKIA ADR REPSG 1 SER A ORD (NYS)</t>
+  </si>
+  <si>
     <t>BLOCK CL A ORD (NYS)</t>
   </si>
   <si>
     <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
   </si>
   <si>
+    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WAYFAIR CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TRIMBLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>EATON ORD (NYS)</t>
+  </si>
+  <si>
     <t>ALPHABET CL A ORD (NMS)</t>
   </si>
   <si>
+    <t>AUTO1 GROUP ORD (GER)</t>
+  </si>
+  <si>
+    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LYFT CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AT&amp;T ORD (NYS)</t>
+  </si>
+  <si>
+    <t>PANASONIC HLDG ORD (TYO) CFD</t>
+  </si>
+  <si>
     <t>AMAZON COM ORD (NMS)</t>
   </si>
   <si>
-    <t>AT&amp;T ORD (NYS)</t>
+    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>IRON MOUNTAIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ADVANTEST ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SK HYNIX ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>ROBLOX CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>INTUIT ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAP ORD (GER)</t>
+  </si>
+  <si>
+    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
+  </si>
+  <si>
+    <t>DRAFTKINGS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
+    <t>APPLOVIN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
+  </si>
+  <si>
+    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
   </si>
   <si>
     <t>MAPLEBEAR ORD (NMS)</t>
   </si>
   <si>
-    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>EATON ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AUTO1 GROUP ORD (GER)</t>
-  </si>
-  <si>
-    <t>PANASONIC HLDG ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>ROCKET COMPANIES CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>IRON MOUNTAIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBLOX CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LYFT CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LIBERTY MEDIA FORMULA ONE SRS C ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (NYS)</t>
-  </si>
-  <si>
-    <t>DRAFTKINGS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TRIMBLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SK HYNIX ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>SAP ORD (GER)</t>
-  </si>
-  <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
+    <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
   </si>
   <si>
     <t>STMICROELECTRONICS ADR (NYS)</t>
   </si>
   <si>
-    <t>FERRARI ORD (MIL)</t>
-  </si>
-  <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>MSLYT26L INDEX CFD</t>
-  </si>
-  <si>
-    <t>WAYFAIR CL A ORD (NYS)</t>
-  </si>
-  <si>
     <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
   </si>
   <si>
     <t>BILL HOLDINGS ORD (NYS)</t>
   </si>
   <si>
+    <t>NETAPP ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TERADYNE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NXP SEMICONDUCTORS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>APPLIED MATERIAL ORD (NMS)</t>
+  </si>
+  <si>
+    <t>META US 01/15/27 P620 OTC (META 1/15/27 P620 OTC)</t>
+  </si>
+  <si>
     <t>SANDISK ORD (NMS)</t>
   </si>
   <si>
-    <t>EVERPURE CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CLOUDFLARE CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>QORVO ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ETSY ORD (NYS)</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>NXPI</t>
-  </si>
-  <si>
-    <t>CMCSA</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>LION</t>
-  </si>
-  <si>
-    <t>RDDT</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>BCE</t>
-  </si>
-  <si>
-    <t>CBOE</t>
-  </si>
-  <si>
-    <t>CIEN</t>
-  </si>
-  <si>
-    <t>NBIS</t>
-  </si>
-  <si>
-    <t>CRWV</t>
-  </si>
-  <si>
-    <t>LITE</t>
-  </si>
-  <si>
-    <t>SITM</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>NOKIA</t>
-  </si>
-  <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>AAOI</t>
+    <t>LIONSGATE STUDIOS ORD (NYS)</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1241,7 +1262,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -1332,27 +1353,27 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C11" s="10">
-        <v>10.64005596812768</v>
+        <v>11.360598682213555</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D48" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10640055968127679</v>
+        <f t="shared" ref="D11:D51" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.11360598682213555</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-6.4259951438552427</v>
+        <v>-7.1465236511326653</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" ref="H11:H74" si="1">IF(F11="","",G11/100)</f>
-        <v>-6.4259951438552426E-2</v>
+        <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
+        <v>-7.1465236511326649E-2</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
@@ -1360,7 +1381,7 @@
         <v/>
       </c>
       <c r="O11" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="12" t="str">
@@ -1370,24 +1391,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C12" s="10">
-        <v>7.1950650992045766</v>
+        <v>7.3223789442194986</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.195065099204577E-2</v>
+        <v>7.3223789442194986E-2</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.2216320699761347</v>
+        <v>-5.252425636630301</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.221632069976135E-2</v>
+        <v>-5.2524256366303007E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1398,1299 +1419,1263 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C13" s="10">
-        <v>5.2547784652781599</v>
+        <v>5.2562789779318946</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.25477846527816E-2</v>
+        <v>5.2562789779318948E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-4.365073485393987</v>
+        <v>-4.657430598765564</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.3650734853939867E-2</v>
+        <v>-4.6574305987655641E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C14" s="10">
-        <v>4.9119947853290071</v>
+        <v>5.2371338471596927</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.9119947853290075E-2</v>
+        <v>5.2371338471596925E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.3408345472357777</v>
+        <v>-4.625419931418211</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.3408345472357779E-2</v>
+        <v>-4.6254199314182107E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C15" s="10">
-        <v>4.879267170305237</v>
+        <v>4.8499200592306648</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.8792671703052369E-2</v>
+        <v>4.8499200592306647E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-3.8140152582354738</v>
+        <v>-4.4537942425225863</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8140152582354737E-2</v>
+        <v>-4.4537942425225865E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C16" s="10">
-        <v>4.7918802751980447</v>
+        <v>4.5709296842828993</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.7918802751980447E-2</v>
+        <v>4.5709296842828991E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.6106726835593657</v>
+        <v>-4.0710223920934956</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6106726835593655E-2</v>
+        <v>-4.0710223920934957E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C17" s="10">
-        <v>4.7381546652776985</v>
+        <v>4.4351668733261436</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.7381546652776982E-2</v>
+        <v>4.4351668733261435E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.5520112268146975</v>
+        <v>-4.0300444235888992</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5520112268146976E-2</v>
+        <v>-4.0300444235888994E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C18" s="10">
-        <v>4.3307314974614863</v>
+        <v>4.3869361626066272</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.3307314974614861E-2</v>
+        <v>4.3869361626066271E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.4496143935110948</v>
+        <v>-3.9139934025209446</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4496143935110947E-2</v>
+        <v>-3.9139934025209447E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C19" s="10">
-        <v>4.1460580439357262</v>
+        <v>4.1238389723573805</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>4.1460580439357263E-2</v>
+        <v>4.1238389723573805E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.4211573857452673</v>
+        <v>-3.4383931829236136</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4211573857452673E-2</v>
+        <v>-3.4383931829236138E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C20" s="10">
-        <v>4.1216441647674635</v>
+        <v>4.0876103987069197</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>4.1216441647674636E-2</v>
+        <v>4.0876103987069194E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.0710882033923217</v>
+        <v>-3.19925255308089</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0710882033923217E-2</v>
+        <v>-3.1992525530808898E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C21" s="10">
-        <v>4.0422262295122326</v>
+        <v>3.5982051807134328</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>4.042226229512233E-2</v>
+        <v>3.5982051807134326E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-3.0473678223257492</v>
+        <v>-3.1608527990597519</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0473678223257493E-2</v>
+        <v>-3.1608527990597518E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C22" s="10">
-        <v>3.5991535325953463</v>
+        <v>3.4986501305543851</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.5991535325953464E-2</v>
+        <v>3.498650130554385E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-3.0344210290871141</v>
+        <v>-2.6992477945087519</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-3.034421029087114E-2</v>
+        <v>-2.6992477945087519E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C23" s="10">
-        <v>3.3814452225683911</v>
+        <v>3.4909462847660033</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.3814452225683911E-2</v>
+        <v>3.4909462847660035E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-3.0047060322135644</v>
+        <v>-2.6427309406746797</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0047060322135645E-2</v>
+        <v>-2.6427309406746799E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C24" s="10">
-        <v>3.3235701789410972</v>
+        <v>3.4308613324308639</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.3235701789410974E-2</v>
+        <v>3.4308613324308637E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.846663571898902</v>
+        <v>-2.5198156852531883</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8466635718989018E-2</v>
+        <v>-2.5198156852531885E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C25" s="10">
-        <v>3.3115135890385243</v>
+        <v>3.4307808726457028</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>3.3115135890385242E-2</v>
+        <v>3.4307808726457029E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.5229770882784228</v>
+        <v>-2.502881687272315</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.522977088278423E-2</v>
+        <v>-2.502881687272315E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C26" s="10">
-        <v>3.2683840292570423</v>
+        <v>3.2894100289545229</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>3.2683840292570425E-2</v>
+        <v>3.2894100289545231E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.3856987210331826</v>
+        <v>-2.2992191065700536</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3856987210331825E-2</v>
+        <v>-2.2992191065700537E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C27" s="10">
-        <v>3.0222359078790135</v>
+        <v>3.2447562773163225</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>3.0222359078790135E-2</v>
+        <v>3.2447562773163227E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.3761832582530054</v>
+        <v>-2.2552449042718847</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3761832582530052E-2</v>
+        <v>-2.2552449042718848E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C28" s="10">
-        <v>2.8433870771432437</v>
+        <v>3.0319993113769916</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.8433870771432435E-2</v>
+        <v>3.0319993113769917E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.3540382862818929</v>
+        <v>-2.2342810572289262</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3540382862818929E-2</v>
+        <v>-2.2342810572289262E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C29" s="10">
-        <v>2.7046177195658769</v>
+        <v>2.6572137020035593</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.7046177195658768E-2</v>
+        <v>2.6572137020035594E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.3165984967731266</v>
+        <v>-2.1528088078624963</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3165984967731267E-2</v>
+        <v>-2.1528088078624961E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="10">
-        <v>2.3384310105678714</v>
+        <v>2.6184623830241716</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.3384310105678714E-2</v>
+        <v>2.6184623830241716E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.2906035669978437</v>
+        <v>-2.1191678999977666</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2906035669978439E-2</v>
+        <v>-2.1191678999977665E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C31" s="10">
-        <v>2.2703685525546646</v>
+        <v>2.5507109819371037</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.2703685525546646E-2</v>
+        <v>2.5507109819371036E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>203</v>
+        <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.2171344338401728</v>
+        <v>-2.0851903615398832</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2171344338401729E-2</v>
+        <v>-2.0851903615398834E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C32" s="10">
-        <v>2.2584248608532977</v>
+        <v>2.5294670008326556</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.2584248608532979E-2</v>
+        <v>2.5294670008326556E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.0650361555785475</v>
+        <v>-1.9935662452662335</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0650361555785476E-2</v>
+        <v>-1.9935662452662335E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="C33" s="10">
-        <v>2.2387676595398327</v>
+        <v>2.325839433713635</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.2387676595398327E-2</v>
+        <v>2.3258394337136348E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9827602150565788</v>
+        <v>-1.9578388136655487</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9827602150565789E-2</v>
+        <v>-1.9578388136655488E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="C34" s="10">
-        <v>2.1941851726367463</v>
+        <v>2.288535962129381</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.1941851726367465E-2</v>
+        <v>2.2885359621293809E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.9602637021482971</v>
+        <v>-1.9526454417954988</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9602637021482971E-2</v>
+        <v>-1.9526454417954989E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C35" s="10">
-        <v>2.1727092295605615</v>
+        <v>2.2706651721560984</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>2.1727092295605613E-2</v>
+        <v>2.2706651721560986E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.8487967456276129</v>
+        <v>-1.7353219900387054</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.8487967456276129E-2</v>
+        <v>-1.7353219900387053E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C36" s="10">
-        <v>1.8923947547785789</v>
+        <v>2.1204859827660343</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.8923947547785789E-2</v>
+        <v>2.1204859827660343E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.7851622624583465</v>
+        <v>-1.6991631768012412</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7851622624583466E-2</v>
+        <v>-1.6991631768012411E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C37" s="10">
-        <v>1.8376374279430556</v>
+        <v>1.8865232728703381</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.8376374279430556E-2</v>
+        <v>1.8865232728703381E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.7103975527725646</v>
+        <v>-1.6564405314631836</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7103975527725645E-2</v>
+        <v>-1.6564405314631835E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C38" s="10">
-        <v>1.8052287869531423</v>
+        <v>1.7784042034397534</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.8052287869531423E-2</v>
+        <v>1.7784042034397533E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.5565238467242555</v>
+        <v>-1.6431933208849332</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5565238467242554E-2</v>
+        <v>-1.6431933208849333E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C39" s="10">
-        <v>1.7885051185863587</v>
+        <v>1.6843748683663697</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.7885051185863587E-2</v>
+        <v>1.6843748683663697E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.546089004395887</v>
+        <v>-1.5764715795747337</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5460890043958871E-2</v>
+        <v>-1.5764715795747338E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C40" s="10">
-        <v>1.1734697487598551</v>
+        <v>1.5277512503401913</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.1734697487598551E-2</v>
+        <v>1.5277512503401914E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.5430879921263745</v>
+        <v>-1.5316039592535979</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5430879921263746E-2</v>
+        <v>-1.5316039592535979E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C41" s="10">
-        <v>1.1247678708981241</v>
+        <v>1.5162775134812103</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.1247678708981241E-2</v>
+        <v>1.5162775134812102E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.4811772286335634</v>
+        <v>-1.4608424364566794</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4811772286335633E-2</v>
+        <v>-1.4608424364566795E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="C42" s="10">
-        <v>0.97437978627921507</v>
+        <v>1.410043443678338</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>9.7437978627921504E-3</v>
+        <v>1.4100434436783381E-2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.3918029071695248</v>
+        <v>-1.4473915039890042</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.3918029071695249E-2</v>
+        <v>-1.4473915039890041E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="C43" s="10">
-        <v>0.95525050810167356</v>
+        <v>1.2833550101968005</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>9.5525050810167361E-3</v>
+        <v>1.2833550101968006E-2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.3439701619380315</v>
+        <v>-1.406816477516841</v>
       </c>
       <c r="H43" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.3439701619380316E-2</v>
+        <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
+        <v>-1.406816477516841E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="C44" s="10">
-        <v>0.86489775821718662</v>
+        <v>1.1635814021237674</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>8.6489775821718667E-3</v>
+        <v>1.1635814021237674E-2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.3329396474390769</v>
+        <v>-1.3035422702547468</v>
       </c>
       <c r="H44" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.3329396474390768E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.3035422702547468E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C45" s="10">
-        <v>0.78258783268582433</v>
+        <v>1.028621188242431</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>7.8258783268582433E-3</v>
+        <v>1.0286211882424311E-2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>209</v>
+        <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.302842523119903</v>
+        <v>-1.2707897784725211</v>
       </c>
       <c r="H45" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.302842523119903E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.2707897784725211E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C46" s="10">
-        <v>0.7564468353401671</v>
+        <v>0.96589864124490898</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>7.5644683534016712E-3</v>
+        <v>9.6589864124490901E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.2861151014962608</v>
+        <v>-1.2559765317916276</v>
       </c>
       <c r="H46" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.2861151014962609E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.2559765317916275E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C47" s="10">
-        <v>0.4816872103436059</v>
+        <v>0.96031111646638234</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="0"/>
-        <v>4.816872103436059E-3</v>
+        <v>9.6031111646638235E-3</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.2512477732885505</v>
+        <v>-1.236953437648276</v>
       </c>
       <c r="H47" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.2512477732885505E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.236953437648276E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="C48" s="10">
-        <v>0.2768825325933561</v>
+        <v>0.59826116207443003</v>
       </c>
       <c r="D48" s="10">
         <f t="shared" si="0"/>
-        <v>2.7688253259335609E-3</v>
+        <v>5.9826116207443002E-3</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.245197897856299</v>
+        <v>-1.2054720030982795</v>
       </c>
       <c r="H48" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.245197897856299E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.2054720030982796E-2</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="9"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
+      <c r="B49" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="10">
+        <v>0.49461030869547906</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="0"/>
+        <v>4.9461030869547909E-3</v>
+      </c>
       <c r="F49" s="11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.1713001457601533</v>
+        <v>-1.1325393596109783</v>
       </c>
       <c r="H49" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.1713001457601534E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.1325393596109783E-2</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="10">
+        <v>0.25503922614777574</v>
+      </c>
+      <c r="D50" s="10">
+        <f t="shared" si="0"/>
+        <v>2.5503922614777573E-3</v>
+      </c>
       <c r="F50" s="11" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.1605663203932066</v>
+        <v>-1.1301898767192593</v>
       </c>
       <c r="H50" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.1605663203932066E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.1301898767192594E-2</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="10">
+        <v>0.22440191207472793</v>
+      </c>
+      <c r="D51" s="10">
+        <f t="shared" si="0"/>
+        <v>2.2440191207472792E-3</v>
+      </c>
       <c r="F51" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-1.1509750922079443</v>
+        <v>-1.1104264953873979</v>
       </c>
       <c r="H51" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.1509750922079443E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.1104264953873979E-2</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="9"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
       <c r="F52" s="11" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-1.0709084280107859</v>
+        <v>-1.0757973469997824</v>
       </c>
       <c r="H52" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.0709084280107859E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.0757973469997824E-2</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-1.0610580769480413</v>
+        <v>-1.0410910258164536</v>
       </c>
       <c r="H53" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.0610580769480413E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.0410910258164536E-2</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D54" s="1"/>
       <c r="F54" s="11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-1.0207023736332841</v>
+        <v>-1.0113173324924725</v>
       </c>
       <c r="H54" s="12">
-        <f t="shared" si="1"/>
-        <v>-1.0207023736332841E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.0113173324924724E-2</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.98033362007491975</v>
+        <v>-0.99299951195439062</v>
       </c>
       <c r="H55" s="12">
-        <f t="shared" si="1"/>
-        <v>-9.8033362007491978E-3</v>
+        <f t="shared" si="2"/>
+        <v>-9.9299951195439065E-3</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.9644062055724083</v>
+        <v>-0.97283654703583544</v>
       </c>
       <c r="H56" s="12">
-        <f t="shared" si="1"/>
-        <v>-9.6440620557240835E-3</v>
+        <f t="shared" si="2"/>
+        <v>-9.7283654703583539E-3</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.92358035363769697</v>
+        <v>-0.9639482417458376</v>
       </c>
       <c r="H57" s="12">
-        <f t="shared" si="1"/>
-        <v>-9.2358035363769696E-3</v>
+        <f t="shared" si="2"/>
+        <v>-9.6394824174583765E-3</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.91996570803856947</v>
+        <v>-0.96344125935177616</v>
       </c>
       <c r="H58" s="12">
-        <f t="shared" si="1"/>
-        <v>-9.1996570803856946E-3</v>
+        <f t="shared" si="2"/>
+        <v>-9.6344125935177612E-3</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.89122288634373958</v>
+        <v>-0.95932073225472714</v>
       </c>
       <c r="H59" s="12">
-        <f t="shared" si="1"/>
-        <v>-8.9122288634373957E-3</v>
+        <f t="shared" si="2"/>
+        <v>-9.5932073225472713E-3</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.88366122175361306</v>
+        <v>-0.94330194646598109</v>
       </c>
       <c r="H60" s="12">
-        <f t="shared" si="1"/>
-        <v>-8.8366122175361304E-3</v>
+        <f t="shared" si="2"/>
+        <v>-9.4330194646598114E-3</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.85920520117370169</v>
+        <v>-0.91090194857380546</v>
       </c>
       <c r="H61" s="12">
-        <f t="shared" si="1"/>
-        <v>-8.5920520117370169E-3</v>
+        <f t="shared" si="2"/>
+        <v>-9.1090194857380551E-3</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.83451957787032593</v>
+        <v>-0.83461735457403963</v>
       </c>
       <c r="H62" s="12">
-        <f t="shared" si="1"/>
-        <v>-8.3451957787032596E-3</v>
+        <f t="shared" si="2"/>
+        <v>-8.3461735457403957E-3</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.78195496384089247</v>
+        <v>-0.79701140150879368</v>
       </c>
       <c r="H63" s="12">
-        <f t="shared" si="1"/>
-        <v>-7.819549638408925E-3</v>
+        <f t="shared" si="2"/>
+        <v>-7.9701140150879365E-3</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.75481416200005946</v>
+        <v>-0.78120413334090721</v>
       </c>
       <c r="H64" s="12">
-        <f t="shared" si="1"/>
-        <v>-7.5481416200005947E-3</v>
+        <f t="shared" si="2"/>
+        <v>-7.8120413334090725E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.67829021780682441</v>
+        <v>-0.76789075423596198</v>
       </c>
       <c r="H65" s="12">
-        <f t="shared" si="1"/>
-        <v>-6.7829021780682446E-3</v>
+        <f t="shared" si="2"/>
+        <v>-7.6789075423596195E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.6310523461797608</v>
+        <v>-0.72496124293161701</v>
       </c>
       <c r="H66" s="12">
-        <f t="shared" si="1"/>
-        <v>-6.3105234617976081E-3</v>
+        <f t="shared" si="2"/>
+        <v>-7.2496124293161702E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.63061754196957609</v>
+        <v>-0.65253243046582754</v>
       </c>
       <c r="H67" s="12">
-        <f t="shared" si="1"/>
-        <v>-6.3061754196957606E-3</v>
+        <f t="shared" si="2"/>
+        <v>-6.5253243046582751E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>214</v>
+        <v>74</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.56071187298688574</v>
+        <v>-0.61445765966219379</v>
       </c>
       <c r="H68" s="12">
-        <f t="shared" si="1"/>
-        <v>-5.6071187298688575E-3</v>
+        <f t="shared" si="2"/>
+        <v>-6.1445765966219382E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.56007034541067402</v>
+        <v>-0.4394205411225075</v>
       </c>
       <c r="H69" s="12">
-        <f t="shared" si="1"/>
-        <v>-5.6007034541067403E-3</v>
+        <f t="shared" si="2"/>
+        <v>-4.3942054112250748E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>215</v>
+        <v>76</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.49515880009730046</v>
+        <v>-0.43136734552093792</v>
       </c>
       <c r="H70" s="12">
-        <f t="shared" si="1"/>
-        <v>-4.9515880009730045E-3</v>
+        <f t="shared" si="2"/>
+        <v>-4.3136734552093794E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.48492530203864975</v>
+        <v>-0.41302437236795692</v>
       </c>
       <c r="H71" s="12">
-        <f t="shared" si="1"/>
-        <v>-4.8492530203864976E-3</v>
+        <f t="shared" si="2"/>
+        <v>-4.130243723679569E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.46923884125274068</v>
+        <v>-0.32088361740630644</v>
       </c>
       <c r="H72" s="12">
-        <f t="shared" si="1"/>
-        <v>-4.6923884125274068E-3</v>
+        <f t="shared" si="2"/>
+        <v>-3.2088361740630644E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
       <c r="F73" s="11" t="s">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="G73" s="10">
-        <v>-0.46173053312736234</v>
+        <v>-0.30536417788281817</v>
       </c>
       <c r="H73" s="12">
-        <f t="shared" si="1"/>
-        <v>-4.6173053312736235E-3</v>
+        <f t="shared" si="2"/>
+        <v>-3.0536417788281818E-3</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
       <c r="F74" s="11" t="s">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="G74" s="10">
-        <v>-0.44554891075458514</v>
+        <v>-0.24664925704046803</v>
       </c>
       <c r="H74" s="12">
-        <f t="shared" si="1"/>
-        <v>-4.4554891075458515E-3</v>
+        <f t="shared" si="2"/>
+        <v>-2.4664925704046803E-3</v>
       </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
       <c r="F75" s="11" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="G75" s="10">
-        <v>-0.3679944396176823</v>
+        <v>-0.23190425111874699</v>
       </c>
       <c r="H75" s="12">
-        <f t="shared" ref="H75:H85" si="2">IF(F75="","",G75/100)</f>
-        <v>-3.6799443961768232E-3</v>
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-2.3190425111874698E-3</v>
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
       <c r="F76" s="11" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G76" s="10">
-        <v>-0.35606298251969726</v>
+        <v>-0.20541433170866308</v>
       </c>
       <c r="H76" s="12">
-        <f t="shared" si="2"/>
-        <v>-3.5606298251969724E-3</v>
+        <f t="shared" si="3"/>
+        <v>-2.0541433170866309E-3</v>
       </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
       <c r="F77" s="11" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="G77" s="10">
-        <v>-0.34449675752917985</v>
+        <v>-0.19230317391100385</v>
       </c>
       <c r="H77" s="12">
-        <f t="shared" si="2"/>
-        <v>-3.4449675752917987E-3</v>
+        <f t="shared" si="3"/>
+        <v>-1.9230317391100385E-3</v>
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
       <c r="F78" s="11" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="G78" s="10">
-        <v>-0.27875728165155722</v>
+        <v>-0.11565380945359117</v>
       </c>
       <c r="H78" s="12">
-        <f t="shared" si="2"/>
-        <v>-2.787572816515572E-3</v>
+        <f t="shared" si="3"/>
+        <v>-1.1565380945359118E-3</v>
       </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
-      <c r="F79" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="G79" s="10">
-        <v>-0.24921887088681788</v>
-      </c>
-      <c r="H79" s="12">
-        <f t="shared" si="2"/>
-        <v>-2.4921887088681788E-3</v>
-      </c>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="13"/>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
-      <c r="F80" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="G80" s="10">
-        <v>-0.23320955251166742</v>
-      </c>
-      <c r="H80" s="12">
-        <f t="shared" si="2"/>
-        <v>-2.3320955251166743E-3</v>
-      </c>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
-      <c r="F81" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="G81" s="10">
-        <v>-0.23178456106778422</v>
-      </c>
-      <c r="H81" s="12">
-        <f t="shared" si="2"/>
-        <v>-2.3178456106778423E-3</v>
-      </c>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="F82" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="G82" s="10">
-        <v>-0.23062227374651528</v>
-      </c>
-      <c r="H82" s="12">
-        <f t="shared" si="2"/>
-        <v>-2.3062227374651529E-3</v>
+      <c r="G82" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="F83" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G83" s="10">
-        <v>-0.2198304019835241</v>
-      </c>
-      <c r="H83" s="12">
-        <f t="shared" si="2"/>
-        <v>-2.198304019835241E-3</v>
-      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="F84" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="G84" s="10">
-        <v>-0.21575192897618961</v>
-      </c>
-      <c r="H84" s="12">
-        <f t="shared" si="2"/>
-        <v>-2.157519289761896E-3</v>
-      </c>
+      <c r="H84" s="1"/>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
-      <c r="F85" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="G85" s="10">
-        <v>-0.17906361599513917</v>
-      </c>
-      <c r="H85" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.7906361599513917E-3</v>
-      </c>
+      <c r="H85" s="1"/>
     </row>
     <row r="86" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D86" s="1"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="13"/>
+      <c r="H86" s="1"/>
     </row>
     <row r="87" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D87" s="1"/>
+      <c r="H87" s="1"/>
     </row>
     <row r="88" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D88" s="1"/>
+      <c r="H88" s="1"/>
     </row>
     <row r="89" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
-      <c r="G89" t="s">
-        <v>5</v>
-      </c>
+      <c r="H89" s="1"/>
     </row>
     <row r="90" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
+      <c r="H90" s="1"/>
     </row>
     <row r="91" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
@@ -3029,57 +3014,63 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -3108,6 +3099,21 @@
     </row>
     <row r="201" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3117,7 +3123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -3141,7 +3147,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -3178,7 +3184,7 @@
     <row r="8" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
@@ -3186,7 +3192,7 @@
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="5" t="s">
@@ -3195,7 +3201,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>2</v>
@@ -3205,7 +3211,7 @@
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>2</v>
@@ -3232,27 +3238,27 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C11" s="10">
-        <v>9.3676345958810714</v>
+        <v>11.360598682213555</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
-        <v>9.3676345958810719E-2</v>
+        <f t="shared" ref="D11:D52" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.11360598682213555</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-6.6747511166068776</v>
+        <v>-7.1465236511326653</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-6.6747511166068779E-2</v>
+        <v>-7.1465236511326649E-2</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
@@ -3260,7 +3266,7 @@
         <v/>
       </c>
       <c r="O11" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="12" t="str">
@@ -3270,24 +3276,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C12" s="10">
-        <v>7.178295390076145</v>
+        <v>7.3223789442194986</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.1782953900761448E-2</v>
+        <v>7.3223789442194986E-2</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.1257189854440615</v>
+        <v>-5.252425636630301</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1257189854440617E-2</v>
+        <v>-5.2524256366303007E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3298,1158 +3304,1257 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C13" s="10">
-        <v>5.0098197800339523</v>
+        <v>5.2371338471596927</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.0098197800339521E-2</v>
+        <v>5.2371338471596925E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="G13" s="10">
-        <v>-5.0593808269021654</v>
+        <v>-4.657430598765564</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0593808269021656E-2</v>
+        <v>-4.6574305987655641E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C14" s="10">
-        <v>4.9893411504096523</v>
+        <v>4.8499200592306648</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.989341150409652E-2</v>
+        <v>4.8499200592306647E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.7845448503728001</v>
+        <v>-4.625419931418211</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7845448503728003E-2</v>
+        <v>-4.6254199314182107E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C15" s="10">
-        <v>4.8934917789138455</v>
+        <v>4.5709296842828993</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.8934917789138457E-2</v>
+        <v>4.5709296842828991E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.2526844426100716</v>
+        <v>-4.4537942425225863</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2526844426100718E-2</v>
+        <v>-4.4537942425225865E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C16" s="10">
-        <v>4.7956028569605618</v>
+        <v>4.4351668733261436</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.7956028569605617E-2</v>
+        <v>4.4351668733261435E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.7538715318079805</v>
+        <v>-4.0710223920934956</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7538715318079806E-2</v>
+        <v>-4.0710223920934957E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C17" s="10">
-        <v>4.6320517671014345</v>
+        <v>4.3869361626066272</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.6320517671014347E-2</v>
+        <v>4.3869361626066271E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.5028928974400122</v>
+        <v>-4.0300444235888992</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5028928974400124E-2</v>
+        <v>-4.0300444235888994E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C18" s="10">
-        <v>4.1488266383129728</v>
+        <v>4.1238389723573805</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.1488266383129725E-2</v>
+        <v>4.1238389723573805E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.4100075996797381</v>
+        <v>-3.9139934025209446</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4100075996797381E-2</v>
+        <v>-3.9139934025209447E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C19" s="10">
-        <v>3.9941428681304529</v>
+        <v>4.0876103987069197</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.9941428681304528E-2</v>
+        <v>4.0876103987069194E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.2883526862952359</v>
+        <v>-3.4383931829236136</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2883526862952359E-2</v>
+        <v>-3.4383931829236138E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="C20" s="10">
-        <v>3.960998571869724</v>
+        <v>3.5982051807134328</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.9609985718697241E-2</v>
+        <v>3.5982051807134326E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.2377588228208172</v>
+        <v>-3.19925255308089</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2377588228208173E-2</v>
+        <v>-3.1992525530808898E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="C21" s="10">
-        <v>3.6679107565062949</v>
+        <v>3.4986501305543851</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.667910756506295E-2</v>
+        <v>3.498650130554385E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.9534394867720826</v>
+        <v>-3.1608527990597519</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9534394867720824E-2</v>
+        <v>-3.1608527990597518E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C22" s="10">
-        <v>3.3901254552592754</v>
+        <v>3.4909462847660033</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.3901254552592755E-2</v>
+        <v>3.4909462847660035E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.8758244405332403</v>
+        <v>-2.6992477945087519</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8758244405332402E-2</v>
+        <v>-2.6992477945087519E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C23" s="10">
-        <v>3.3536380206432495</v>
+        <v>3.4308613324308639</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.3536380206432494E-2</v>
+        <v>3.4308613324308637E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.8675313674108578</v>
+        <v>-2.6427309406746797</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8675313674108579E-2</v>
+        <v>-2.6427309406746799E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="C24" s="10">
-        <v>3.2000877018935543</v>
+        <v>3.4307808726457028</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.2000877018935545E-2</v>
+        <v>3.4307808726457029E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.5902503120703009</v>
+        <v>-2.5198156852531883</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.590250312070301E-2</v>
+        <v>-2.5198156852531885E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C25" s="10">
-        <v>3.1627821872447059</v>
+        <v>3.2894100289545229</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>3.1627821872447059E-2</v>
+        <v>3.2894100289545231E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.5047802005457753</v>
+        <v>-2.502881687272315</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5047802005457753E-2</v>
+        <v>-2.502881687272315E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C26" s="10">
-        <v>3.0505612112986151</v>
+        <v>3.2447562773163225</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>3.050561211298615E-2</v>
+        <v>3.2447562773163227E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.4719791999441085</v>
+        <v>-2.2992191065700536</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4719791999441087E-2</v>
+        <v>-2.2992191065700537E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C27" s="10">
-        <v>2.9758227955613918</v>
+        <v>3.106429686047159</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.975822795561392E-2</v>
+        <v>3.1064296860471588E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.4280737722724806</v>
+        <v>-2.2552449042718847</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4280737722724807E-2</v>
+        <v>-2.2552449042718848E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="C28" s="10">
-        <v>2.5627698903959235</v>
+        <v>3.0319993113769916</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.5627698903959235E-2</v>
+        <v>3.0319993113769917E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.209426104135249</v>
+        <v>-2.2342810572289262</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2094261041352491E-2</v>
+        <v>-2.2342810572289262E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="C29" s="10">
-        <v>2.5098554346299311</v>
+        <v>2.6572137020035593</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.5098554346299311E-2</v>
+        <v>2.6572137020035594E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.1433936519179007</v>
+        <v>-2.1528088078624963</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1433936519179006E-2</v>
+        <v>-2.1528088078624961E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C30" s="10">
-        <v>2.4321920966956521</v>
+        <v>2.6184623830241716</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.4321920966956522E-2</v>
+        <v>2.6184623830241716E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1271937672668861</v>
+        <v>-2.1191678999977666</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1271937672668863E-2</v>
+        <v>-2.1191678999977665E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="C31" s="10">
-        <v>2.2075253833059327</v>
+        <v>2.5507109819371037</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.2075253833059326E-2</v>
+        <v>2.5507109819371036E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0435843613963227</v>
+        <v>-2.0851903615398832</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0435843613963226E-2</v>
+        <v>-2.0851903615398834E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="C32" s="10">
-        <v>2.0981973233901021</v>
+        <v>2.5294670008326556</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.0981973233901021E-2</v>
+        <v>2.5294670008326556E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.0210862608719604</v>
+        <v>-1.9935662452662335</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0210862608719606E-2</v>
+        <v>-1.9935662452662335E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C33" s="10">
-        <v>2.0850481380747117</v>
+        <v>2.325839433713635</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.0850481380747118E-2</v>
+        <v>2.3258394337136348E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9955531802970969</v>
+        <v>-1.9578388136655487</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.995553180297097E-2</v>
+        <v>-1.9578388136655488E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C34" s="10">
-        <v>2.0104689250012719</v>
+        <v>2.288535962129381</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.0104689250012721E-2</v>
+        <v>2.2885359621293809E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.9941591425575136</v>
+        <v>-1.9526454417954988</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9941591425575136E-2</v>
+        <v>-1.9526454417954989E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="C35" s="10">
-        <v>1.9912055076369131</v>
+        <v>2.2706651721560984</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.9912055076369131E-2</v>
+        <v>2.2706651721560986E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.9119858208758242</v>
+        <v>-1.7353219900387054</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9119858208758243E-2</v>
+        <v>-1.7353219900387053E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="C36" s="10">
-        <v>1.9481978272974623</v>
+        <v>2.1498492918847365</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.9481978272974623E-2</v>
+        <v>2.1498492918847364E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.7937745156034437</v>
+        <v>-1.6991631768012412</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7937745156034437E-2</v>
+        <v>-1.6991631768012411E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C37" s="10">
-        <v>1.7446904333315016</v>
+        <v>2.1204859827660343</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.7446904333315017E-2</v>
+        <v>2.1204859827660343E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.7896264676777158</v>
+        <v>-1.6564405314631836</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7896264676777157E-2</v>
+        <v>-1.6564405314631835E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="C38" s="10">
-        <v>1.6067850405688737</v>
+        <v>1.8865232728703381</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.6067850405688738E-2</v>
+        <v>1.8865232728703381E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.7321728084499362</v>
+        <v>-1.6431933208849332</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.732172808449936E-2</v>
+        <v>-1.6431933208849333E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="C39" s="10">
-        <v>1.4968446417390027</v>
+        <v>1.7784042034397534</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.4968446417390027E-2</v>
+        <v>1.7784042034397533E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.6089367918507707</v>
+        <v>-1.5764715795747337</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6089367918507708E-2</v>
+        <v>-1.5764715795747338E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="C40" s="10">
-        <v>0.98481520791170696</v>
+        <v>1.6843748683663697</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>9.8481520791170694E-3</v>
+        <v>1.6843748683663697E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.494577307054914</v>
+        <v>-1.5316039592535979</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.494577307054914E-2</v>
+        <v>-1.5316039592535979E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="C41" s="10">
-        <v>0.94212419763022948</v>
+        <v>1.5277512503401913</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>9.4212419763022946E-3</v>
+        <v>1.5277512503401914E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.4765597546543652</v>
+        <v>-1.4608424364566794</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4765597546543652E-2</v>
+        <v>-1.4608424364566795E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C42" s="10">
-        <v>0.74655664930348975</v>
+        <v>1.5162775134812103</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>7.4655664930348975E-3</v>
+        <v>1.5162775134812102E-2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.4492896285598154</v>
+        <v>-1.4473915039890042</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4492896285598154E-2</v>
+        <v>-1.4473915039890041E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="C43" s="10">
-        <v>0.72041709585217106</v>
+        <v>1.410043443678338</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>7.204170958521711E-3</v>
+        <v>1.4100434436783381E-2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.3909880938269175</v>
+        <v>-1.406816477516841</v>
       </c>
       <c r="H43" s="12">
-        <f t="shared" ref="H43:H73" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.3909880938269175E-2</v>
+        <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
+        <v>-1.406816477516841E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C44" s="10">
-        <v>0.6712714794526613</v>
+        <v>1.2833550101968005</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>6.7127147945266127E-3</v>
+        <v>1.2833550101968006E-2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.3884102113419121</v>
+        <v>-1.3035422702547468</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3884102113419122E-2</v>
+        <v>-1.3035422702547468E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C45" s="10">
-        <v>0.61628335957250424</v>
+        <v>1.1635814021237674</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>6.1628335957250426E-3</v>
+        <v>1.1635814021237674E-2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.3074682183127213</v>
+        <v>-1.2707897784725211</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3074682183127214E-2</v>
+        <v>-1.2707897784725211E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C46" s="10">
-        <v>0.54435032429445362</v>
+        <v>1.028621188242431</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>5.4435032429445366E-3</v>
+        <v>1.0286211882424311E-2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.3069378013300608</v>
+        <v>-1.2559765317916276</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3069378013300608E-2</v>
+        <v>-1.2559765317916275E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>12</v>
+        <v>226</v>
       </c>
       <c r="C47" s="10">
-        <v>0.35372342663835893</v>
+        <v>0.96589864124490898</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="0"/>
-        <v>3.5372342663835894E-3</v>
+        <v>9.6589864124490901E-3</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.3040521026412208</v>
+        <v>-1.236953437648276</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3040521026412209E-2</v>
+        <v>-1.236953437648276E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.96031111646638234</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="0"/>
+        <v>9.6031111646638235E-3</v>
+      </c>
       <c r="F48" s="11" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.2845994016584155</v>
+        <v>-1.2054720030982795</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2845994016584155E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.2054720030982796E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C49" s="10">
+        <v>0.68846737113943057</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="0"/>
+        <v>6.8846737113943055E-3</v>
+      </c>
       <c r="F49" s="11" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.2806145811026568</v>
+        <v>-1.1325393596109783</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2806145811026569E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.1325393596109783E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C50" s="10">
+        <v>0.59826116207443003</v>
+      </c>
+      <c r="D50" s="10">
+        <f t="shared" si="0"/>
+        <v>5.9826116207443002E-3</v>
+      </c>
       <c r="F50" s="11" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.2733598873867638</v>
+        <v>-1.1301898767192593</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2733598873867637E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.1301898767192594E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C51" s="10">
+        <v>0.49461030869547906</v>
+      </c>
+      <c r="D51" s="10">
+        <f t="shared" si="0"/>
+        <v>4.9461030869547909E-3</v>
+      </c>
       <c r="F51" s="11" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="G51" s="10">
-        <v>-1.2325645600528132</v>
+        <v>-1.1104264953873979</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2325645600528132E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.1104264953873979E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="10">
+        <v>0.25503922614777574</v>
+      </c>
+      <c r="D52" s="10">
+        <f t="shared" si="0"/>
+        <v>2.5503922614777573E-3</v>
+      </c>
       <c r="F52" s="11" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.98810854320703134</v>
+        <v>-1.0757973469997824</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-9.8810854320703131E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D53" s="1"/>
+        <v>-1.0757973469997824E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B53" s="9"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
       <c r="F53" s="11" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.94154124273748196</v>
+        <v>-1.0410910258164536</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4154124273748193E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D54" s="1"/>
+        <v>-1.0410910258164536E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F54" s="11" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.89393254013237</v>
+        <v>-1.0113173324924725</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-8.9393254013236997E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D55" s="1"/>
+        <v>-1.0113173324924724E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F55" s="11" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.85959217876515093</v>
+        <v>-0.99299951195439062</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-8.5959217876515094E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D56" s="1"/>
+        <v>-9.9299951195439065E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F56" s="11" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.83076110098309497</v>
+        <v>-0.97283654703583544</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.3076110098309498E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D57" s="1"/>
+        <v>-9.7283654703583539E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F57" s="11" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.82131867111538226</v>
+        <v>-0.9639482417458376</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.2131867111538224E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.6394824174583765E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.79351820000791196</v>
+        <v>-0.96344125935177616</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-7.9351820000791197E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.6344125935177612E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.78645940792387792</v>
+        <v>-0.95932073225472714</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8645940792387795E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.5932073225472713E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.76066545316329681</v>
+        <v>-0.94330194646598109</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.6066545316329677E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.4330194646598114E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.73616695371993224</v>
+        <v>-0.91090194857380546</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.3616695371993227E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.1090194857380551E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.7106220142592159</v>
+        <v>-0.83461735457403963</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.1062201425921593E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.3461735457403957E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.69770510126098817</v>
+        <v>-0.79701140150879368</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9770510126098816E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.9701140150879365E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.69122760876568512</v>
+        <v>-0.78120413334090721</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9122760876568516E-3</v>
+        <v>-7.8120413334090725E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.63807820273744953</v>
+        <v>-0.76789075423596198</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.3807820273744957E-3</v>
+        <v>-7.6789075423596195E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.56896397532157073</v>
+        <v>-0.72496124293161701</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-5.6896397532157075E-3</v>
+        <v>-7.2496124293161702E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.41722081673939365</v>
+        <v>-0.65253243046582754</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-4.1722081673939366E-3</v>
+        <v>-6.5253243046582751E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.3938261891657775</v>
+        <v>-0.61445765966219379</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-3.9382618916577747E-3</v>
+        <v>-6.1445765966219382E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.39343732974725998</v>
+        <v>-0.46406545906470265</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-3.9343732974726001E-3</v>
+        <v>-4.6406545906470262E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.37300865403654426</v>
+        <v>-0.4394205411225075</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-3.7300865403654426E-3</v>
+        <v>-4.3942054112250748E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.34174543086615383</v>
+        <v>-0.43136734552093792</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-3.4174543086615385E-3</v>
+        <v>-4.3136734552093794E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.25310390078560174</v>
+        <v>-0.41302437236795692</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-2.5310390078560176E-3</v>
+        <v>-4.130243723679569E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
       <c r="F73" s="11" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="G73" s="10">
-        <v>-2.7968664389488827E-2</v>
+        <v>-0.32088361740630644</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>-2.7968664389488827E-4</v>
+        <v>-3.2088361740630644E-3</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="13"/>
+      <c r="F74" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-0.30536417788281817</v>
+      </c>
+      <c r="H74" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.0536417788281818E-3</v>
+      </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
+      <c r="F75" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-0.24664925704046803</v>
+      </c>
+      <c r="H75" s="12">
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-2.4664925704046803E-3</v>
+      </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
+      <c r="F76" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-0.23190425111874699</v>
+      </c>
+      <c r="H76" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.3190425111874698E-3</v>
+      </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
-      <c r="G77" t="s">
-        <v>5</v>
+      <c r="F77" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-0.20541433170866308</v>
+      </c>
+      <c r="H77" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.0541433170866309E-3</v>
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
+      <c r="F78" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-0.19230317391100385</v>
+      </c>
+      <c r="H78" s="12">
+        <f t="shared" si="3"/>
+        <v>-1.9230317391100385E-3</v>
+      </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
-      <c r="H79" s="1"/>
+      <c r="F79" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-0.11565380945359117</v>
+      </c>
+      <c r="H79" s="12">
+        <f t="shared" si="3"/>
+        <v>-1.1565380945359118E-3</v>
+      </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
-      <c r="H80" s="1"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="13"/>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
+      <c r="G83" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="H84" s="1"/>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
@@ -4819,52 +4924,57 @@
       <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D181" s="1"/>
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -4893,6 +5003,24 @@
     </row>
     <row r="201" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
